--- a/New joiner-Details.xlsx
+++ b/New joiner-Details.xlsx
@@ -1,30 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26707"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr updateLinks="always" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ruby-lnu\OneDrive - MMC\Desktop\INDIA - TA Ops Templates\TA Ops Process Material\Updated Welcome Letter\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ps2385\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{631E87FB-ACAC-41BE-89C4-9FAEC9507B74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E1AC5538-1F2D-44D7-A0C2-AF188779B5A9}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74187666-B779-48DE-8214-07850079A438}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="New Joiner Form" sheetId="4" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="13" r:id="rId2"/>
-    <sheet name="Data" sheetId="5" state="hidden" r:id="rId3"/>
-    <sheet name="Joining Detail Form" sheetId="6" state="hidden" r:id="rId4"/>
-    <sheet name="Access Request Form" sheetId="7" state="hidden" r:id="rId5"/>
-    <sheet name="Transport Form" sheetId="8" state="hidden" r:id="rId6"/>
-    <sheet name="Mediclaim Form" sheetId="9" state="hidden" r:id="rId7"/>
-    <sheet name="Gratuity Nom Form" sheetId="10" state="hidden" r:id="rId8"/>
-    <sheet name="Life Insurance Nomination Form" sheetId="11" state="hidden" r:id="rId9"/>
-    <sheet name="Security Policy Form" sheetId="12" state="hidden" r:id="rId10"/>
+    <sheet name="Data" sheetId="5" state="hidden" r:id="rId2"/>
+    <sheet name="Joining Detail Form" sheetId="6" state="hidden" r:id="rId3"/>
+    <sheet name="Access Request Form" sheetId="7" state="hidden" r:id="rId4"/>
+    <sheet name="Transport Form" sheetId="8" state="hidden" r:id="rId5"/>
+    <sheet name="Mediclaim Form" sheetId="9" state="hidden" r:id="rId6"/>
+    <sheet name="Gratuity Nom Form" sheetId="10" state="hidden" r:id="rId7"/>
+    <sheet name="Life Insurance Nomination Form" sheetId="11" state="hidden" r:id="rId8"/>
+    <sheet name="Security Policy Form" sheetId="12" state="hidden" r:id="rId9"/>
   </sheets>
-  <calcPr calcId="191028" iterate="1"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -45,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="406">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="440">
   <si>
     <t>New Joiner Onboarding Form</t>
   </si>
@@ -249,7 +248,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="0"/>
-        <rFont val="Calibri"/>
+        <rFont val="Mangal"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -268,7 +267,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="0"/>
-        <rFont val="Calibri"/>
+        <rFont val="Mangal"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -287,7 +286,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="0"/>
-        <rFont val="Calibri"/>
+        <rFont val="Mangal"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -311,7 +310,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="0"/>
-        <rFont val="Calibri"/>
+        <rFont val="Mangal"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -331,7 +330,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="0"/>
-        <rFont val="Calibri"/>
+        <rFont val="Mangal"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -350,7 +349,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="0"/>
-        <rFont val="Calibri"/>
+        <rFont val="Mangal"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -370,7 +369,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="0"/>
-        <rFont val="Calibri"/>
+        <rFont val="Mangal"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -389,7 +388,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="0"/>
-        <rFont val="Calibri"/>
+        <rFont val="Mangal"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -408,7 +407,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="0"/>
-        <rFont val="Calibri"/>
+        <rFont val="Mangal"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -427,7 +426,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="0"/>
-        <rFont val="Calibri"/>
+        <rFont val="Mangal"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -446,7 +445,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="0"/>
-        <rFont val="Calibri"/>
+        <rFont val="Mangal"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -1485,7 +1484,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="Mangal"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -1575,7 +1574,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="Mangal"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -1587,7 +1586,7 @@
         <b/>
         <sz val="12"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="Mangal"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -1598,7 +1597,7 @@
       <rPr>
         <sz val="12"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="Mangal"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -1614,7 +1613,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="Mangal"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -1624,7 +1623,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="Mangal"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -1638,7 +1637,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="Mangal"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -1827,27 +1826,136 @@
   <si>
     <t>User Signature:</t>
   </si>
+  <si>
+    <t>Pushkar Singh</t>
+  </si>
+  <si>
+    <t>Male</t>
+  </si>
+  <si>
+    <t>Satender Kumar</t>
+  </si>
+  <si>
+    <t>Suman</t>
+  </si>
+  <si>
+    <t>23/04/1994</t>
+  </si>
+  <si>
+    <t>A+</t>
+  </si>
+  <si>
+    <t>Hindu</t>
+  </si>
+  <si>
+    <t>159-160,1st floor, Pocket-7, Sector-24 Rohini</t>
+  </si>
+  <si>
+    <t>Delhi</t>
+  </si>
+  <si>
+    <t>India</t>
+  </si>
+  <si>
+    <t>JABPS9654C</t>
+  </si>
+  <si>
+    <t>B8876011</t>
+  </si>
+  <si>
+    <t>Father</t>
+  </si>
+  <si>
+    <t>Mother</t>
+  </si>
+  <si>
+    <t>Suman
+159-160,1st floor, Pocket-7, Sector-24 Rohini Delhi-85 
+Mother</t>
+  </si>
+  <si>
+    <t>Satender Kumar
+159-160,1st floor, Pocket-7, Sector-24 Rohini Delhi-85
+Father</t>
+  </si>
+  <si>
+    <t>Satender Kumar
+159-160,1st floor, Pocket-7, Sector-24 Rohini Delhi-85</t>
+  </si>
+  <si>
+    <t>Suman
+159-160,1st floor, Pocket-7, Sector-24 Rohini Delhi-85</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>pushkar23.saini04@gmail.com</t>
+  </si>
+  <si>
+    <t>U</t>
+  </si>
+  <si>
+    <t>Indian</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>9th November 2026</t>
+  </si>
+  <si>
+    <t>P</t>
+  </si>
+  <si>
+    <t>DSNHP09434290000010565</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>20/12/2023</t>
+  </si>
+  <si>
+    <t>19/12/2033</t>
+  </si>
+  <si>
+    <t>G</t>
+  </si>
+  <si>
+    <t>UTIB0005140</t>
+  </si>
+  <si>
+    <t>30th Oct 2026</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="[$-409]mmmm\ d\,\ yyyy;@"/>
     <numFmt numFmtId="165" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Mangal"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Mangal"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1855,28 +1963,28 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Mangal"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="Calibri"/>
+      <name val="Mangal"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="24"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Mangal"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="14"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Mangal"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1890,7 +1998,7 @@
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Mangal"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1899,7 +2007,7 @@
       <u/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Mangal"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1919,7 +2027,7 @@
       <b/>
       <sz val="14"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Mangal"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1927,7 +2035,7 @@
       <b/>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Mangal"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1935,7 +2043,7 @@
       <b/>
       <sz val="18"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Mangal"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1944,7 +2052,7 @@
       <u/>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Mangal"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -2001,7 +2109,7 @@
     <font>
       <sz val="14"/>
       <color theme="0"/>
-      <name val="Calibri"/>
+      <name val="Mangal"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -2016,6 +2124,14 @@
       <color theme="0"/>
       <name val="Tahoma"/>
       <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Mangal"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="7">
@@ -2585,11 +2701,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="232">
+  <cellXfs count="235">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2785,14 +2903,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -2921,6 +3033,21 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="34" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="1" fontId="20" fillId="0" borderId="34" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="1" fontId="20" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -3267,7 +3394,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="4">
+    <cellStyle name="Comma" xfId="2" builtinId="3"/>
+    <cellStyle name="Hyperlink" xfId="3" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
@@ -4102,174 +4231,214 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:AF45"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="25.5" x14ac:dyDescent="0.7"/>
   <cols>
-    <col min="1" max="1" width="54.42578125" style="31" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="54.44140625" style="31" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="32" style="31" customWidth="1"/>
     <col min="3" max="3" width="29" style="31" customWidth="1"/>
-    <col min="4" max="4" width="26.85546875" style="31" customWidth="1"/>
-    <col min="5" max="5" width="30.5703125" style="31" customWidth="1"/>
-    <col min="6" max="6" width="25.85546875" style="31" customWidth="1"/>
-    <col min="7" max="7" width="23.140625" style="31" customWidth="1"/>
-    <col min="8" max="8" width="9.140625"/>
-    <col min="9" max="9" width="40.140625" customWidth="1"/>
-    <col min="10" max="10" width="27.7109375" customWidth="1"/>
-    <col min="11" max="11" width="29.42578125" customWidth="1"/>
-    <col min="12" max="12" width="19.85546875" customWidth="1"/>
-    <col min="13" max="13" width="40.5703125" customWidth="1"/>
-    <col min="14" max="14" width="30.42578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="47.42578125" customWidth="1"/>
-    <col min="16" max="16" width="32.140625" customWidth="1"/>
-    <col min="17" max="17" width="17.42578125" customWidth="1"/>
-    <col min="18" max="18" width="40.5703125" customWidth="1"/>
-    <col min="19" max="19" width="35.42578125" customWidth="1"/>
-    <col min="20" max="21" width="9.140625"/>
-    <col min="22" max="22" width="12.85546875" customWidth="1"/>
-    <col min="23" max="24" width="9.140625"/>
-    <col min="25" max="25" width="26.85546875" customWidth="1"/>
-    <col min="26" max="28" width="9.140625"/>
-    <col min="29" max="29" width="18.85546875" customWidth="1"/>
-    <col min="30" max="30" width="25.140625" customWidth="1"/>
-    <col min="31" max="31" width="25.85546875" customWidth="1"/>
-    <col min="32" max="32" width="36.85546875" customWidth="1"/>
+    <col min="4" max="4" width="26.88671875" style="31" customWidth="1"/>
+    <col min="5" max="5" width="30.5546875" style="31" customWidth="1"/>
+    <col min="6" max="6" width="25.88671875" style="31" customWidth="1"/>
+    <col min="7" max="7" width="37.88671875" style="31" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.109375"/>
+    <col min="9" max="9" width="40.109375" customWidth="1"/>
+    <col min="10" max="10" width="27.6640625" customWidth="1"/>
+    <col min="11" max="11" width="29.44140625" customWidth="1"/>
+    <col min="12" max="12" width="19.88671875" customWidth="1"/>
+    <col min="13" max="13" width="40.5546875" customWidth="1"/>
+    <col min="14" max="14" width="30.44140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="47.44140625" customWidth="1"/>
+    <col min="16" max="16" width="32.109375" customWidth="1"/>
+    <col min="17" max="17" width="17.44140625" customWidth="1"/>
+    <col min="18" max="18" width="40.5546875" customWidth="1"/>
+    <col min="19" max="19" width="35.44140625" customWidth="1"/>
+    <col min="20" max="21" width="9.109375"/>
+    <col min="22" max="22" width="12.88671875" customWidth="1"/>
+    <col min="23" max="24" width="9.109375"/>
+    <col min="25" max="25" width="26.88671875" customWidth="1"/>
+    <col min="26" max="26" width="19.21875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="23" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="18.88671875" customWidth="1"/>
+    <col min="30" max="30" width="25.109375" customWidth="1"/>
+    <col min="31" max="31" width="25.88671875" customWidth="1"/>
+    <col min="32" max="32" width="36.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15" customHeight="1">
-      <c r="A1" s="131" t="s">
+    <row r="1" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A1" s="134" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="132"/>
-      <c r="C1" s="132"/>
-      <c r="D1" s="132"/>
-      <c r="E1" s="132"/>
-      <c r="F1" s="132"/>
-      <c r="G1" s="133"/>
-    </row>
-    <row r="2" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A2" s="134"/>
-      <c r="B2" s="135"/>
-      <c r="C2" s="135"/>
-      <c r="D2" s="135"/>
-      <c r="E2" s="135"/>
-      <c r="F2" s="135"/>
-      <c r="G2" s="136"/>
-    </row>
-    <row r="3" spans="1:7" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A3" s="137"/>
-      <c r="B3" s="138"/>
-      <c r="C3" s="138"/>
-      <c r="D3" s="138"/>
-      <c r="E3" s="138"/>
-      <c r="F3" s="138"/>
-      <c r="G3" s="139"/>
-    </row>
-    <row r="4" spans="1:7" ht="18.600000000000001">
-      <c r="A4" s="122" t="s">
+      <c r="B1" s="135"/>
+      <c r="C1" s="135"/>
+      <c r="D1" s="135"/>
+      <c r="E1" s="135"/>
+      <c r="F1" s="135"/>
+      <c r="G1" s="136"/>
+    </row>
+    <row r="2" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A2" s="137"/>
+      <c r="B2" s="138"/>
+      <c r="C2" s="138"/>
+      <c r="D2" s="138"/>
+      <c r="E2" s="138"/>
+      <c r="F2" s="138"/>
+      <c r="G2" s="139"/>
+    </row>
+    <row r="3" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A3" s="140"/>
+      <c r="B3" s="141"/>
+      <c r="C3" s="141"/>
+      <c r="D3" s="141"/>
+      <c r="E3" s="141"/>
+      <c r="F3" s="141"/>
+      <c r="G3" s="142"/>
+    </row>
+    <row r="4" spans="1:7" ht="30.75" x14ac:dyDescent="0.7">
+      <c r="A4" s="125" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="123"/>
-      <c r="C4" s="123"/>
-      <c r="D4" s="123"/>
-      <c r="E4" s="123"/>
-      <c r="F4" s="123"/>
-      <c r="G4" s="124"/>
-    </row>
-    <row r="5" spans="1:7" ht="15" customHeight="1">
-      <c r="A5" s="143" t="s">
+      <c r="B4" s="126"/>
+      <c r="C4" s="126"/>
+      <c r="D4" s="126"/>
+      <c r="E4" s="126"/>
+      <c r="F4" s="126"/>
+      <c r="G4" s="127"/>
+    </row>
+    <row r="5" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A5" s="146" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="144"/>
-      <c r="C5" s="1"/>
+      <c r="B5" s="147"/>
+      <c r="C5" s="1" t="s">
+        <v>406</v>
+      </c>
       <c r="D5" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="E5" s="45"/>
+      <c r="E5" s="45" t="s">
+        <v>413</v>
+      </c>
       <c r="F5" s="62" t="s">
         <v>4</v>
       </c>
-      <c r="G5" s="46"/>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="143" t="s">
+      <c r="G5" s="45" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.7">
+      <c r="A6" s="146" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="144"/>
-      <c r="C6" s="1"/>
+      <c r="B6" s="147"/>
+      <c r="C6" s="1" t="s">
+        <v>407</v>
+      </c>
       <c r="D6" s="62" t="s">
         <v>6</v>
       </c>
-      <c r="E6" s="45"/>
+      <c r="E6" s="45" t="s">
+        <v>414</v>
+      </c>
       <c r="F6" s="62" t="s">
         <v>6</v>
       </c>
-      <c r="G6" s="46"/>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="143" t="s">
+      <c r="G6" s="45" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.7">
+      <c r="A7" s="146" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="144"/>
-      <c r="C7" s="1"/>
+      <c r="B7" s="147"/>
+      <c r="C7" s="1" t="s">
+        <v>408</v>
+      </c>
       <c r="D7" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="E7" s="45"/>
+      <c r="E7" s="45" t="s">
+        <v>414</v>
+      </c>
       <c r="F7" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="G7" s="46"/>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="143" t="s">
+      <c r="G7" s="45" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.7">
+      <c r="A8" s="146" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="144"/>
-      <c r="C8" s="1"/>
+      <c r="B8" s="147"/>
+      <c r="C8" s="1" t="s">
+        <v>409</v>
+      </c>
       <c r="D8" s="62" t="s">
         <v>10</v>
       </c>
-      <c r="E8" s="45"/>
+      <c r="E8" s="45" t="s">
+        <v>415</v>
+      </c>
       <c r="F8" s="62" t="s">
         <v>10</v>
       </c>
-      <c r="G8" s="46"/>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="143" t="s">
+      <c r="G8" s="46" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.7">
+      <c r="A9" s="146" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="144"/>
-      <c r="C9" s="43"/>
+      <c r="B9" s="147"/>
+      <c r="C9" s="43" t="s">
+        <v>410</v>
+      </c>
       <c r="D9" s="62" t="s">
         <v>12</v>
       </c>
-      <c r="E9" s="44"/>
+      <c r="E9" s="44">
+        <v>110085</v>
+      </c>
       <c r="F9" s="62" t="s">
         <v>12</v>
       </c>
-      <c r="G9" s="71"/>
-    </row>
-    <row r="10" spans="1:7" ht="15" customHeight="1">
-      <c r="A10" s="143" t="s">
+      <c r="G9" s="44">
+        <v>110085</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A10" s="146" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="144"/>
-      <c r="C10" s="1"/>
+      <c r="B10" s="147"/>
+      <c r="C10" s="1" t="s">
+        <v>411</v>
+      </c>
       <c r="D10" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="E10" s="45"/>
+      <c r="E10" s="45">
+        <v>9313569413</v>
+      </c>
       <c r="F10" s="62" t="s">
         <v>15</v>
       </c>
-      <c r="G10" s="71"/>
-    </row>
-    <row r="11" spans="1:7" ht="15" customHeight="1">
-      <c r="A11" s="143" t="s">
+      <c r="G10" s="115">
+        <v>720812235123</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A11" s="146" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="144"/>
-      <c r="C11" s="1"/>
+      <c r="B11" s="147"/>
+      <c r="C11" s="1" t="s">
+        <v>412</v>
+      </c>
       <c r="D11" s="62" t="s">
         <v>17</v>
       </c>
@@ -4277,66 +4446,72 @@
       <c r="F11" s="62" t="s">
         <v>18</v>
       </c>
-      <c r="G11" s="46"/>
-    </row>
-    <row r="12" spans="1:7" ht="15" thickBot="1">
-      <c r="A12" s="145" t="s">
+      <c r="G11" s="46" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="26.25" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A12" s="148" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="146"/>
+      <c r="B12" s="149"/>
       <c r="C12" s="47"/>
       <c r="D12" s="63" t="s">
         <v>20</v>
       </c>
-      <c r="E12" s="47"/>
+      <c r="E12" s="47">
+        <v>9711396405</v>
+      </c>
       <c r="F12" s="63" t="s">
         <v>21</v>
       </c>
-      <c r="G12" s="48"/>
-    </row>
-    <row r="15" spans="1:7" hidden="1"/>
-    <row r="16" spans="1:7" ht="18.95" hidden="1" thickBot="1">
-      <c r="A16" s="128" t="s">
+      <c r="G12" s="48" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" hidden="1" x14ac:dyDescent="0.7"/>
+    <row r="16" spans="1:7" ht="31.5" hidden="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A16" s="131" t="s">
         <v>22</v>
       </c>
-      <c r="B16" s="129"/>
-      <c r="C16" s="129"/>
-      <c r="D16" s="129"/>
-      <c r="E16" s="129"/>
-      <c r="F16" s="129"/>
-      <c r="G16" s="130"/>
-    </row>
-    <row r="17" spans="1:7" hidden="1">
-      <c r="A17" s="125" t="s">
+      <c r="B16" s="132"/>
+      <c r="C16" s="132"/>
+      <c r="D16" s="132"/>
+      <c r="E16" s="132"/>
+      <c r="F16" s="132"/>
+      <c r="G16" s="133"/>
+    </row>
+    <row r="17" spans="1:7" hidden="1" x14ac:dyDescent="0.7">
+      <c r="A17" s="128" t="s">
         <v>23</v>
       </c>
-      <c r="B17" s="126"/>
-      <c r="C17" s="126"/>
-      <c r="D17" s="126"/>
-      <c r="E17" s="126"/>
-      <c r="F17" s="126"/>
-      <c r="G17" s="127"/>
-    </row>
-    <row r="18" spans="1:7" ht="15" hidden="1" customHeight="1">
+      <c r="B17" s="129"/>
+      <c r="C17" s="129"/>
+      <c r="D17" s="129"/>
+      <c r="E17" s="129"/>
+      <c r="F17" s="129"/>
+      <c r="G17" s="130"/>
+    </row>
+    <row r="18" spans="1:7" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A18" s="64" t="s">
         <v>24</v>
       </c>
       <c r="B18" s="62" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="72" t="s">
+      <c r="C18" s="71" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="72" t="s">
+      <c r="D18" s="71" t="s">
         <v>27</v>
       </c>
-      <c r="E18" s="72" t="s">
+      <c r="E18" s="71" t="s">
         <v>28</v>
       </c>
       <c r="F18" s="62"/>
       <c r="G18" s="65"/>
     </row>
-    <row r="19" spans="1:7" ht="15" hidden="1" customHeight="1">
+    <row r="19" spans="1:7" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A19" s="52"/>
       <c r="B19" s="1"/>
       <c r="C19" s="56"/>
@@ -4345,7 +4520,7 @@
       <c r="F19" s="51"/>
       <c r="G19" s="46"/>
     </row>
-    <row r="20" spans="1:7" ht="15" hidden="1" customHeight="1">
+    <row r="20" spans="1:7" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A20" s="52"/>
       <c r="B20" s="1"/>
       <c r="C20" s="56"/>
@@ -4354,7 +4529,7 @@
       <c r="F20" s="51"/>
       <c r="G20" s="46"/>
     </row>
-    <row r="21" spans="1:7" hidden="1">
+    <row r="21" spans="1:7" hidden="1" x14ac:dyDescent="0.7">
       <c r="A21" s="53"/>
       <c r="B21" s="44"/>
       <c r="C21" s="55"/>
@@ -4363,7 +4538,7 @@
       <c r="F21" s="51"/>
       <c r="G21" s="61"/>
     </row>
-    <row r="22" spans="1:7" hidden="1">
+    <row r="22" spans="1:7" hidden="1" x14ac:dyDescent="0.7">
       <c r="A22" s="53"/>
       <c r="B22" s="44"/>
       <c r="C22" s="55"/>
@@ -4372,7 +4547,7 @@
       <c r="F22" s="51"/>
       <c r="G22" s="61"/>
     </row>
-    <row r="23" spans="1:7" ht="15.75" hidden="1" customHeight="1">
+    <row r="23" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A23" s="53"/>
       <c r="B23" s="1"/>
       <c r="C23" s="44"/>
@@ -4381,45 +4556,45 @@
       <c r="F23" s="45"/>
       <c r="G23" s="46"/>
     </row>
-    <row r="24" spans="1:7" ht="15" hidden="1" thickBot="1">
-      <c r="A24" s="140" t="s">
+    <row r="24" spans="1:7" ht="26.25" hidden="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A24" s="143" t="s">
         <v>29</v>
       </c>
-      <c r="B24" s="141"/>
-      <c r="C24" s="141"/>
-      <c r="D24" s="141"/>
-      <c r="E24" s="141"/>
-      <c r="F24" s="141"/>
-      <c r="G24" s="142"/>
-    </row>
-    <row r="25" spans="1:7" hidden="1">
+      <c r="B24" s="144"/>
+      <c r="C24" s="144"/>
+      <c r="D24" s="144"/>
+      <c r="E24" s="144"/>
+      <c r="F24" s="144"/>
+      <c r="G24" s="145"/>
+    </row>
+    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.7">
       <c r="E25" s="2"/>
       <c r="F25" s="2"/>
     </row>
-    <row r="26" spans="1:7" ht="15" thickBot="1"/>
-    <row r="27" spans="1:7" ht="18.95" thickBot="1">
-      <c r="A27" s="122" t="s">
+    <row r="26" spans="1:7" ht="26.25" thickBot="1" x14ac:dyDescent="0.75"/>
+    <row r="27" spans="1:7" ht="31.5" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A27" s="125" t="s">
         <v>30</v>
       </c>
-      <c r="B27" s="123"/>
-      <c r="C27" s="123"/>
-      <c r="D27" s="123"/>
-      <c r="E27" s="123"/>
-      <c r="F27" s="123"/>
-      <c r="G27" s="124"/>
-    </row>
-    <row r="28" spans="1:7" ht="15" thickBot="1">
-      <c r="A28" s="125" t="s">
+      <c r="B27" s="126"/>
+      <c r="C27" s="126"/>
+      <c r="D27" s="126"/>
+      <c r="E27" s="126"/>
+      <c r="F27" s="126"/>
+      <c r="G27" s="127"/>
+    </row>
+    <row r="28" spans="1:7" ht="26.25" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A28" s="128" t="s">
         <v>31</v>
       </c>
-      <c r="B28" s="126"/>
-      <c r="C28" s="126"/>
-      <c r="D28" s="126"/>
-      <c r="E28" s="126"/>
-      <c r="F28" s="126"/>
-      <c r="G28" s="127"/>
-    </row>
-    <row r="29" spans="1:7" ht="87">
+      <c r="B28" s="129"/>
+      <c r="C28" s="129"/>
+      <c r="D28" s="129"/>
+      <c r="E28" s="129"/>
+      <c r="F28" s="129"/>
+      <c r="G28" s="130"/>
+    </row>
+    <row r="29" spans="1:7" ht="144" x14ac:dyDescent="0.7">
       <c r="A29" s="66" t="s">
         <v>32</v>
       </c>
@@ -4440,25 +4615,49 @@
       </c>
       <c r="G29" s="69"/>
     </row>
-    <row r="30" spans="1:7">
-      <c r="A30" s="50"/>
-      <c r="B30" s="56"/>
-      <c r="C30" s="56"/>
-      <c r="D30" s="56"/>
-      <c r="E30" s="56"/>
-      <c r="F30" s="56"/>
+    <row r="30" spans="1:7" ht="102" x14ac:dyDescent="0.7">
+      <c r="A30" s="50" t="s">
+        <v>422</v>
+      </c>
+      <c r="B30" s="56" t="s">
+        <v>418</v>
+      </c>
+      <c r="C30" s="56">
+        <v>67</v>
+      </c>
+      <c r="D30" s="116">
+        <v>0.5</v>
+      </c>
+      <c r="E30" s="56" t="s">
+        <v>424</v>
+      </c>
+      <c r="F30" s="50" t="s">
+        <v>420</v>
+      </c>
       <c r="G30" s="70"/>
     </row>
-    <row r="31" spans="1:7">
-      <c r="A31" s="50"/>
-      <c r="B31" s="56"/>
-      <c r="C31" s="56"/>
-      <c r="D31" s="56"/>
-      <c r="E31" s="56"/>
-      <c r="F31" s="56"/>
+    <row r="31" spans="1:7" ht="102" x14ac:dyDescent="0.7">
+      <c r="A31" s="50" t="s">
+        <v>423</v>
+      </c>
+      <c r="B31" s="56" t="s">
+        <v>419</v>
+      </c>
+      <c r="C31" s="56">
+        <v>58</v>
+      </c>
+      <c r="D31" s="116">
+        <v>0.5</v>
+      </c>
+      <c r="E31" s="56" t="s">
+        <v>424</v>
+      </c>
+      <c r="F31" s="50" t="s">
+        <v>421</v>
+      </c>
       <c r="G31" s="70"/>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.7">
       <c r="A32" s="50"/>
       <c r="B32" s="56"/>
       <c r="C32" s="56"/>
@@ -4467,7 +4666,7 @@
       <c r="F32" s="56"/>
       <c r="G32" s="70"/>
     </row>
-    <row r="33" spans="1:32" ht="15" customHeight="1">
+    <row r="33" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A33" s="50"/>
       <c r="B33" s="56"/>
       <c r="C33" s="56"/>
@@ -4476,7 +4675,7 @@
       <c r="F33" s="55"/>
       <c r="G33" s="70"/>
     </row>
-    <row r="34" spans="1:32" ht="15.75" customHeight="1" thickBot="1">
+    <row r="34" spans="1:32" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
       <c r="A34" s="54"/>
       <c r="B34" s="57"/>
       <c r="C34" s="58"/>
@@ -4485,7 +4684,7 @@
       <c r="F34" s="58"/>
       <c r="G34" s="48"/>
     </row>
-    <row r="35" spans="1:32">
+    <row r="35" spans="1:32" x14ac:dyDescent="0.7">
       <c r="A35" s="49"/>
       <c r="B35" s="49"/>
       <c r="C35" s="49"/>
@@ -4493,8 +4692,8 @@
       <c r="E35" s="49"/>
       <c r="F35" s="49"/>
     </row>
-    <row r="36" spans="1:32" ht="16.5" customHeight="1">
-      <c r="A36" s="112" t="s">
+    <row r="36" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A36" s="110" t="s">
         <v>37</v>
       </c>
       <c r="B36" s="49"/>
@@ -4503,181 +4702,241 @@
       <c r="F36"/>
       <c r="G36"/>
     </row>
-    <row r="37" spans="1:32">
-      <c r="A37" s="51"/>
+    <row r="37" spans="1:32" x14ac:dyDescent="0.7">
+      <c r="A37" s="51" t="s">
+        <v>424</v>
+      </c>
       <c r="B37" s="49"/>
       <c r="C37" s="49"/>
       <c r="D37" s="49"/>
       <c r="E37" s="49"/>
       <c r="F37" s="49"/>
     </row>
-    <row r="38" spans="1:32">
+    <row r="38" spans="1:32" x14ac:dyDescent="0.7">
       <c r="C38" s="34"/>
       <c r="D38" s="5"/>
       <c r="E38" s="5"/>
-      <c r="F38" s="77"/>
+      <c r="F38" s="75"/>
       <c r="G38" s="5"/>
     </row>
-    <row r="39" spans="1:32" ht="15" thickBot="1"/>
-    <row r="40" spans="1:32" s="109" customFormat="1" ht="40.5" customHeight="1" thickBot="1">
-      <c r="A40" s="113" t="s">
+    <row r="39" spans="1:32" ht="26.25" thickBot="1" x14ac:dyDescent="0.75"/>
+    <row r="40" spans="1:32" s="107" customFormat="1" ht="40.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A40" s="111" t="s">
         <v>38</v>
       </c>
-      <c r="B40" s="114" t="s">
+      <c r="B40" s="112" t="s">
         <v>39</v>
       </c>
-      <c r="C40" s="114" t="s">
+      <c r="C40" s="112" t="s">
         <v>40</v>
       </c>
-      <c r="D40" s="114" t="s">
+      <c r="D40" s="112" t="s">
         <v>41</v>
       </c>
-      <c r="E40" s="114" t="s">
+      <c r="E40" s="112" t="s">
         <v>42</v>
       </c>
-      <c r="F40" s="114" t="s">
+      <c r="F40" s="112" t="s">
         <v>43</v>
       </c>
-      <c r="G40" s="114" t="s">
+      <c r="G40" s="112" t="s">
         <v>44</v>
       </c>
-      <c r="H40" s="114" t="s">
+      <c r="H40" s="112" t="s">
         <v>45</v>
       </c>
-      <c r="I40" s="114" t="s">
+      <c r="I40" s="112" t="s">
         <v>46</v>
       </c>
-      <c r="J40" s="114" t="s">
+      <c r="J40" s="112" t="s">
         <v>47</v>
       </c>
-      <c r="K40" s="114" t="s">
+      <c r="K40" s="112" t="s">
         <v>48</v>
       </c>
-      <c r="L40" s="114" t="s">
+      <c r="L40" s="112" t="s">
         <v>49</v>
       </c>
-      <c r="M40" s="114" t="s">
+      <c r="M40" s="112" t="s">
         <v>50</v>
       </c>
-      <c r="N40" s="114" t="s">
+      <c r="N40" s="112" t="s">
         <v>51</v>
       </c>
-      <c r="O40" s="114" t="s">
+      <c r="O40" s="112" t="s">
         <v>52</v>
       </c>
-      <c r="P40" s="114" t="s">
+      <c r="P40" s="112" t="s">
         <v>53</v>
       </c>
-      <c r="Q40" s="114" t="s">
+      <c r="Q40" s="112" t="s">
         <v>54</v>
       </c>
-      <c r="R40" s="114" t="s">
+      <c r="R40" s="112" t="s">
         <v>55</v>
       </c>
-      <c r="S40" s="114" t="s">
+      <c r="S40" s="112" t="s">
         <v>56</v>
       </c>
-      <c r="T40" s="114" t="s">
+      <c r="T40" s="112" t="s">
         <v>57</v>
       </c>
-      <c r="U40" s="114" t="s">
+      <c r="U40" s="112" t="s">
         <v>58</v>
       </c>
-      <c r="V40" s="114" t="s">
+      <c r="V40" s="112" t="s">
         <v>59</v>
       </c>
-      <c r="W40" s="114" t="s">
+      <c r="W40" s="112" t="s">
         <v>60</v>
       </c>
-      <c r="X40" s="114" t="s">
+      <c r="X40" s="112" t="s">
         <v>61</v>
       </c>
-      <c r="Y40" s="111" t="s">
+      <c r="Y40" s="109" t="s">
         <v>62</v>
       </c>
-      <c r="Z40" s="115" t="s">
+      <c r="Z40" s="113" t="s">
         <v>63</v>
       </c>
-      <c r="AA40" s="115" t="s">
+      <c r="AA40" s="113" t="s">
         <v>64</v>
       </c>
-      <c r="AB40" s="115" t="s">
+      <c r="AB40" s="113" t="s">
         <v>65</v>
       </c>
-      <c r="AC40" s="115" t="s">
+      <c r="AC40" s="113" t="s">
         <v>66</v>
       </c>
-      <c r="AD40" s="115" t="s">
+      <c r="AD40" s="113" t="s">
         <v>67</v>
       </c>
-      <c r="AE40" s="115" t="s">
+      <c r="AE40" s="113" t="s">
         <v>68</v>
       </c>
-      <c r="AF40" s="116" t="s">
+      <c r="AF40" s="114" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="41" spans="1:32" s="109" customFormat="1" ht="14.1">
-      <c r="A41" s="110"/>
-      <c r="B41" s="110"/>
-      <c r="C41" s="110"/>
-      <c r="D41" s="110"/>
-      <c r="E41" s="110"/>
-      <c r="F41" s="110"/>
-      <c r="G41" s="110"/>
-      <c r="H41" s="110"/>
-      <c r="I41" s="110"/>
-      <c r="J41" s="110"/>
-      <c r="K41" s="110"/>
-      <c r="L41" s="110"/>
-      <c r="M41" s="110"/>
-      <c r="N41" s="110"/>
-      <c r="O41" s="110"/>
-      <c r="P41" s="110"/>
-      <c r="Q41" s="110"/>
-      <c r="R41" s="110"/>
-      <c r="S41" s="110"/>
-      <c r="T41" s="110"/>
-      <c r="U41" s="110"/>
-      <c r="V41" s="110"/>
-      <c r="W41" s="110"/>
-      <c r="X41" s="110"/>
-      <c r="Y41" s="110"/>
-      <c r="Z41" s="110"/>
-      <c r="AA41" s="110"/>
-      <c r="AB41" s="110"/>
-      <c r="AC41" s="110"/>
-      <c r="AD41" s="110"/>
-      <c r="AE41" s="110"/>
-      <c r="AF41" s="110"/>
-    </row>
-    <row r="42" spans="1:32" s="109" customFormat="1" ht="14.1"/>
-    <row r="43" spans="1:32" s="109" customFormat="1" ht="14.1"/>
-    <row r="44" spans="1:32" s="109" customFormat="1" thickBot="1">
-      <c r="A44" s="117" t="s">
+    <row r="41" spans="1:32" s="107" customFormat="1" x14ac:dyDescent="0.7">
+      <c r="A41" s="108"/>
+      <c r="B41" s="108" t="s">
+        <v>406</v>
+      </c>
+      <c r="C41" s="108" t="s">
+        <v>408</v>
+      </c>
+      <c r="D41" s="108" t="s">
+        <v>425</v>
+      </c>
+      <c r="E41" s="108" t="s">
+        <v>410</v>
+      </c>
+      <c r="F41" s="108" t="s">
+        <v>426</v>
+      </c>
+      <c r="G41" s="108">
+        <v>9711396405</v>
+      </c>
+      <c r="H41" s="117" t="s">
+        <v>427</v>
+      </c>
+      <c r="I41" s="108" t="s">
+        <v>428</v>
+      </c>
+      <c r="J41" s="108" t="s">
+        <v>429</v>
+      </c>
+      <c r="K41" s="108" t="s">
+        <v>430</v>
+      </c>
+      <c r="L41" s="108" t="s">
+        <v>431</v>
+      </c>
+      <c r="M41" s="108" t="s">
+        <v>432</v>
+      </c>
+      <c r="N41" s="118">
+        <v>101194215929</v>
+      </c>
+      <c r="O41" s="108" t="s">
+        <v>433</v>
+      </c>
+      <c r="P41" s="108" t="s">
+        <v>434</v>
+      </c>
+      <c r="Q41" s="108"/>
+      <c r="R41" s="108" t="s">
+        <v>430</v>
+      </c>
+      <c r="S41" s="108" t="s">
+        <v>439</v>
+      </c>
+      <c r="T41" s="108" t="s">
+        <v>417</v>
+      </c>
+      <c r="U41" s="108" t="s">
+        <v>415</v>
+      </c>
+      <c r="V41" s="108" t="s">
+        <v>435</v>
+      </c>
+      <c r="W41" s="108" t="s">
+        <v>436</v>
+      </c>
+      <c r="X41" s="108"/>
+      <c r="Y41" s="108" t="s">
+        <v>437</v>
+      </c>
+      <c r="Z41" s="108">
+        <v>5914707229</v>
+      </c>
+      <c r="AA41" s="108" t="s">
+        <v>438</v>
+      </c>
+      <c r="AB41" s="108" t="s">
+        <v>406</v>
+      </c>
+      <c r="AC41" s="108" t="s">
+        <v>416</v>
+      </c>
+      <c r="AD41" s="108" t="s">
+        <v>406</v>
+      </c>
+      <c r="AE41" s="119">
+        <v>720812235123</v>
+      </c>
+      <c r="AF41" s="108" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="42" spans="1:32" s="107" customFormat="1" ht="14.25" x14ac:dyDescent="0.7"/>
+    <row r="43" spans="1:32" s="107" customFormat="1" ht="14.25" x14ac:dyDescent="0.7"/>
+    <row r="44" spans="1:32" s="107" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A44" s="120" t="s">
         <v>70</v>
       </c>
-      <c r="B44" s="118"/>
-    </row>
-    <row r="45" spans="1:32" s="109" customFormat="1" thickBot="1">
-      <c r="A45" s="119" t="s">
+      <c r="B44" s="121"/>
+    </row>
+    <row r="45" spans="1:32" s="107" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A45" s="122" t="s">
         <v>71</v>
       </c>
-      <c r="B45" s="120"/>
-      <c r="C45" s="120"/>
-      <c r="D45" s="120"/>
-      <c r="E45" s="120"/>
-      <c r="F45" s="120"/>
-      <c r="G45" s="120"/>
-      <c r="H45" s="120"/>
-      <c r="I45" s="120"/>
-      <c r="J45" s="120"/>
-      <c r="K45" s="120"/>
-      <c r="L45" s="120"/>
-      <c r="M45" s="120"/>
-      <c r="N45" s="120"/>
-      <c r="O45" s="120"/>
-      <c r="P45" s="121"/>
+      <c r="B45" s="123"/>
+      <c r="C45" s="123"/>
+      <c r="D45" s="123"/>
+      <c r="E45" s="123"/>
+      <c r="F45" s="123"/>
+      <c r="G45" s="123"/>
+      <c r="H45" s="123"/>
+      <c r="I45" s="123"/>
+      <c r="J45" s="123"/>
+      <c r="K45" s="123"/>
+      <c r="L45" s="123"/>
+      <c r="M45" s="123"/>
+      <c r="N45" s="123"/>
+      <c r="O45" s="123"/>
+      <c r="P45" s="124"/>
     </row>
   </sheetData>
   <mergeCells count="17">
@@ -4707,1779 +4966,1419 @@
       <formula1>"Male,Female"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="H41" r:id="rId1" xr:uid="{9F879F2B-DEB6-436E-B153-588CF0BF6125}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <sheetPr codeName="Sheet9"/>
-  <dimension ref="A6:H36"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
-  <cols>
-    <col min="3" max="3" width="10.7109375" customWidth="1"/>
-    <col min="4" max="4" width="12.140625" customWidth="1"/>
-    <col min="5" max="5" width="11.5703125" customWidth="1"/>
-    <col min="6" max="6" width="12.42578125" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" customWidth="1"/>
-    <col min="8" max="8" width="12.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="6" spans="1:8" ht="15">
-      <c r="A6" s="230" t="s">
-        <v>401</v>
-      </c>
-      <c r="B6" s="230"/>
-      <c r="C6" s="230"/>
-      <c r="D6" s="230"/>
-      <c r="E6" s="230"/>
-      <c r="F6" s="230"/>
-      <c r="G6" s="230"/>
-      <c r="H6" s="230"/>
-    </row>
-    <row r="8" spans="1:8" ht="199.5" customHeight="1">
-      <c r="A8" s="229" t="s">
-        <v>402</v>
-      </c>
-      <c r="B8" s="229"/>
-      <c r="C8" s="229"/>
-      <c r="D8" s="229"/>
-      <c r="E8" s="229"/>
-      <c r="F8" s="229"/>
-      <c r="G8" s="229"/>
-      <c r="H8" s="229"/>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" s="49"/>
-      <c r="B9" s="49"/>
-      <c r="C9" s="49"/>
-      <c r="D9" s="49"/>
-      <c r="E9" s="49"/>
-      <c r="F9" s="49"/>
-      <c r="G9" s="49"/>
-      <c r="H9" s="49"/>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" s="229" t="s">
-        <v>403</v>
-      </c>
-      <c r="B10" s="229"/>
-      <c r="C10" s="229" t="str">
-        <f>Data!B5</f>
-        <v/>
-      </c>
-      <c r="D10" s="229"/>
-      <c r="E10" s="229"/>
-      <c r="F10" s="229"/>
-      <c r="G10" s="229"/>
-      <c r="H10" s="229"/>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11" s="229" t="s">
-        <v>404</v>
-      </c>
-      <c r="B11" s="229"/>
-      <c r="C11" s="231"/>
-      <c r="D11" s="231"/>
-      <c r="E11" s="231"/>
-      <c r="F11" s="231"/>
-      <c r="G11" s="231"/>
-      <c r="H11" s="231"/>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="A12" s="229" t="s">
-        <v>405</v>
-      </c>
-      <c r="B12" s="229"/>
-      <c r="C12" s="231"/>
-      <c r="D12" s="231"/>
-      <c r="E12" s="231"/>
-      <c r="F12" s="231"/>
-      <c r="G12" s="231"/>
-      <c r="H12" s="231"/>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="A13" s="229" t="s">
-        <v>250</v>
-      </c>
-      <c r="B13" s="229"/>
-      <c r="C13" s="228" t="e">
-        <f>Data!FX5</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D13" s="229"/>
-      <c r="E13" s="229"/>
-      <c r="F13" s="229"/>
-      <c r="G13" s="229"/>
-      <c r="H13" s="229"/>
-    </row>
-    <row r="14" spans="1:8">
-      <c r="A14" s="49"/>
-      <c r="B14" s="49"/>
-      <c r="C14" s="49"/>
-      <c r="D14" s="49"/>
-      <c r="E14" s="49"/>
-      <c r="F14" s="49"/>
-      <c r="G14" s="49"/>
-      <c r="H14" s="49"/>
-    </row>
-    <row r="15" spans="1:8">
-      <c r="A15" s="49"/>
-      <c r="B15" s="49"/>
-      <c r="C15" s="49"/>
-      <c r="D15" s="49"/>
-      <c r="E15" s="49"/>
-      <c r="F15" s="49"/>
-      <c r="G15" s="49"/>
-      <c r="H15" s="49"/>
-    </row>
-    <row r="16" spans="1:8">
-      <c r="A16" s="49"/>
-      <c r="B16" s="49"/>
-      <c r="C16" s="49"/>
-      <c r="D16" s="49"/>
-      <c r="E16" s="49"/>
-      <c r="F16" s="49"/>
-      <c r="G16" s="49"/>
-      <c r="H16" s="49"/>
-    </row>
-    <row r="17" spans="1:8">
-      <c r="A17" s="49"/>
-      <c r="B17" s="49"/>
-      <c r="C17" s="49"/>
-      <c r="D17" s="49"/>
-      <c r="E17" s="49"/>
-      <c r="F17" s="49"/>
-      <c r="G17" s="49"/>
-      <c r="H17" s="49"/>
-    </row>
-    <row r="18" spans="1:8">
-      <c r="A18" s="49"/>
-      <c r="B18" s="49"/>
-      <c r="C18" s="49"/>
-      <c r="D18" s="49"/>
-      <c r="E18" s="49"/>
-      <c r="F18" s="49"/>
-      <c r="G18" s="49"/>
-      <c r="H18" s="49"/>
-    </row>
-    <row r="19" spans="1:8">
-      <c r="A19" s="49"/>
-      <c r="B19" s="49"/>
-      <c r="C19" s="49"/>
-      <c r="D19" s="49"/>
-      <c r="E19" s="49"/>
-      <c r="F19" s="49"/>
-      <c r="G19" s="49"/>
-      <c r="H19" s="49"/>
-    </row>
-    <row r="20" spans="1:8">
-      <c r="A20" s="49"/>
-      <c r="B20" s="49"/>
-      <c r="C20" s="49"/>
-      <c r="D20" s="49"/>
-      <c r="E20" s="49"/>
-      <c r="F20" s="49"/>
-      <c r="G20" s="49"/>
-      <c r="H20" s="49"/>
-    </row>
-    <row r="21" spans="1:8">
-      <c r="A21" s="49"/>
-      <c r="B21" s="49"/>
-      <c r="C21" s="49"/>
-      <c r="D21" s="49"/>
-      <c r="E21" s="49"/>
-      <c r="F21" s="49"/>
-      <c r="G21" s="49"/>
-      <c r="H21" s="49"/>
-    </row>
-    <row r="22" spans="1:8">
-      <c r="A22" s="49"/>
-      <c r="B22" s="49"/>
-      <c r="C22" s="49"/>
-      <c r="D22" s="49"/>
-      <c r="E22" s="49"/>
-      <c r="F22" s="49"/>
-      <c r="G22" s="49"/>
-      <c r="H22" s="49"/>
-    </row>
-    <row r="23" spans="1:8">
-      <c r="A23" s="49"/>
-      <c r="B23" s="49"/>
-      <c r="C23" s="49"/>
-      <c r="D23" s="49"/>
-      <c r="E23" s="49"/>
-      <c r="F23" s="49"/>
-      <c r="G23" s="49"/>
-      <c r="H23" s="49"/>
-    </row>
-    <row r="24" spans="1:8">
-      <c r="A24" s="49"/>
-      <c r="B24" s="49"/>
-      <c r="C24" s="49"/>
-      <c r="D24" s="49"/>
-      <c r="E24" s="49"/>
-      <c r="F24" s="49"/>
-      <c r="G24" s="49"/>
-      <c r="H24" s="49"/>
-    </row>
-    <row r="25" spans="1:8">
-      <c r="A25" s="49"/>
-      <c r="B25" s="49"/>
-      <c r="C25" s="49"/>
-      <c r="D25" s="49"/>
-      <c r="E25" s="49"/>
-      <c r="F25" s="49"/>
-      <c r="G25" s="49"/>
-      <c r="H25" s="49"/>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" s="49"/>
-      <c r="B26" s="49"/>
-      <c r="C26" s="49"/>
-      <c r="D26" s="49"/>
-      <c r="E26" s="49"/>
-      <c r="F26" s="49"/>
-      <c r="G26" s="49"/>
-      <c r="H26" s="49"/>
-    </row>
-    <row r="27" spans="1:8">
-      <c r="A27" s="49"/>
-      <c r="B27" s="49"/>
-      <c r="C27" s="49"/>
-      <c r="D27" s="49"/>
-      <c r="E27" s="49"/>
-      <c r="F27" s="49"/>
-      <c r="G27" s="49"/>
-      <c r="H27" s="49"/>
-    </row>
-    <row r="28" spans="1:8">
-      <c r="A28" s="49"/>
-      <c r="B28" s="49"/>
-      <c r="C28" s="49"/>
-      <c r="D28" s="49"/>
-      <c r="E28" s="49"/>
-      <c r="F28" s="49"/>
-      <c r="G28" s="49"/>
-      <c r="H28" s="49"/>
-    </row>
-    <row r="29" spans="1:8">
-      <c r="A29" s="49"/>
-      <c r="B29" s="49"/>
-      <c r="C29" s="49"/>
-      <c r="D29" s="49"/>
-      <c r="E29" s="49"/>
-      <c r="F29" s="49"/>
-      <c r="G29" s="49"/>
-      <c r="H29" s="49"/>
-    </row>
-    <row r="30" spans="1:8">
-      <c r="A30" s="49"/>
-      <c r="B30" s="49"/>
-      <c r="C30" s="49"/>
-      <c r="D30" s="49"/>
-      <c r="E30" s="49"/>
-      <c r="F30" s="49"/>
-      <c r="G30" s="49"/>
-      <c r="H30" s="49"/>
-    </row>
-    <row r="31" spans="1:8">
-      <c r="A31" s="49"/>
-      <c r="B31" s="49"/>
-      <c r="C31" s="49"/>
-      <c r="D31" s="49"/>
-      <c r="E31" s="49"/>
-      <c r="F31" s="49"/>
-      <c r="G31" s="49"/>
-      <c r="H31" s="49"/>
-    </row>
-    <row r="32" spans="1:8">
-      <c r="A32" s="49"/>
-      <c r="B32" s="49"/>
-      <c r="C32" s="49"/>
-      <c r="D32" s="49"/>
-      <c r="E32" s="49"/>
-      <c r="F32" s="49"/>
-      <c r="G32" s="49"/>
-      <c r="H32" s="49"/>
-    </row>
-    <row r="33" spans="1:8">
-      <c r="A33" s="49"/>
-      <c r="B33" s="49"/>
-      <c r="C33" s="49"/>
-      <c r="D33" s="49"/>
-      <c r="E33" s="49"/>
-      <c r="F33" s="49"/>
-      <c r="G33" s="49"/>
-      <c r="H33" s="49"/>
-    </row>
-    <row r="34" spans="1:8">
-      <c r="A34" s="49"/>
-      <c r="B34" s="49"/>
-      <c r="C34" s="49"/>
-      <c r="D34" s="49"/>
-      <c r="E34" s="49"/>
-      <c r="F34" s="49"/>
-      <c r="G34" s="49"/>
-      <c r="H34" s="49"/>
-    </row>
-    <row r="35" spans="1:8">
-      <c r="A35" s="49"/>
-      <c r="B35" s="49"/>
-      <c r="C35" s="49"/>
-      <c r="D35" s="49"/>
-      <c r="E35" s="49"/>
-      <c r="F35" s="49"/>
-      <c r="G35" s="49"/>
-      <c r="H35" s="49"/>
-    </row>
-    <row r="36" spans="1:8">
-      <c r="A36" s="49"/>
-      <c r="B36" s="49"/>
-      <c r="C36" s="49"/>
-      <c r="D36" s="49"/>
-      <c r="E36" s="49"/>
-      <c r="F36" s="49"/>
-      <c r="G36" s="49"/>
-      <c r="H36" s="49"/>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="C13:H13"/>
-    <mergeCell ref="A6:H6"/>
-    <mergeCell ref="A8:H8"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="C10:H10"/>
-    <mergeCell ref="C11:H11"/>
-    <mergeCell ref="C12:H12"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" copies="0" r:id="rId1"/>
-  <drawing r:id="rId2"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F52E9576-270B-4680-8425-E53A2E0AE167}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
-  <cols>
-    <col min="1" max="1" width="50.42578125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="73" t="s">
-        <v>37</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:GH5"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="25.5" x14ac:dyDescent="0.7"/>
   <cols>
-    <col min="1" max="1" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="12.85546875" customWidth="1"/>
-    <col min="7" max="7" width="17.5703125" customWidth="1"/>
-    <col min="8" max="8" width="9.7109375" customWidth="1"/>
-    <col min="9" max="9" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.5703125" customWidth="1"/>
-    <col min="11" max="11" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="12.88671875" customWidth="1"/>
+    <col min="7" max="7" width="17.5546875" customWidth="1"/>
+    <col min="8" max="8" width="9.6640625" customWidth="1"/>
+    <col min="9" max="9" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.5546875" customWidth="1"/>
+    <col min="11" max="11" width="4.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.5546875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="8" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="16" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="5.5703125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="9.7109375" customWidth="1"/>
-    <col min="21" max="21" width="13.140625" customWidth="1"/>
-    <col min="22" max="22" width="9.28515625" customWidth="1"/>
-    <col min="23" max="25" width="9.85546875" customWidth="1"/>
-    <col min="26" max="26" width="9.140625" customWidth="1"/>
+    <col min="14" max="14" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.6640625" customWidth="1"/>
+    <col min="16" max="16" width="4.88671875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.6640625" customWidth="1"/>
+    <col min="21" max="21" width="13.109375" customWidth="1"/>
+    <col min="22" max="22" width="9.33203125" customWidth="1"/>
+    <col min="23" max="25" width="9.88671875" customWidth="1"/>
+    <col min="26" max="26" width="9.109375" customWidth="1"/>
     <col min="27" max="27" width="12" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="10.85546875" customWidth="1"/>
-    <col min="29" max="55" width="13.28515625" customWidth="1"/>
-    <col min="116" max="117" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="119" max="119" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="123" max="124" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="126" max="126" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="130" max="131" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="133" max="133" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="134" max="135" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="136" max="136" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="137" max="137" width="15.140625" customWidth="1"/>
-    <col min="138" max="138" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="139" max="139" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="140" max="140" width="18.7109375" customWidth="1"/>
-    <col min="141" max="141" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="142" max="142" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="143" max="143" width="25.7109375" bestFit="1" customWidth="1"/>
-    <col min="144" max="144" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="145" max="145" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="155" max="155" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="10.88671875" customWidth="1"/>
+    <col min="29" max="55" width="13.33203125" customWidth="1"/>
+    <col min="116" max="117" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="119" max="119" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="123" max="124" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="126" max="126" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="130" max="131" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="133" max="133" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="134" max="135" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="136" max="136" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="137" max="137" width="15.109375" customWidth="1"/>
+    <col min="138" max="138" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="139" max="139" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="140" max="140" width="18.6640625" customWidth="1"/>
+    <col min="141" max="141" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="142" max="142" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="143" max="143" width="25.6640625" bestFit="1" customWidth="1"/>
+    <col min="144" max="144" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="145" max="145" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="155" max="155" width="10.6640625" bestFit="1" customWidth="1"/>
     <col min="158" max="158" width="12" bestFit="1" customWidth="1"/>
-    <col min="177" max="177" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="180" max="180" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="177" max="177" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="180" max="180" width="10.6640625" bestFit="1" customWidth="1"/>
     <col min="185" max="185" width="10" bestFit="1" customWidth="1"/>
     <col min="187" max="187" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:190" ht="15.6">
+    <row r="1" spans="1:190" ht="26.25" x14ac:dyDescent="0.7">
       <c r="D1" s="3"/>
       <c r="E1" s="4"/>
       <c r="F1" s="3"/>
       <c r="G1" s="4"/>
     </row>
-    <row r="2" spans="1:190" ht="15.6">
+    <row r="2" spans="1:190" ht="26.25" x14ac:dyDescent="0.7">
       <c r="D2" s="3"/>
       <c r="E2" s="4"/>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
     </row>
-    <row r="3" spans="1:190" ht="15" thickBot="1"/>
-    <row r="4" spans="1:190" s="77" customFormat="1" ht="120" customHeight="1" thickBot="1">
-      <c r="A4" s="80" t="s">
+    <row r="3" spans="1:190" ht="26.25" thickBot="1" x14ac:dyDescent="0.75"/>
+    <row r="4" spans="1:190" s="75" customFormat="1" ht="120" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A4" s="78" t="s">
         <v>72</v>
       </c>
-      <c r="B4" s="79" t="s">
+      <c r="B4" s="77" t="s">
         <v>73</v>
       </c>
-      <c r="C4" s="79" t="s">
+      <c r="C4" s="77" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="79" t="s">
+      <c r="D4" s="77" t="s">
         <v>74</v>
       </c>
-      <c r="E4" s="79" t="s">
+      <c r="E4" s="77" t="s">
         <v>75</v>
       </c>
-      <c r="F4" s="79" t="s">
+      <c r="F4" s="77" t="s">
         <v>76</v>
       </c>
-      <c r="G4" s="79" t="s">
+      <c r="G4" s="77" t="s">
         <v>77</v>
       </c>
-      <c r="H4" s="79" t="s">
+      <c r="H4" s="77" t="s">
         <v>78</v>
       </c>
-      <c r="I4" s="79" t="s">
+      <c r="I4" s="77" t="s">
         <v>79</v>
       </c>
-      <c r="J4" s="79" t="s">
+      <c r="J4" s="77" t="s">
         <v>80</v>
       </c>
-      <c r="K4" s="79" t="s">
+      <c r="K4" s="77" t="s">
         <v>81</v>
       </c>
-      <c r="L4" s="79" t="s">
+      <c r="L4" s="77" t="s">
         <v>82</v>
       </c>
-      <c r="M4" s="79" t="s">
+      <c r="M4" s="77" t="s">
         <v>83</v>
       </c>
-      <c r="N4" s="79" t="s">
+      <c r="N4" s="77" t="s">
         <v>84</v>
       </c>
-      <c r="O4" s="79" t="s">
+      <c r="O4" s="77" t="s">
         <v>85</v>
       </c>
-      <c r="P4" s="79" t="s">
+      <c r="P4" s="77" t="s">
         <v>81</v>
       </c>
-      <c r="Q4" s="79" t="s">
+      <c r="Q4" s="77" t="s">
         <v>82</v>
       </c>
-      <c r="R4" s="79" t="s">
+      <c r="R4" s="77" t="s">
         <v>83</v>
       </c>
-      <c r="S4" s="79" t="s">
+      <c r="S4" s="77" t="s">
         <v>84</v>
       </c>
-      <c r="T4" s="79" t="s">
+      <c r="T4" s="77" t="s">
         <v>86</v>
       </c>
-      <c r="U4" s="79" t="s">
+      <c r="U4" s="77" t="s">
         <v>87</v>
       </c>
-      <c r="V4" s="79" t="s">
+      <c r="V4" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="W4" s="79" t="s">
+      <c r="W4" s="77" t="s">
         <v>89</v>
       </c>
-      <c r="X4" s="79" t="s">
+      <c r="X4" s="77" t="s">
         <v>90</v>
       </c>
-      <c r="Y4" s="79" t="s">
+      <c r="Y4" s="77" t="s">
         <v>91</v>
       </c>
-      <c r="Z4" s="78" t="s">
+      <c r="Z4" s="76" t="s">
         <v>92</v>
       </c>
-      <c r="AA4" s="78" t="s">
+      <c r="AA4" s="76" t="s">
         <v>93</v>
       </c>
-      <c r="AB4" s="79" t="s">
+      <c r="AB4" s="77" t="s">
         <v>94</v>
       </c>
-      <c r="AC4" s="79" t="s">
+      <c r="AC4" s="77" t="s">
         <v>95</v>
       </c>
-      <c r="AD4" s="79" t="s">
+      <c r="AD4" s="77" t="s">
         <v>96</v>
       </c>
-      <c r="AE4" s="79" t="s">
+      <c r="AE4" s="77" t="s">
         <v>97</v>
       </c>
-      <c r="AF4" s="79" t="s">
+      <c r="AF4" s="77" t="s">
         <v>98</v>
       </c>
-      <c r="AG4" s="79" t="s">
+      <c r="AG4" s="77" t="s">
         <v>99</v>
       </c>
-      <c r="AH4" s="79" t="s">
+      <c r="AH4" s="77" t="s">
         <v>100</v>
       </c>
-      <c r="AI4" s="79" t="s">
+      <c r="AI4" s="77" t="s">
         <v>101</v>
       </c>
-      <c r="AJ4" s="79" t="s">
+      <c r="AJ4" s="77" t="s">
         <v>102</v>
       </c>
-      <c r="AK4" s="79" t="s">
+      <c r="AK4" s="77" t="s">
         <v>103</v>
       </c>
-      <c r="AL4" s="79" t="s">
+      <c r="AL4" s="77" t="s">
         <v>104</v>
       </c>
-      <c r="AM4" s="79" t="s">
+      <c r="AM4" s="77" t="s">
         <v>105</v>
       </c>
-      <c r="AN4" s="79" t="s">
+      <c r="AN4" s="77" t="s">
         <v>106</v>
       </c>
-      <c r="AO4" s="79" t="s">
+      <c r="AO4" s="77" t="s">
         <v>107</v>
       </c>
-      <c r="AP4" s="79" t="s">
+      <c r="AP4" s="77" t="s">
         <v>108</v>
       </c>
-      <c r="AQ4" s="79" t="s">
+      <c r="AQ4" s="77" t="s">
         <v>109</v>
       </c>
-      <c r="AR4" s="79" t="s">
+      <c r="AR4" s="77" t="s">
         <v>110</v>
       </c>
-      <c r="AS4" s="79" t="s">
+      <c r="AS4" s="77" t="s">
         <v>111</v>
       </c>
-      <c r="AT4" s="79" t="s">
+      <c r="AT4" s="77" t="s">
         <v>112</v>
       </c>
-      <c r="AU4" s="79" t="s">
+      <c r="AU4" s="77" t="s">
         <v>113</v>
       </c>
-      <c r="AV4" s="79" t="s">
+      <c r="AV4" s="77" t="s">
         <v>114</v>
       </c>
-      <c r="AW4" s="79" t="s">
+      <c r="AW4" s="77" t="s">
         <v>115</v>
       </c>
-      <c r="AX4" s="79" t="s">
+      <c r="AX4" s="77" t="s">
         <v>116</v>
       </c>
-      <c r="AY4" s="79" t="s">
+      <c r="AY4" s="77" t="s">
         <v>117</v>
       </c>
-      <c r="AZ4" s="79" t="s">
+      <c r="AZ4" s="77" t="s">
         <v>118</v>
       </c>
-      <c r="BA4" s="78" t="s">
+      <c r="BA4" s="76" t="s">
         <v>119</v>
       </c>
-      <c r="BB4" s="78" t="s">
+      <c r="BB4" s="76" t="s">
         <v>120</v>
       </c>
-      <c r="BC4" s="78" t="s">
+      <c r="BC4" s="76" t="s">
         <v>121</v>
       </c>
-      <c r="BD4" s="78" t="s">
+      <c r="BD4" s="76" t="s">
         <v>122</v>
       </c>
-      <c r="BE4" s="78" t="s">
+      <c r="BE4" s="76" t="s">
         <v>123</v>
       </c>
-      <c r="BF4" s="78" t="s">
+      <c r="BF4" s="76" t="s">
         <v>124</v>
       </c>
-      <c r="BG4" s="78" t="s">
+      <c r="BG4" s="76" t="s">
         <v>125</v>
       </c>
-      <c r="BH4" s="78" t="s">
+      <c r="BH4" s="76" t="s">
         <v>126</v>
       </c>
-      <c r="BI4" s="78" t="s">
+      <c r="BI4" s="76" t="s">
         <v>127</v>
       </c>
-      <c r="BJ4" s="78" t="s">
+      <c r="BJ4" s="76" t="s">
         <v>128</v>
       </c>
-      <c r="BK4" s="78" t="s">
+      <c r="BK4" s="76" t="s">
         <v>129</v>
       </c>
-      <c r="BL4" s="78" t="s">
+      <c r="BL4" s="76" t="s">
         <v>130</v>
       </c>
-      <c r="BM4" s="78" t="s">
+      <c r="BM4" s="76" t="s">
         <v>131</v>
       </c>
-      <c r="BN4" s="78" t="s">
+      <c r="BN4" s="76" t="s">
         <v>132</v>
       </c>
-      <c r="BO4" s="78" t="s">
+      <c r="BO4" s="76" t="s">
         <v>133</v>
       </c>
-      <c r="BP4" s="78" t="s">
+      <c r="BP4" s="76" t="s">
         <v>134</v>
       </c>
-      <c r="BQ4" s="78" t="s">
+      <c r="BQ4" s="76" t="s">
         <v>135</v>
       </c>
-      <c r="BR4" s="78" t="s">
+      <c r="BR4" s="76" t="s">
         <v>136</v>
       </c>
-      <c r="BS4" s="78" t="s">
+      <c r="BS4" s="76" t="s">
         <v>137</v>
       </c>
-      <c r="BT4" s="78" t="s">
+      <c r="BT4" s="76" t="s">
         <v>138</v>
       </c>
-      <c r="BU4" s="78" t="s">
+      <c r="BU4" s="76" t="s">
         <v>139</v>
       </c>
-      <c r="BV4" s="78" t="s">
+      <c r="BV4" s="76" t="s">
         <v>140</v>
       </c>
-      <c r="BW4" s="78" t="s">
+      <c r="BW4" s="76" t="s">
         <v>141</v>
       </c>
-      <c r="BX4" s="78" t="s">
+      <c r="BX4" s="76" t="s">
         <v>142</v>
       </c>
-      <c r="BY4" s="78" t="s">
+      <c r="BY4" s="76" t="s">
         <v>143</v>
       </c>
-      <c r="BZ4" s="78" t="s">
+      <c r="BZ4" s="76" t="s">
         <v>144</v>
       </c>
-      <c r="CA4" s="78" t="s">
+      <c r="CA4" s="76" t="s">
         <v>145</v>
       </c>
-      <c r="CB4" s="78" t="s">
+      <c r="CB4" s="76" t="s">
         <v>146</v>
       </c>
-      <c r="CC4" s="78" t="s">
+      <c r="CC4" s="76" t="s">
         <v>147</v>
       </c>
-      <c r="CD4" s="78" t="s">
+      <c r="CD4" s="76" t="s">
         <v>148</v>
       </c>
-      <c r="CE4" s="79" t="s">
+      <c r="CE4" s="77" t="s">
         <v>149</v>
       </c>
-      <c r="CF4" s="79" t="s">
+      <c r="CF4" s="77" t="s">
         <v>150</v>
       </c>
-      <c r="CG4" s="79" t="s">
+      <c r="CG4" s="77" t="s">
         <v>151</v>
       </c>
-      <c r="CH4" s="79" t="s">
+      <c r="CH4" s="77" t="s">
         <v>152</v>
       </c>
-      <c r="CI4" s="79" t="s">
+      <c r="CI4" s="77" t="s">
         <v>153</v>
       </c>
-      <c r="CJ4" s="79" t="s">
+      <c r="CJ4" s="77" t="s">
         <v>154</v>
       </c>
-      <c r="CK4" s="79" t="s">
+      <c r="CK4" s="77" t="s">
         <v>155</v>
       </c>
-      <c r="CL4" s="79" t="s">
+      <c r="CL4" s="77" t="s">
         <v>156</v>
       </c>
-      <c r="CM4" s="79" t="s">
+      <c r="CM4" s="77" t="s">
         <v>157</v>
       </c>
-      <c r="CN4" s="79" t="s">
+      <c r="CN4" s="77" t="s">
         <v>158</v>
       </c>
-      <c r="CO4" s="79" t="s">
+      <c r="CO4" s="77" t="s">
         <v>159</v>
       </c>
-      <c r="CP4" s="79" t="s">
+      <c r="CP4" s="77" t="s">
         <v>160</v>
       </c>
-      <c r="CQ4" s="79" t="s">
+      <c r="CQ4" s="77" t="s">
         <v>161</v>
       </c>
-      <c r="CR4" s="79" t="s">
+      <c r="CR4" s="77" t="s">
         <v>162</v>
       </c>
-      <c r="CS4" s="79" t="s">
+      <c r="CS4" s="77" t="s">
         <v>163</v>
       </c>
-      <c r="CT4" s="79" t="s">
+      <c r="CT4" s="77" t="s">
         <v>164</v>
       </c>
-      <c r="CU4" s="79" t="s">
+      <c r="CU4" s="77" t="s">
         <v>165</v>
       </c>
-      <c r="CV4" s="79" t="s">
+      <c r="CV4" s="77" t="s">
         <v>166</v>
       </c>
-      <c r="CW4" s="79" t="s">
+      <c r="CW4" s="77" t="s">
         <v>167</v>
       </c>
-      <c r="CX4" s="79" t="s">
+      <c r="CX4" s="77" t="s">
         <v>168</v>
       </c>
-      <c r="CY4" s="79" t="s">
+      <c r="CY4" s="77" t="s">
         <v>169</v>
       </c>
-      <c r="CZ4" s="79" t="s">
+      <c r="CZ4" s="77" t="s">
         <v>170</v>
       </c>
-      <c r="DA4" s="79" t="s">
+      <c r="DA4" s="77" t="s">
         <v>171</v>
       </c>
-      <c r="DB4" s="79" t="s">
+      <c r="DB4" s="77" t="s">
         <v>172</v>
       </c>
-      <c r="DC4" s="79" t="s">
+      <c r="DC4" s="77" t="s">
         <v>173</v>
       </c>
-      <c r="DD4" s="79" t="s">
+      <c r="DD4" s="77" t="s">
         <v>174</v>
       </c>
-      <c r="DE4" s="79" t="s">
+      <c r="DE4" s="77" t="s">
         <v>175</v>
       </c>
-      <c r="DF4" s="79" t="s">
+      <c r="DF4" s="77" t="s">
         <v>176</v>
       </c>
-      <c r="DG4" s="79" t="s">
+      <c r="DG4" s="77" t="s">
         <v>177</v>
       </c>
-      <c r="DH4" s="79" t="s">
+      <c r="DH4" s="77" t="s">
         <v>178</v>
       </c>
-      <c r="DI4" s="78" t="s">
+      <c r="DI4" s="76" t="s">
         <v>179</v>
       </c>
-      <c r="DJ4" s="78" t="s">
+      <c r="DJ4" s="76" t="s">
         <v>180</v>
       </c>
-      <c r="DK4" s="78" t="s">
+      <c r="DK4" s="76" t="s">
         <v>181</v>
       </c>
-      <c r="DL4" s="78" t="s">
+      <c r="DL4" s="76" t="s">
         <v>182</v>
       </c>
-      <c r="DM4" s="78" t="s">
+      <c r="DM4" s="76" t="s">
         <v>183</v>
       </c>
-      <c r="DN4" s="78" t="s">
+      <c r="DN4" s="76" t="s">
         <v>184</v>
       </c>
-      <c r="DO4" s="78" t="s">
+      <c r="DO4" s="76" t="s">
         <v>185</v>
       </c>
-      <c r="DP4" s="78" t="s">
+      <c r="DP4" s="76" t="s">
         <v>186</v>
       </c>
-      <c r="DQ4" s="78" t="s">
+      <c r="DQ4" s="76" t="s">
         <v>187</v>
       </c>
-      <c r="DR4" s="78" t="s">
+      <c r="DR4" s="76" t="s">
         <v>188</v>
       </c>
-      <c r="DS4" s="78" t="s">
+      <c r="DS4" s="76" t="s">
         <v>189</v>
       </c>
-      <c r="DT4" s="78" t="s">
+      <c r="DT4" s="76" t="s">
         <v>190</v>
       </c>
-      <c r="DU4" s="78" t="s">
+      <c r="DU4" s="76" t="s">
         <v>191</v>
       </c>
-      <c r="DV4" s="78" t="s">
+      <c r="DV4" s="76" t="s">
         <v>192</v>
       </c>
-      <c r="DW4" s="78" t="s">
+      <c r="DW4" s="76" t="s">
         <v>193</v>
       </c>
-      <c r="DX4" s="78" t="s">
+      <c r="DX4" s="76" t="s">
         <v>194</v>
       </c>
-      <c r="DY4" s="78" t="s">
+      <c r="DY4" s="76" t="s">
         <v>195</v>
       </c>
-      <c r="DZ4" s="78" t="s">
+      <c r="DZ4" s="76" t="s">
         <v>196</v>
       </c>
-      <c r="EA4" s="78" t="s">
+      <c r="EA4" s="76" t="s">
         <v>197</v>
       </c>
-      <c r="EB4" s="78" t="s">
+      <c r="EB4" s="76" t="s">
         <v>198</v>
       </c>
-      <c r="EC4" s="78" t="s">
+      <c r="EC4" s="76" t="s">
         <v>199</v>
       </c>
-      <c r="ED4" s="79" t="s">
+      <c r="ED4" s="77" t="s">
         <v>200</v>
       </c>
-      <c r="EE4" s="79" t="s">
+      <c r="EE4" s="77" t="s">
         <v>201</v>
       </c>
-      <c r="EF4" s="79" t="s">
+      <c r="EF4" s="77" t="s">
         <v>202</v>
       </c>
-      <c r="EG4" s="79" t="s">
+      <c r="EG4" s="77" t="s">
         <v>203</v>
       </c>
-      <c r="EH4" s="79" t="s">
+      <c r="EH4" s="77" t="s">
         <v>204</v>
       </c>
-      <c r="EI4" s="79" t="s">
+      <c r="EI4" s="77" t="s">
         <v>205</v>
       </c>
-      <c r="EJ4" s="79" t="s">
+      <c r="EJ4" s="77" t="s">
         <v>206</v>
       </c>
-      <c r="EK4" s="79" t="s">
+      <c r="EK4" s="77" t="s">
         <v>207</v>
       </c>
-      <c r="EL4" s="79" t="s">
+      <c r="EL4" s="77" t="s">
         <v>208</v>
       </c>
-      <c r="EM4" s="79" t="s">
+      <c r="EM4" s="77" t="s">
         <v>209</v>
       </c>
-      <c r="EN4" s="79" t="s">
+      <c r="EN4" s="77" t="s">
         <v>210</v>
       </c>
-      <c r="EO4" s="79" t="s">
+      <c r="EO4" s="77" t="s">
         <v>211</v>
       </c>
-      <c r="EP4" s="79" t="s">
+      <c r="EP4" s="77" t="s">
         <v>212</v>
       </c>
-      <c r="EQ4" s="79" t="s">
+      <c r="EQ4" s="77" t="s">
         <v>213</v>
       </c>
-      <c r="ER4" s="79" t="s">
+      <c r="ER4" s="77" t="s">
         <v>214</v>
       </c>
-      <c r="ES4" s="78" t="s">
+      <c r="ES4" s="76" t="s">
         <v>215</v>
       </c>
-      <c r="ET4" s="78" t="s">
+      <c r="ET4" s="76" t="s">
         <v>216</v>
       </c>
-      <c r="EU4" s="78" t="s">
+      <c r="EU4" s="76" t="s">
         <v>217</v>
       </c>
-      <c r="EV4" s="78" t="s">
+      <c r="EV4" s="76" t="s">
         <v>28</v>
       </c>
-      <c r="EW4" s="78" t="s">
+      <c r="EW4" s="76" t="s">
         <v>218</v>
       </c>
-      <c r="EX4" s="78" t="s">
+      <c r="EX4" s="76" t="s">
         <v>219</v>
       </c>
-      <c r="EY4" s="78" t="s">
+      <c r="EY4" s="76" t="s">
         <v>74</v>
       </c>
-      <c r="EZ4" s="78" t="s">
+      <c r="EZ4" s="76" t="s">
         <v>220</v>
       </c>
-      <c r="FA4" s="78" t="s">
+      <c r="FA4" s="76" t="s">
         <v>221</v>
       </c>
-      <c r="FB4" s="78" t="s">
+      <c r="FB4" s="76" t="s">
         <v>222</v>
       </c>
-      <c r="FC4" s="78" t="s">
+      <c r="FC4" s="76" t="s">
         <v>223</v>
       </c>
-      <c r="FD4" s="78" t="s">
+      <c r="FD4" s="76" t="s">
         <v>224</v>
       </c>
-      <c r="FE4" s="78" t="s">
+      <c r="FE4" s="76" t="s">
         <v>225</v>
       </c>
-      <c r="FF4" s="78" t="s">
+      <c r="FF4" s="76" t="s">
         <v>226</v>
       </c>
-      <c r="FG4" s="78" t="s">
+      <c r="FG4" s="76" t="s">
         <v>227</v>
       </c>
-      <c r="FH4" s="78" t="s">
+      <c r="FH4" s="76" t="s">
         <v>228</v>
       </c>
-      <c r="FI4" s="78" t="s">
+      <c r="FI4" s="76" t="s">
         <v>229</v>
       </c>
-      <c r="FJ4" s="78" t="s">
+      <c r="FJ4" s="76" t="s">
         <v>230</v>
       </c>
-      <c r="FK4" s="78" t="s">
+      <c r="FK4" s="76" t="s">
         <v>231</v>
       </c>
-      <c r="FL4" s="78" t="s">
+      <c r="FL4" s="76" t="s">
         <v>232</v>
       </c>
-      <c r="FM4" s="78" t="s">
+      <c r="FM4" s="76" t="s">
         <v>233</v>
       </c>
-      <c r="FN4" s="78" t="s">
+      <c r="FN4" s="76" t="s">
         <v>234</v>
       </c>
-      <c r="FO4" s="78" t="s">
+      <c r="FO4" s="76" t="s">
         <v>235</v>
       </c>
-      <c r="FP4" s="78" t="s">
+      <c r="FP4" s="76" t="s">
         <v>236</v>
       </c>
-      <c r="FQ4" s="78" t="s">
+      <c r="FQ4" s="76" t="s">
         <v>237</v>
       </c>
-      <c r="FR4" s="78" t="s">
+      <c r="FR4" s="76" t="s">
         <v>238</v>
       </c>
-      <c r="FS4" s="79" t="s">
+      <c r="FS4" s="77" t="s">
         <v>38</v>
       </c>
-      <c r="FT4" s="79" t="s">
+      <c r="FT4" s="77" t="s">
         <v>239</v>
       </c>
-      <c r="FU4" s="79" t="s">
+      <c r="FU4" s="77" t="s">
         <v>42</v>
       </c>
-      <c r="FV4" s="79" t="s">
+      <c r="FV4" s="77" t="s">
         <v>240</v>
       </c>
-      <c r="FW4" s="79" t="s">
+      <c r="FW4" s="77" t="s">
         <v>241</v>
       </c>
-      <c r="FX4" s="79" t="s">
+      <c r="FX4" s="77" t="s">
         <v>49</v>
       </c>
-      <c r="FY4" s="79" t="s">
+      <c r="FY4" s="77" t="s">
         <v>28</v>
       </c>
-      <c r="FZ4" s="79" t="s">
+      <c r="FZ4" s="77" t="s">
         <v>242</v>
       </c>
-      <c r="GA4" s="79" t="s">
+      <c r="GA4" s="77" t="s">
         <v>243</v>
       </c>
-      <c r="GB4" s="79" t="s">
+      <c r="GB4" s="77" t="s">
         <v>244</v>
       </c>
-      <c r="GC4" s="79" t="s">
+      <c r="GC4" s="77" t="s">
         <v>44</v>
       </c>
-      <c r="GD4" s="79" t="s">
+      <c r="GD4" s="77" t="s">
         <v>245</v>
       </c>
-      <c r="GE4" s="79" t="s">
+      <c r="GE4" s="77" t="s">
         <v>63</v>
       </c>
-      <c r="GF4" s="79" t="s">
+      <c r="GF4" s="77" t="s">
         <v>246</v>
       </c>
-      <c r="GG4" s="79" t="s">
+      <c r="GG4" s="77" t="s">
         <v>247</v>
       </c>
-      <c r="GH4" s="81" t="s">
+      <c r="GH4" s="79" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="5" spans="1:190" s="77" customFormat="1" ht="103.5" customHeight="1" thickBot="1">
-      <c r="A5" s="75" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="B5" s="76" t="str">
+    <row r="5" spans="1:190" s="75" customFormat="1" ht="103.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A5" s="73" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="B5" s="74" t="str">
         <f>IF('New Joiner Form'!C5=0,"",'New Joiner Form'!C5)</f>
-        <v/>
-      </c>
-      <c r="C5" s="76" t="str">
+        <v>Pushkar Singh</v>
+      </c>
+      <c r="C5" s="74" t="str">
         <f>IF('New Joiner Form'!C6=0,"",'New Joiner Form'!C6)</f>
-        <v/>
-      </c>
-      <c r="D5" s="89" t="str">
+        <v>Male</v>
+      </c>
+      <c r="D5" s="87" t="str">
         <f>IF('New Joiner Form'!C9=0,"",'New Joiner Form'!C9)</f>
-        <v/>
-      </c>
-      <c r="E5" s="76" t="str">
+        <v>23/04/1994</v>
+      </c>
+      <c r="E5" s="74" t="str">
         <f>IF('New Joiner Form'!C10=0,"",'New Joiner Form'!C10)</f>
-        <v/>
-      </c>
-      <c r="F5" s="76" t="str">
+        <v>A+</v>
+      </c>
+      <c r="F5" s="74" t="str">
         <f>IF('New Joiner Form'!C12=0,"",'New Joiner Form'!C12)</f>
         <v/>
       </c>
-      <c r="G5" s="76" t="str">
+      <c r="G5" s="74">
         <f>IF('New Joiner Form'!G10=0,"",'New Joiner Form'!G10)</f>
-        <v/>
-      </c>
-      <c r="H5" s="76" t="str">
+        <v>720812235123</v>
+      </c>
+      <c r="H5" s="74" t="str">
         <f>IF('New Joiner Form'!G11=0,"",'New Joiner Form'!G11)</f>
-        <v/>
-      </c>
-      <c r="I5" s="76" t="str">
+        <v>JABPS9654C</v>
+      </c>
+      <c r="I5" s="74" t="str">
         <f>IF('New Joiner Form'!C11=0,"",'New Joiner Form'!C11)</f>
-        <v/>
-      </c>
-      <c r="J5" s="76" t="str">
+        <v>Hindu</v>
+      </c>
+      <c r="J5" s="74" t="str">
         <f>IF('New Joiner Form'!E5=0,"",'New Joiner Form'!E5)</f>
-        <v/>
-      </c>
-      <c r="K5" s="76" t="str">
+        <v>159-160,1st floor, Pocket-7, Sector-24 Rohini</v>
+      </c>
+      <c r="K5" s="74" t="str">
         <f>IF('New Joiner Form'!E6=0,"",'New Joiner Form'!E6)</f>
-        <v/>
-      </c>
-      <c r="L5" s="76" t="str">
+        <v>Delhi</v>
+      </c>
+      <c r="L5" s="74" t="str">
         <f>IF('New Joiner Form'!E7=0,"",'New Joiner Form'!E7)</f>
-        <v/>
-      </c>
-      <c r="M5" s="76" t="str">
+        <v>Delhi</v>
+      </c>
+      <c r="M5" s="74" t="str">
         <f>IF('New Joiner Form'!E8=0,"",'New Joiner Form'!E8)</f>
-        <v/>
-      </c>
-      <c r="N5" s="76" t="str">
+        <v>India</v>
+      </c>
+      <c r="N5" s="74">
         <f>IF('New Joiner Form'!E9=0,"",'New Joiner Form'!E9)</f>
-        <v/>
-      </c>
-      <c r="O5" s="76" t="str">
+        <v>110085</v>
+      </c>
+      <c r="O5" s="74" t="str">
         <f>IF('New Joiner Form'!G5=0,"",'New Joiner Form'!G5)</f>
-        <v/>
-      </c>
-      <c r="P5" s="76" t="str">
+        <v>159-160,1st floor, Pocket-7, Sector-24 Rohini</v>
+      </c>
+      <c r="P5" s="74" t="str">
         <f>IF('New Joiner Form'!G6=0,"",'New Joiner Form'!G6)</f>
-        <v/>
-      </c>
-      <c r="Q5" s="76" t="str">
+        <v>Delhi</v>
+      </c>
+      <c r="Q5" s="74" t="str">
         <f>IF('New Joiner Form'!G7=0,"",'New Joiner Form'!G7)</f>
-        <v/>
-      </c>
-      <c r="R5" s="76" t="str">
+        <v>Delhi</v>
+      </c>
+      <c r="R5" s="74" t="str">
         <f>IF('New Joiner Form'!G8=0,"",'New Joiner Form'!G8)</f>
-        <v/>
-      </c>
-      <c r="S5" s="76" t="str">
+        <v>India</v>
+      </c>
+      <c r="S5" s="74">
         <f>IF('New Joiner Form'!G9=0,"",'New Joiner Form'!G9)</f>
-        <v/>
-      </c>
-      <c r="T5" s="76" t="str">
+        <v>110085</v>
+      </c>
+      <c r="T5" s="74">
         <f>IF('New Joiner Form'!E10=0,"",'New Joiner Form'!E10)</f>
-        <v/>
-      </c>
-      <c r="U5" s="76" t="str">
+        <v>9313569413</v>
+      </c>
+      <c r="U5" s="74" t="str">
         <f>IF('New Joiner Form'!E11=0,"",'New Joiner Form'!E11)</f>
         <v/>
       </c>
-      <c r="V5" s="76" t="str">
+      <c r="V5" s="74" t="str">
         <f>IF('New Joiner Form'!C7=0,"",'New Joiner Form'!C7)</f>
-        <v/>
-      </c>
-      <c r="W5" s="76" t="str">
+        <v>Satender Kumar</v>
+      </c>
+      <c r="W5" s="74" t="str">
         <f>IF('New Joiner Form'!C8=0,"",'New Joiner Form'!C8)</f>
-        <v/>
-      </c>
-      <c r="X5" s="76" t="str">
+        <v>Suman</v>
+      </c>
+      <c r="X5" s="74">
         <f>IF('New Joiner Form'!E12=0,"",'New Joiner Form'!E12)</f>
-        <v/>
-      </c>
-      <c r="Y5" s="76" t="str">
+        <v>9711396405</v>
+      </c>
+      <c r="Y5" s="74" t="str">
         <f>IF('New Joiner Form'!G12=0,"",'New Joiner Form'!G12)</f>
-        <v/>
-      </c>
-      <c r="Z5" s="76" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AA5" s="76" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AB5" s="76" t="str">
+        <v>B8876011</v>
+      </c>
+      <c r="Z5" s="74" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="AA5" s="74" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="AB5" s="74" t="str">
         <f>IF('New Joiner Form'!A19=0,"",'New Joiner Form'!A19)</f>
         <v/>
       </c>
-      <c r="AC5" s="76" t="str">
+      <c r="AC5" s="74" t="str">
         <f>IF('New Joiner Form'!B19=0,"",'New Joiner Form'!B19)</f>
         <v/>
       </c>
-      <c r="AD5" s="76" t="str">
+      <c r="AD5" s="74" t="str">
         <f>IF('New Joiner Form'!C19=0,"",'New Joiner Form'!C19)</f>
         <v/>
       </c>
-      <c r="AE5" s="89" t="str">
+      <c r="AE5" s="87" t="str">
         <f>IF('New Joiner Form'!D19=0,"",'New Joiner Form'!D19)</f>
         <v/>
       </c>
-      <c r="AF5" s="76" t="str">
+      <c r="AF5" s="74" t="str">
         <f>IF('New Joiner Form'!E19=0,"",'New Joiner Form'!E19)</f>
         <v/>
       </c>
-      <c r="AG5" s="76" t="str">
+      <c r="AG5" s="74" t="str">
         <f>IF('New Joiner Form'!A20=0,"",'New Joiner Form'!A20)</f>
         <v/>
       </c>
-      <c r="AH5" s="76" t="str">
+      <c r="AH5" s="74" t="str">
         <f>IF('New Joiner Form'!B20=0,"",'New Joiner Form'!B20)</f>
         <v/>
       </c>
-      <c r="AI5" s="76" t="str">
+      <c r="AI5" s="74" t="str">
         <f>IF('New Joiner Form'!C20=0,"",'New Joiner Form'!C20)</f>
         <v/>
       </c>
-      <c r="AJ5" s="89" t="str">
+      <c r="AJ5" s="87" t="str">
         <f>IF('New Joiner Form'!D20=0,"",'New Joiner Form'!D20)</f>
         <v/>
       </c>
-      <c r="AK5" s="76" t="str">
+      <c r="AK5" s="74" t="str">
         <f>IF('New Joiner Form'!E20=0,"",'New Joiner Form'!E20)</f>
         <v/>
       </c>
-      <c r="AL5" s="76" t="str">
+      <c r="AL5" s="74" t="str">
         <f>IF('New Joiner Form'!A21=0,"",'New Joiner Form'!A21)</f>
         <v/>
       </c>
-      <c r="AM5" s="76" t="str">
+      <c r="AM5" s="74" t="str">
         <f>IF('New Joiner Form'!B21=0,"",'New Joiner Form'!B21)</f>
         <v/>
       </c>
-      <c r="AN5" s="76" t="str">
+      <c r="AN5" s="74" t="str">
         <f>IF('New Joiner Form'!C21=0,"",'New Joiner Form'!C21)</f>
         <v/>
       </c>
-      <c r="AO5" s="89" t="str">
+      <c r="AO5" s="87" t="str">
         <f>IF('New Joiner Form'!D21=0,"",'New Joiner Form'!D21)</f>
         <v/>
       </c>
-      <c r="AP5" s="76" t="str">
+      <c r="AP5" s="74" t="str">
         <f>IF('New Joiner Form'!E21=0,"",'New Joiner Form'!E21)</f>
         <v/>
       </c>
-      <c r="AQ5" s="76" t="str">
+      <c r="AQ5" s="74" t="str">
         <f>IF('New Joiner Form'!A22=0,"",'New Joiner Form'!A22)</f>
         <v/>
       </c>
-      <c r="AR5" s="76" t="str">
+      <c r="AR5" s="74" t="str">
         <f>IF('New Joiner Form'!B22=0,"",'New Joiner Form'!B22)</f>
         <v/>
       </c>
-      <c r="AS5" s="76" t="str">
+      <c r="AS5" s="74" t="str">
         <f>IF('New Joiner Form'!C22=0,"",'New Joiner Form'!C22)</f>
         <v/>
       </c>
-      <c r="AT5" s="89" t="str">
+      <c r="AT5" s="87" t="str">
         <f>IF('New Joiner Form'!D22=0,"",'New Joiner Form'!D22)</f>
         <v/>
       </c>
-      <c r="AU5" s="76" t="str">
+      <c r="AU5" s="74" t="str">
         <f>IF('New Joiner Form'!E22=0,"",'New Joiner Form'!E22)</f>
         <v/>
       </c>
-      <c r="AV5" s="76" t="str">
+      <c r="AV5" s="74" t="str">
         <f>IF('New Joiner Form'!A23=0,"",'New Joiner Form'!A23)</f>
         <v/>
       </c>
-      <c r="AW5" s="76" t="str">
+      <c r="AW5" s="74" t="str">
         <f>IF('New Joiner Form'!B23=0,"",'New Joiner Form'!B23)</f>
         <v/>
       </c>
-      <c r="AX5" s="76" t="str">
+      <c r="AX5" s="74" t="str">
         <f>IF('New Joiner Form'!C23=0,"",'New Joiner Form'!C23)</f>
         <v/>
       </c>
-      <c r="AY5" s="76" t="str">
+      <c r="AY5" s="74" t="str">
         <f>IF('New Joiner Form'!D23=0,"",'New Joiner Form'!D23)</f>
         <v/>
       </c>
-      <c r="AZ5" s="76" t="str">
+      <c r="AZ5" s="74" t="str">
         <f>IF('New Joiner Form'!E23=0,"",'New Joiner Form'!E23)</f>
         <v/>
       </c>
-      <c r="BA5" s="76" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="BB5" s="76" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="BC5" s="76" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="BD5" s="76" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="BE5" s="76" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="BF5" s="76" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="BG5" s="76" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="BH5" s="76" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="BI5" s="76" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="BJ5" s="76" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="BK5" s="76" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="BL5" s="76" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="BM5" s="76" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="BN5" s="76" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="BO5" s="76" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="BP5" s="76" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="BQ5" s="76" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="BR5" s="76" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="BS5" s="76" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="BT5" s="76" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="BU5" s="76" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="BV5" s="76" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="BW5" s="76" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="BX5" s="76" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="BY5" s="76" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="BZ5" s="76" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="CA5" s="76" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="CB5" s="76" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="CC5" s="76" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="CD5" s="76" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="CE5" s="76" t="str">
+      <c r="BA5" s="74" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="BB5" s="74" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="BC5" s="74" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="BD5" s="74" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="BE5" s="74" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="BF5" s="74" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="BG5" s="74" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="BH5" s="74" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="BI5" s="74" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="BJ5" s="74" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="BK5" s="74" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="BL5" s="74" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="BM5" s="74" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="BN5" s="74" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="BO5" s="74" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="BP5" s="74" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="BQ5" s="74" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="BR5" s="74" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="BS5" s="74" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="BT5" s="74" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="BU5" s="74" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="BV5" s="74" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="BW5" s="74" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="BX5" s="74" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="BY5" s="74" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="BZ5" s="74" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="CA5" s="74" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="CB5" s="74" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="CC5" s="74" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="CD5" s="74" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="CE5" s="74" t="str">
         <f>IF('New Joiner Form'!A30=0,"",'New Joiner Form'!A30)</f>
-        <v/>
-      </c>
-      <c r="CF5" s="76" t="str">
+        <v>Satender Kumar
+159-160,1st floor, Pocket-7, Sector-24 Rohini Delhi-85</v>
+      </c>
+      <c r="CF5" s="74" t="str">
         <f>IF('New Joiner Form'!B30=0,"",'New Joiner Form'!B30)</f>
-        <v/>
-      </c>
-      <c r="CG5" s="76" t="str">
+        <v>Father</v>
+      </c>
+      <c r="CG5" s="74">
         <f>IF('New Joiner Form'!C30=0,"",'New Joiner Form'!C30)</f>
-        <v/>
-      </c>
-      <c r="CH5" s="76" t="str">
+        <v>67</v>
+      </c>
+      <c r="CH5" s="74">
         <f>IF('New Joiner Form'!D30=0,"",'New Joiner Form'!D30)</f>
-        <v/>
-      </c>
-      <c r="CI5" s="76" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="CI5" s="74" t="str">
         <f>IF('New Joiner Form'!E30=0,"",'New Joiner Form'!E30)</f>
-        <v/>
-      </c>
-      <c r="CJ5" s="76" t="str">
+        <v>NA</v>
+      </c>
+      <c r="CJ5" s="74" t="str">
         <f>IF('New Joiner Form'!F30=0,"",'New Joiner Form'!F30)</f>
-        <v/>
-      </c>
-      <c r="CK5" s="76" t="str">
+        <v>Suman
+159-160,1st floor, Pocket-7, Sector-24 Rohini Delhi-85 
+Mother</v>
+      </c>
+      <c r="CK5" s="74" t="str">
         <f>IF('New Joiner Form'!A31=0,"",'New Joiner Form'!A31)</f>
-        <v/>
-      </c>
-      <c r="CL5" s="76" t="str">
+        <v>Suman
+159-160,1st floor, Pocket-7, Sector-24 Rohini Delhi-85</v>
+      </c>
+      <c r="CL5" s="74" t="str">
         <f>IF('New Joiner Form'!B31=0,"",'New Joiner Form'!B31)</f>
-        <v/>
-      </c>
-      <c r="CM5" s="76" t="str">
+        <v>Mother</v>
+      </c>
+      <c r="CM5" s="74">
         <f>IF('New Joiner Form'!C31=0,"",'New Joiner Form'!C31)</f>
-        <v/>
-      </c>
-      <c r="CN5" s="76" t="str">
+        <v>58</v>
+      </c>
+      <c r="CN5" s="74">
         <f>IF('New Joiner Form'!D31=0,"",'New Joiner Form'!D31)</f>
-        <v/>
-      </c>
-      <c r="CO5" s="76" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="CO5" s="74" t="str">
         <f>IF('New Joiner Form'!E31=0,"",'New Joiner Form'!E31)</f>
-        <v/>
-      </c>
-      <c r="CP5" s="76" t="str">
+        <v>NA</v>
+      </c>
+      <c r="CP5" s="74" t="str">
         <f>IF('New Joiner Form'!F31=0,"",'New Joiner Form'!F31)</f>
-        <v/>
-      </c>
-      <c r="CQ5" s="76" t="str">
+        <v>Satender Kumar
+159-160,1st floor, Pocket-7, Sector-24 Rohini Delhi-85
+Father</v>
+      </c>
+      <c r="CQ5" s="74" t="str">
         <f>IF('New Joiner Form'!A32=0,"",'New Joiner Form'!A32)</f>
         <v/>
       </c>
-      <c r="CR5" s="76" t="str">
+      <c r="CR5" s="74" t="str">
         <f>IF('New Joiner Form'!B32=0,"",'New Joiner Form'!B32)</f>
         <v/>
       </c>
-      <c r="CS5" s="76" t="str">
+      <c r="CS5" s="74" t="str">
         <f>IF('New Joiner Form'!C32=0,"",'New Joiner Form'!C32)</f>
         <v/>
       </c>
-      <c r="CT5" s="76" t="str">
+      <c r="CT5" s="74" t="str">
         <f>IF('New Joiner Form'!D32=0,"",'New Joiner Form'!D32)</f>
         <v/>
       </c>
-      <c r="CU5" s="76" t="str">
+      <c r="CU5" s="74" t="str">
         <f>IF('New Joiner Form'!E32=0,"",'New Joiner Form'!E32)</f>
         <v/>
       </c>
-      <c r="CV5" s="76" t="str">
+      <c r="CV5" s="74" t="str">
         <f>IF('New Joiner Form'!F32=0,"",'New Joiner Form'!F32)</f>
         <v/>
       </c>
-      <c r="CW5" s="76" t="str">
+      <c r="CW5" s="74" t="str">
         <f>IF('New Joiner Form'!A33=0,"",'New Joiner Form'!A33)</f>
         <v/>
       </c>
-      <c r="CX5" s="76" t="str">
+      <c r="CX5" s="74" t="str">
         <f>IF('New Joiner Form'!B33=0,"",'New Joiner Form'!B33)</f>
         <v/>
       </c>
-      <c r="CY5" s="76" t="str">
+      <c r="CY5" s="74" t="str">
         <f>IF('New Joiner Form'!C33=0,"",'New Joiner Form'!C33)</f>
         <v/>
       </c>
-      <c r="CZ5" s="76" t="str">
+      <c r="CZ5" s="74" t="str">
         <f>IF('New Joiner Form'!D33=0,"",'New Joiner Form'!D33)</f>
         <v/>
       </c>
-      <c r="DA5" s="76" t="str">
+      <c r="DA5" s="74" t="str">
         <f>IF('New Joiner Form'!E33=0,"",'New Joiner Form'!E33)</f>
         <v/>
       </c>
-      <c r="DB5" s="76" t="str">
+      <c r="DB5" s="74" t="str">
         <f>IF('New Joiner Form'!F33=0,"",'New Joiner Form'!F33)</f>
         <v/>
       </c>
-      <c r="DC5" s="76" t="str">
+      <c r="DC5" s="74" t="str">
         <f>IF('New Joiner Form'!A34=0,"",'New Joiner Form'!A34)</f>
         <v/>
       </c>
-      <c r="DD5" s="76" t="str">
+      <c r="DD5" s="74" t="str">
         <f>IF('New Joiner Form'!B34=0,"",'New Joiner Form'!B34)</f>
         <v/>
       </c>
-      <c r="DE5" s="76" t="str">
+      <c r="DE5" s="74" t="str">
         <f>IF('New Joiner Form'!C34=0,"",'New Joiner Form'!C34)</f>
         <v/>
       </c>
-      <c r="DF5" s="76" t="str">
+      <c r="DF5" s="74" t="str">
         <f>IF('New Joiner Form'!D34=0,"",'New Joiner Form'!D34)</f>
         <v/>
       </c>
-      <c r="DG5" s="76" t="str">
+      <c r="DG5" s="74" t="str">
         <f>IF('New Joiner Form'!E34=0,"",'New Joiner Form'!E34)</f>
         <v/>
       </c>
-      <c r="DH5" s="76" t="str">
+      <c r="DH5" s="74" t="str">
         <f>IF('New Joiner Form'!F34=0,"",'New Joiner Form'!F34)</f>
         <v/>
       </c>
-      <c r="DI5" s="76" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="DJ5" s="76" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="DK5" s="76" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="DL5" s="89" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="DM5" s="89" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="DN5" s="76" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="DO5" s="89" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="DP5" s="76" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="DQ5" s="76" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="DR5" s="76" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="DS5" s="89" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="DT5" s="89" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="DU5" s="76" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="DV5" s="89" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="DW5" s="76" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="DX5" s="76" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="DY5" s="76" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="DZ5" s="89" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="EA5" s="89" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="EB5" s="76" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="EC5" s="89" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="ED5" s="76" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="EE5" s="76" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="EF5" s="76" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="EG5" s="76" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="EH5" s="76" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="EI5" s="76" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="EJ5" s="76" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="EK5" s="76" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="EL5" s="76" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="EM5" s="76" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="EN5" s="76" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="EO5" s="76" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="EP5" s="76" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="EQ5" s="76" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="ER5" s="76" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="ES5" s="76" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="ET5" s="76" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="EU5" s="76" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="EV5" s="76" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="EW5" s="76" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="EX5" s="76" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="EY5" s="89" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="EZ5" s="76" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="FA5" s="76" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="FB5" s="76" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="FC5" s="76" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="FD5" s="76" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="FE5" s="76" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="FF5" s="76" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="FG5" s="76" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="FH5" s="76" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="FI5" s="76" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="FJ5" s="76" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="FK5" s="76" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="FL5" s="76" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="FM5" s="76" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="FN5" s="76" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="FO5" s="76" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="FP5" s="76" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="FQ5" s="76" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="FR5" s="76" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="FS5" s="76" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="FT5" s="76" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="FU5" s="89" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="FV5" s="76" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="FW5" s="76" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="FX5" s="89" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="FY5" s="76" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="FZ5" s="76" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="GA5" s="76" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="GB5" s="76" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="GC5" s="76" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="GD5" s="76" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="GE5" s="76" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="GF5" s="76" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="GG5" s="76" t="e">
-        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="GH5" s="76" t="e">
+      <c r="DI5" s="74" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="DJ5" s="74" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="DK5" s="74" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="DL5" s="87" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="DM5" s="87" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="DN5" s="74" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="DO5" s="87" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="DP5" s="74" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="DQ5" s="74" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="DR5" s="74" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="DS5" s="87" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="DT5" s="87" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="DU5" s="74" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="DV5" s="87" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="DW5" s="74" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="DX5" s="74" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="DY5" s="74" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="DZ5" s="87" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="EA5" s="87" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="EB5" s="74" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="EC5" s="87" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="ED5" s="74" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="EE5" s="74" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="EF5" s="74" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="EG5" s="74" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="EH5" s="74" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="EI5" s="74" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="EJ5" s="74" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="EK5" s="74" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="EL5" s="74" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="EM5" s="74" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="EN5" s="74" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="EO5" s="74" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="EP5" s="74" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="EQ5" s="74" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="ER5" s="74" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="ES5" s="74" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="ET5" s="74" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="EU5" s="74" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="EV5" s="74" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="EW5" s="74" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="EX5" s="74" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="EY5" s="87" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="EZ5" s="74" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="FA5" s="74" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="FB5" s="74" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="FC5" s="74" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="FD5" s="74" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="FE5" s="74" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="FF5" s="74" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="FG5" s="74" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="FH5" s="74" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="FI5" s="74" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="FJ5" s="74" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="FK5" s="74" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="FL5" s="74" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="FM5" s="74" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="FN5" s="74" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="FO5" s="74" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="FP5" s="74" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="FQ5" s="74" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="FR5" s="74" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="FS5" s="74" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="FT5" s="74" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="FU5" s="87" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="FV5" s="74" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="FW5" s="74" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="FX5" s="87" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="FY5" s="74" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="FZ5" s="74" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="GA5" s="74" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="GB5" s="74" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="GC5" s="74" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="GD5" s="74" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="GE5" s="74" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="GF5" s="74" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="GG5" s="74" t="e">
+        <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="GH5" s="74" t="e">
         <f>IF('New Joiner Form'!#REF!=0,"",'New Joiner Form'!#REF!)</f>
         <v>#REF!</v>
       </c>
@@ -6490,170 +6389,170 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:N71"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="25.5" x14ac:dyDescent="0.7"/>
   <cols>
     <col min="1" max="1" width="29" style="6" customWidth="1"/>
     <col min="2" max="2" width="28" style="6" customWidth="1"/>
-    <col min="3" max="3" width="34.42578125" style="6" customWidth="1"/>
-    <col min="4" max="4" width="10.140625" style="6" customWidth="1"/>
-    <col min="5" max="5" width="9.7109375" style="9" customWidth="1"/>
-    <col min="6" max="6" width="11.7109375" style="9" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="9" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.7109375" style="9"/>
+    <col min="3" max="3" width="34.44140625" style="6" customWidth="1"/>
+    <col min="4" max="4" width="10.109375" style="6" customWidth="1"/>
+    <col min="5" max="5" width="9.6640625" style="9" customWidth="1"/>
+    <col min="6" max="6" width="11.6640625" style="9" customWidth="1"/>
+    <col min="7" max="7" width="14.44140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.6640625" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="149"/>
-      <c r="B1" s="149"/>
-      <c r="C1" s="149"/>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="150" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.7">
+      <c r="A1" s="152"/>
+      <c r="B1" s="152"/>
+      <c r="C1" s="152"/>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.7">
+      <c r="A4" s="153" t="s">
         <v>249</v>
       </c>
-      <c r="B4" s="150"/>
-      <c r="C4" s="150"/>
-    </row>
-    <row r="6" spans="1:3">
+      <c r="B4" s="153"/>
+      <c r="C4" s="153"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A6" s="6" t="s">
         <v>250</v>
       </c>
-      <c r="B6" s="151"/>
-      <c r="C6" s="151"/>
-    </row>
-    <row r="8" spans="1:3">
+      <c r="B6" s="154"/>
+      <c r="C6" s="154"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A8" s="7" t="s">
         <v>251</v>
       </c>
-      <c r="B8" s="151" t="e">
+      <c r="B8" s="154" t="e">
         <f>Data!A5</f>
         <v>#REF!</v>
       </c>
-      <c r="C8" s="151"/>
-    </row>
-    <row r="9" spans="1:3">
+      <c r="C8" s="154"/>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A9" s="7" t="s">
         <v>252</v>
       </c>
-      <c r="B9" s="151" t="str">
+      <c r="B9" s="154" t="str">
         <f>Data!B5</f>
-        <v/>
-      </c>
-      <c r="C9" s="151"/>
-    </row>
-    <row r="10" spans="1:3">
+        <v>Pushkar Singh</v>
+      </c>
+      <c r="C9" s="154"/>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A10" s="7" t="s">
         <v>253</v>
       </c>
-      <c r="B10" s="152"/>
-      <c r="C10" s="152"/>
-    </row>
-    <row r="11" spans="1:3">
+      <c r="B10" s="155"/>
+      <c r="C10" s="155"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A11" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="B11" s="152"/>
-      <c r="C11" s="152"/>
-    </row>
-    <row r="12" spans="1:3">
+      <c r="B11" s="155"/>
+      <c r="C11" s="155"/>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A12" s="7" t="s">
         <v>255</v>
       </c>
-      <c r="B12" s="152"/>
-      <c r="C12" s="152"/>
-    </row>
-    <row r="13" spans="1:3">
+      <c r="B12" s="155"/>
+      <c r="C12" s="155"/>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A13" s="7" t="s">
         <v>256</v>
       </c>
-      <c r="B13" s="153" t="e">
+      <c r="B13" s="156" t="e">
         <f>Data!FX5</f>
         <v>#REF!</v>
       </c>
-      <c r="C13" s="151"/>
-    </row>
-    <row r="15" spans="1:3">
+      <c r="C13" s="154"/>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A15" s="7" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="29.1">
-      <c r="A16" s="105" t="s">
+    <row r="16" spans="1:3" ht="51" x14ac:dyDescent="0.7">
+      <c r="A16" s="103" t="s">
         <v>258</v>
       </c>
-      <c r="B16" s="154" t="e">
+      <c r="B16" s="157" t="e">
         <f>CONCATENATE( Data!DI5, ",",Data!DJ5)</f>
         <v>#REF!</v>
       </c>
-      <c r="C16" s="154"/>
-    </row>
-    <row r="17" spans="1:9">
+      <c r="C16" s="157"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.7">
       <c r="A17" s="8" t="s">
         <v>259</v>
       </c>
-      <c r="B17" s="147" t="e">
+      <c r="B17" s="150" t="e">
         <f>Data!DK5</f>
         <v>#REF!</v>
       </c>
-      <c r="C17" s="148"/>
-    </row>
-    <row r="18" spans="1:9">
+      <c r="C17" s="151"/>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.7">
       <c r="A18" s="8" t="s">
         <v>260</v>
       </c>
-      <c r="B18" s="147"/>
-      <c r="C18" s="148"/>
-    </row>
-    <row r="19" spans="1:9">
+      <c r="B18" s="150"/>
+      <c r="C18" s="151"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.7">
       <c r="A19" s="8" t="s">
         <v>261</v>
       </c>
-      <c r="B19" s="147" t="e">
+      <c r="B19" s="150" t="e">
         <f>Data!DN5</f>
         <v>#REF!</v>
       </c>
-      <c r="C19" s="148"/>
-    </row>
-    <row r="20" spans="1:9">
+      <c r="C19" s="151"/>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.7">
       <c r="A20" s="8" t="s">
         <v>262</v>
       </c>
-      <c r="B20" s="157" t="e">
+      <c r="B20" s="160" t="e">
         <f>Data!DO5</f>
         <v>#REF!</v>
       </c>
-      <c r="C20" s="158"/>
-    </row>
-    <row r="21" spans="1:9">
+      <c r="C20" s="161"/>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.7">
       <c r="A21" s="10" t="s">
         <v>263</v>
       </c>
-      <c r="B21" s="159" t="e">
+      <c r="B21" s="162" t="e">
         <f>Data!DL5</f>
         <v>#REF!</v>
       </c>
-      <c r="C21" s="148"/>
-    </row>
-    <row r="22" spans="1:9">
+      <c r="C21" s="151"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.7">
       <c r="A22" s="10" t="s">
         <v>264</v>
       </c>
-      <c r="B22" s="159" t="e">
+      <c r="B22" s="162" t="e">
         <f>Data!DM5</f>
         <v>#REF!</v>
       </c>
-      <c r="C22" s="148"/>
-    </row>
-    <row r="24" spans="1:9">
+      <c r="C22" s="151"/>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.7">
       <c r="A24" s="7" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="25" spans="1:9">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.7">
       <c r="A25" s="11" t="s">
         <v>266</v>
       </c>
@@ -6670,16 +6569,16 @@
       <c r="H25" s="12"/>
       <c r="I25" s="12"/>
     </row>
-    <row r="26" spans="1:9">
-      <c r="A26" s="82" t="e">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.7">
+      <c r="A26" s="80" t="e">
         <f>Data!ED5</f>
         <v>#REF!</v>
       </c>
-      <c r="B26" s="82" t="e">
+      <c r="B26" s="80" t="e">
         <f>Data!EE5</f>
         <v>#REF!</v>
       </c>
-      <c r="C26" s="82" t="e">
+      <c r="C26" s="80" t="e">
         <f>Data!EF5</f>
         <v>#REF!</v>
       </c>
@@ -6690,16 +6589,16 @@
       <c r="H26" s="12"/>
       <c r="I26" s="12"/>
     </row>
-    <row r="27" spans="1:9">
-      <c r="A27" s="82" t="e">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.7">
+      <c r="A27" s="80" t="e">
         <f>Data!EG5</f>
         <v>#REF!</v>
       </c>
-      <c r="B27" s="82" t="e">
+      <c r="B27" s="80" t="e">
         <f>Data!EH5</f>
         <v>#REF!</v>
       </c>
-      <c r="C27" s="82" t="e">
+      <c r="C27" s="80" t="e">
         <f>Data!EI5</f>
         <v>#REF!</v>
       </c>
@@ -6710,16 +6609,16 @@
       <c r="H27" s="12"/>
       <c r="I27" s="12"/>
     </row>
-    <row r="28" spans="1:9">
-      <c r="A28" s="82" t="e">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.7">
+      <c r="A28" s="80" t="e">
         <f>Data!EJ5</f>
         <v>#REF!</v>
       </c>
-      <c r="B28" s="82" t="e">
+      <c r="B28" s="80" t="e">
         <f>Data!EK5</f>
         <v>#REF!</v>
       </c>
-      <c r="C28" s="82" t="e">
+      <c r="C28" s="80" t="e">
         <f>Data!EL5</f>
         <v>#REF!</v>
       </c>
@@ -6730,16 +6629,16 @@
       <c r="H28" s="12"/>
       <c r="I28" s="12"/>
     </row>
-    <row r="29" spans="1:9">
-      <c r="A29" s="82" t="e">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.7">
+      <c r="A29" s="80" t="e">
         <f>Data!EM5</f>
         <v>#REF!</v>
       </c>
-      <c r="B29" s="82" t="e">
+      <c r="B29" s="80" t="e">
         <f>Data!EN5</f>
         <v>#REF!</v>
       </c>
-      <c r="C29" s="82" t="e">
+      <c r="C29" s="80" t="e">
         <f>Data!EO5</f>
         <v>#REF!</v>
       </c>
@@ -6750,16 +6649,16 @@
       <c r="H29" s="12"/>
       <c r="I29" s="12"/>
     </row>
-    <row r="30" spans="1:9">
-      <c r="A30" s="82" t="e">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.7">
+      <c r="A30" s="80" t="e">
         <f>Data!EP5</f>
         <v>#REF!</v>
       </c>
-      <c r="B30" s="82" t="e">
+      <c r="B30" s="80" t="e">
         <f>Data!EQ5</f>
         <v>#REF!</v>
       </c>
-      <c r="C30" s="82" t="e">
+      <c r="C30" s="80" t="e">
         <f>Data!ER5</f>
         <v>#REF!</v>
       </c>
@@ -6770,7 +6669,7 @@
       <c r="H30" s="12"/>
       <c r="I30" s="12"/>
     </row>
-    <row r="31" spans="1:9">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.7">
       <c r="D31" s="13"/>
       <c r="E31" s="14"/>
       <c r="F31" s="12"/>
@@ -6778,7 +6677,7 @@
       <c r="H31" s="12"/>
       <c r="I31" s="12"/>
     </row>
-    <row r="32" spans="1:9">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.7">
       <c r="A32" s="7" t="s">
         <v>269</v>
       </c>
@@ -6789,57 +6688,57 @@
       <c r="H32" s="12"/>
       <c r="I32" s="12"/>
     </row>
-    <row r="33" spans="1:14">
-      <c r="A33" s="160" t="s">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.7">
+      <c r="A33" s="163" t="s">
         <v>270</v>
       </c>
-      <c r="B33" s="161"/>
-      <c r="C33" s="148"/>
+      <c r="B33" s="164"/>
+      <c r="C33" s="151"/>
       <c r="D33" s="13"/>
       <c r="E33" s="14"/>
       <c r="L33" s="14"/>
       <c r="M33" s="14"/>
       <c r="N33" s="14"/>
     </row>
-    <row r="34" spans="1:14">
-      <c r="A34" s="160" t="s">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.7">
+      <c r="A34" s="163" t="s">
         <v>271</v>
       </c>
-      <c r="B34" s="161"/>
-      <c r="C34" s="148"/>
+      <c r="B34" s="164"/>
+      <c r="C34" s="151"/>
       <c r="D34" s="13"/>
       <c r="E34" s="14"/>
       <c r="L34" s="14"/>
       <c r="M34" s="14"/>
       <c r="N34" s="14"/>
     </row>
-    <row r="35" spans="1:14">
-      <c r="A35" s="162" t="s">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.7">
+      <c r="A35" s="165" t="s">
         <v>272</v>
       </c>
-      <c r="B35" s="154"/>
-      <c r="C35" s="154"/>
+      <c r="B35" s="157"/>
+      <c r="C35" s="157"/>
       <c r="D35" s="13"/>
       <c r="E35" s="14"/>
       <c r="L35" s="14"/>
       <c r="M35" s="14"/>
       <c r="N35" s="14"/>
     </row>
-    <row r="36" spans="1:14">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.7">
       <c r="D36" s="13"/>
       <c r="E36" s="14"/>
       <c r="L36" s="14"/>
       <c r="M36" s="14"/>
       <c r="N36" s="14"/>
     </row>
-    <row r="37" spans="1:14">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.7">
       <c r="A37" s="7" t="s">
         <v>273</v>
       </c>
       <c r="D37" s="13"/>
       <c r="E37" s="14"/>
     </row>
-    <row r="38" spans="1:14">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.7">
       <c r="A38" s="11" t="s">
         <v>73</v>
       </c>
@@ -6852,12 +6751,12 @@
       <c r="D38" s="13"/>
       <c r="E38" s="14"/>
     </row>
-    <row r="39" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A39" s="82" t="str">
+    <row r="39" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A39" s="80">
         <f>Data!T5</f>
-        <v/>
-      </c>
-      <c r="B39" s="82" t="str">
+        <v>9313569413</v>
+      </c>
+      <c r="B39" s="80" t="str">
         <f>Data!U5</f>
         <v/>
       </c>
@@ -6865,132 +6764,132 @@
       <c r="D39" s="13"/>
       <c r="E39" s="14"/>
     </row>
-    <row r="40" spans="1:14" ht="15.75" customHeight="1">
-      <c r="A40" s="82"/>
-      <c r="B40" s="82"/>
-      <c r="C40" s="82"/>
-    </row>
-    <row r="42" spans="1:14">
+    <row r="40" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A40" s="80"/>
+      <c r="B40" s="80"/>
+      <c r="C40" s="80"/>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.7">
       <c r="A42" s="6" t="s">
         <v>276</v>
       </c>
-      <c r="B42" s="151" t="str">
+      <c r="B42" s="154" t="str">
         <f>Data!V5</f>
-        <v/>
-      </c>
-      <c r="C42" s="151"/>
-    </row>
-    <row r="43" spans="1:14">
+        <v>Satender Kumar</v>
+      </c>
+      <c r="C42" s="154"/>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.7">
       <c r="A43" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="B43" s="151" t="str">
+      <c r="B43" s="154" t="str">
         <f>Data!W5</f>
-        <v/>
-      </c>
-      <c r="C43" s="151"/>
-    </row>
-    <row r="50" spans="1:4">
-      <c r="A50" s="155" t="s">
+        <v>Suman</v>
+      </c>
+      <c r="C43" s="154"/>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.7">
+      <c r="A50" s="158" t="s">
         <v>278</v>
       </c>
-      <c r="B50" s="156" t="str">
+      <c r="B50" s="159" t="str">
         <f>Data!J5</f>
-        <v/>
-      </c>
-      <c r="C50" s="156"/>
-    </row>
-    <row r="51" spans="1:4">
-      <c r="A51" s="155"/>
-      <c r="B51" s="156"/>
-      <c r="C51" s="156"/>
-    </row>
-    <row r="52" spans="1:4" ht="8.25" customHeight="1">
-      <c r="A52" s="155"/>
-      <c r="B52" s="156"/>
-      <c r="C52" s="156"/>
-    </row>
-    <row r="54" spans="1:4">
-      <c r="A54" s="155" t="s">
+        <v>159-160,1st floor, Pocket-7, Sector-24 Rohini</v>
+      </c>
+      <c r="C50" s="159"/>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.7">
+      <c r="A51" s="158"/>
+      <c r="B51" s="159"/>
+      <c r="C51" s="159"/>
+    </row>
+    <row r="52" spans="1:4" ht="8.25" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A52" s="158"/>
+      <c r="B52" s="159"/>
+      <c r="C52" s="159"/>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.7">
+      <c r="A54" s="158" t="s">
         <v>279</v>
       </c>
-      <c r="B54" s="156" t="str">
+      <c r="B54" s="159" t="str">
         <f>Data!O5</f>
-        <v/>
-      </c>
-      <c r="C54" s="156"/>
-    </row>
-    <row r="55" spans="1:4">
-      <c r="A55" s="155"/>
-      <c r="B55" s="156"/>
-      <c r="C55" s="156"/>
-    </row>
-    <row r="56" spans="1:4" ht="7.5" customHeight="1">
-      <c r="A56" s="155"/>
-      <c r="B56" s="156"/>
-      <c r="C56" s="156"/>
-    </row>
-    <row r="58" spans="1:4">
+        <v>159-160,1st floor, Pocket-7, Sector-24 Rohini</v>
+      </c>
+      <c r="C54" s="159"/>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.7">
+      <c r="A55" s="158"/>
+      <c r="B55" s="159"/>
+      <c r="C55" s="159"/>
+    </row>
+    <row r="56" spans="1:4" ht="7.5" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A56" s="158"/>
+      <c r="B56" s="159"/>
+      <c r="C56" s="159"/>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.7">
       <c r="A58" s="15" t="s">
         <v>280</v>
       </c>
-      <c r="B58" s="164" t="str">
+      <c r="B58" s="167" t="str">
         <f>Data!D5</f>
-        <v/>
-      </c>
-      <c r="C58" s="164"/>
-    </row>
-    <row r="59" spans="1:4">
+        <v>23/04/1994</v>
+      </c>
+      <c r="C58" s="167"/>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.7">
       <c r="A59" s="15"/>
       <c r="D59" s="7"/>
     </row>
-    <row r="60" spans="1:4">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.7">
       <c r="A60" s="15" t="s">
         <v>281</v>
       </c>
-      <c r="B60" s="151" t="str">
+      <c r="B60" s="154">
         <f>Data!X5</f>
-        <v/>
-      </c>
-      <c r="C60" s="151"/>
-    </row>
-    <row r="61" spans="1:4">
+        <v>9711396405</v>
+      </c>
+      <c r="C60" s="154"/>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.7">
       <c r="A61" s="15"/>
     </row>
-    <row r="62" spans="1:4">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.7">
       <c r="A62" s="15" t="s">
         <v>282</v>
       </c>
-      <c r="B62" s="151"/>
-      <c r="C62" s="151"/>
-    </row>
-    <row r="63" spans="1:4">
+      <c r="B62" s="154"/>
+      <c r="C62" s="154"/>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.7">
       <c r="A63" s="15"/>
     </row>
-    <row r="64" spans="1:4">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.7">
       <c r="A64" s="15" t="s">
         <v>283</v>
       </c>
-      <c r="B64" s="151" t="str">
+      <c r="B64" s="154" t="str">
         <f>Data!H5</f>
-        <v/>
-      </c>
-      <c r="C64" s="151"/>
-    </row>
-    <row r="65" spans="1:7">
+        <v>JABPS9654C</v>
+      </c>
+      <c r="C64" s="154"/>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.7">
       <c r="A65" s="15"/>
     </row>
-    <row r="66" spans="1:7" ht="30" customHeight="1">
+    <row r="66" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A66" s="16" t="s">
         <v>284</v>
       </c>
-      <c r="B66" s="151" t="str">
+      <c r="B66" s="154" t="str">
         <f>Data!F5</f>
         <v/>
       </c>
-      <c r="C66" s="151"/>
-    </row>
-    <row r="67" spans="1:7">
+      <c r="C66" s="154"/>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.7">
       <c r="A67" s="17"/>
       <c r="C67" s="18"/>
       <c r="D67" s="18"/>
@@ -6998,30 +6897,30 @@
       <c r="F67" s="18"/>
       <c r="G67" s="18"/>
     </row>
-    <row r="68" spans="1:7">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.7">
       <c r="A68" s="15" t="s">
         <v>285</v>
       </c>
-      <c r="B68" s="151" t="str">
+      <c r="B68" s="154">
         <f>Data!G5</f>
-        <v/>
-      </c>
-      <c r="C68" s="151"/>
+        <v>720812235123</v>
+      </c>
+      <c r="C68" s="154"/>
       <c r="D68" s="18"/>
       <c r="E68" s="18"/>
       <c r="F68" s="18"/>
       <c r="G68" s="18"/>
     </row>
-    <row r="69" spans="1:7">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.7">
       <c r="C69" s="19"/>
       <c r="D69" s="19"/>
       <c r="E69" s="18"/>
       <c r="F69" s="18"/>
       <c r="G69" s="18"/>
     </row>
-    <row r="71" spans="1:7">
-      <c r="D71" s="163"/>
-      <c r="E71" s="163"/>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.7">
+      <c r="D71" s="166"/>
+      <c r="E71" s="166"/>
     </row>
   </sheetData>
   <mergeCells count="32">
@@ -7064,70 +6963,70 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:E46"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="25.5" x14ac:dyDescent="0.7"/>
   <cols>
-    <col min="1" max="1" width="29.7109375" style="20" customWidth="1"/>
-    <col min="2" max="2" width="17.7109375" style="20" customWidth="1"/>
-    <col min="3" max="3" width="18.140625" style="20" customWidth="1"/>
-    <col min="4" max="4" width="13.28515625" style="20" customWidth="1"/>
-    <col min="5" max="5" width="13.7109375" style="20" customWidth="1"/>
-    <col min="6" max="6" width="8.85546875" style="20" customWidth="1"/>
-    <col min="7" max="7" width="9.5703125" style="20" customWidth="1"/>
-    <col min="8" max="9" width="14.140625" style="20" customWidth="1"/>
-    <col min="10" max="16384" width="9.140625" style="20"/>
+    <col min="1" max="1" width="29.6640625" style="20" customWidth="1"/>
+    <col min="2" max="2" width="17.6640625" style="20" customWidth="1"/>
+    <col min="3" max="3" width="18.109375" style="20" customWidth="1"/>
+    <col min="4" max="4" width="13.33203125" style="20" customWidth="1"/>
+    <col min="5" max="5" width="13.6640625" style="20" customWidth="1"/>
+    <col min="6" max="6" width="8.88671875" style="20" customWidth="1"/>
+    <col min="7" max="7" width="9.5546875" style="20" customWidth="1"/>
+    <col min="8" max="9" width="14.109375" style="20" customWidth="1"/>
+    <col min="10" max="16384" width="9.109375" style="20"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="9" customFormat="1"/>
-    <row r="2" spans="1:5" s="9" customFormat="1">
+    <row r="1" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.7"/>
+    <row r="2" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.7">
       <c r="A2" s="20"/>
     </row>
-    <row r="3" spans="1:5" s="9" customFormat="1"/>
-    <row r="4" spans="1:5" s="9" customFormat="1"/>
-    <row r="5" spans="1:5">
-      <c r="A5" s="169" t="s">
+    <row r="3" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.7"/>
+    <row r="4" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.7"/>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.7">
+      <c r="A5" s="172" t="s">
         <v>286</v>
       </c>
-      <c r="B5" s="169"/>
-      <c r="C5" s="169"/>
-      <c r="D5" s="169"/>
-      <c r="E5" s="169"/>
-    </row>
-    <row r="6" spans="1:5">
+      <c r="B5" s="172"/>
+      <c r="C5" s="172"/>
+      <c r="D5" s="172"/>
+      <c r="E5" s="172"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A6" s="21"/>
-      <c r="E6" s="166"/>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="E7" s="167"/>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="E8" s="167"/>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="173" t="s">
+      <c r="E6" s="169"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.7">
+      <c r="E7" s="170"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.7">
+      <c r="E8" s="170"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.7">
+      <c r="A9" s="176" t="s">
         <v>287</v>
       </c>
-      <c r="B9" s="173"/>
-      <c r="C9" s="173"/>
-      <c r="E9" s="167"/>
-    </row>
-    <row r="10" spans="1:5">
+      <c r="B9" s="176"/>
+      <c r="C9" s="176"/>
+      <c r="E9" s="170"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A10" s="22" t="s">
         <v>288</v>
       </c>
       <c r="B10" s="23"/>
-      <c r="E10" s="168"/>
-    </row>
-    <row r="11" spans="1:5">
+      <c r="E10" s="171"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A11" s="22" t="s">
         <v>289</v>
       </c>
       <c r="B11" s="23"/>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A13" s="22" t="s">
         <v>290</v>
       </c>
@@ -7135,22 +7034,22 @@
         <v>291</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A14" s="24"/>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A15" s="25" t="s">
         <v>292</v>
       </c>
-      <c r="B15" s="165" t="str">
+      <c r="B15" s="168" t="str">
         <f>Data!B5</f>
-        <v/>
-      </c>
-      <c r="C15" s="165"/>
-      <c r="D15" s="165"/>
-      <c r="E15" s="165"/>
-    </row>
-    <row r="16" spans="1:5">
+        <v>Pushkar Singh</v>
+      </c>
+      <c r="C15" s="168"/>
+      <c r="D15" s="168"/>
+      <c r="E15" s="168"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A16" s="25" t="s">
         <v>293</v>
       </c>
@@ -7161,10 +7060,10 @@
       <c r="C16" s="25" t="s">
         <v>294</v>
       </c>
-      <c r="D16" s="170"/>
-      <c r="E16" s="170"/>
-    </row>
-    <row r="17" spans="1:5" ht="19.5" customHeight="1">
+      <c r="D16" s="173"/>
+      <c r="E16" s="173"/>
+    </row>
+    <row r="17" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A17" s="25" t="s">
         <v>295</v>
       </c>
@@ -7175,167 +7074,167 @@
       <c r="C17" s="25" t="s">
         <v>296</v>
       </c>
-      <c r="D17" s="171" t="e">
+      <c r="D17" s="174" t="e">
         <f>Data!FX5</f>
         <v>#REF!</v>
       </c>
-      <c r="E17" s="171"/>
-    </row>
-    <row r="18" spans="1:5">
+      <c r="E17" s="174"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A18" s="25" t="s">
         <v>297</v>
       </c>
-      <c r="B18" s="94" t="str">
+      <c r="B18" s="92" t="str">
         <f>Data!D5</f>
-        <v/>
+        <v>23/04/1994</v>
       </c>
       <c r="C18" s="25" t="s">
         <v>298</v>
       </c>
-      <c r="D18" s="174" t="str">
+      <c r="D18" s="177" t="str">
         <f>Data!E5</f>
-        <v/>
-      </c>
-      <c r="E18" s="174"/>
-    </row>
-    <row r="19" spans="1:5">
+        <v>A+</v>
+      </c>
+      <c r="E18" s="177"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A19" s="25" t="s">
         <v>299</v>
       </c>
-      <c r="B19" s="93" t="str">
+      <c r="B19" s="91">
         <f>Data!T5</f>
-        <v/>
+        <v>9313569413</v>
       </c>
       <c r="C19" s="25"/>
-      <c r="D19" s="174"/>
-      <c r="E19" s="174"/>
-    </row>
-    <row r="20" spans="1:5">
+      <c r="D19" s="177"/>
+      <c r="E19" s="177"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A20" s="25" t="s">
         <v>300</v>
       </c>
-      <c r="B20" s="92" t="str">
+      <c r="B20" s="90" t="str">
         <f>Data!U5</f>
         <v/>
       </c>
-      <c r="C20" s="91"/>
-      <c r="D20" s="174"/>
-      <c r="E20" s="174"/>
-    </row>
-    <row r="21" spans="1:5">
+      <c r="C20" s="89"/>
+      <c r="D20" s="177"/>
+      <c r="E20" s="177"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A21" s="26"/>
       <c r="B21" s="12"/>
       <c r="C21" s="12"/>
       <c r="D21" s="12"/>
     </row>
-    <row r="23" spans="1:5" ht="19.5" customHeight="1">
-      <c r="A23" s="175" t="s">
+    <row r="23" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A23" s="178" t="s">
         <v>301</v>
       </c>
-      <c r="B23" s="175"/>
-      <c r="C23" s="175"/>
-      <c r="D23" s="175"/>
-      <c r="E23" s="175"/>
-    </row>
-    <row r="24" spans="1:5">
+      <c r="B23" s="178"/>
+      <c r="C23" s="178"/>
+      <c r="D23" s="178"/>
+      <c r="E23" s="178"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A24" s="25" t="s">
         <v>302</v>
       </c>
-      <c r="B24" s="165"/>
-      <c r="C24" s="165"/>
-      <c r="D24" s="165"/>
-      <c r="E24" s="165"/>
-    </row>
-    <row r="25" spans="1:5">
+      <c r="B24" s="168"/>
+      <c r="C24" s="168"/>
+      <c r="D24" s="168"/>
+      <c r="E24" s="168"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A25" s="25" t="s">
         <v>303</v>
       </c>
-      <c r="B25" s="165"/>
-      <c r="C25" s="165"/>
-      <c r="D25" s="165"/>
-      <c r="E25" s="165"/>
-    </row>
-    <row r="26" spans="1:5">
+      <c r="B25" s="168"/>
+      <c r="C25" s="168"/>
+      <c r="D25" s="168"/>
+      <c r="E25" s="168"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A26" s="25" t="s">
         <v>304</v>
       </c>
-      <c r="B26" s="165"/>
-      <c r="C26" s="165"/>
-      <c r="D26" s="165"/>
-      <c r="E26" s="165"/>
-    </row>
-    <row r="27" spans="1:5">
+      <c r="B26" s="168"/>
+      <c r="C26" s="168"/>
+      <c r="D26" s="168"/>
+      <c r="E26" s="168"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A27" s="25" t="s">
         <v>305</v>
       </c>
-      <c r="B27" s="165"/>
-      <c r="C27" s="165"/>
-      <c r="D27" s="165"/>
-      <c r="E27" s="165"/>
-    </row>
-    <row r="28" spans="1:5">
+      <c r="B27" s="168"/>
+      <c r="C27" s="168"/>
+      <c r="D27" s="168"/>
+      <c r="E27" s="168"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A28" s="26"/>
-      <c r="B28" s="172"/>
-      <c r="C28" s="172"/>
-      <c r="D28" s="172"/>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="165" t="s">
+      <c r="B28" s="175"/>
+      <c r="C28" s="175"/>
+      <c r="D28" s="175"/>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.7">
+      <c r="A30" s="168" t="s">
         <v>306</v>
       </c>
-      <c r="B30" s="165"/>
-      <c r="C30" s="165"/>
-      <c r="D30" s="165"/>
-      <c r="E30" s="165"/>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="165" t="s">
+      <c r="B30" s="168"/>
+      <c r="C30" s="168"/>
+      <c r="D30" s="168"/>
+      <c r="E30" s="168"/>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.7">
+      <c r="A31" s="168" t="s">
         <v>307</v>
       </c>
-      <c r="B31" s="165"/>
-      <c r="C31" s="165" t="s">
+      <c r="B31" s="168"/>
+      <c r="C31" s="168" t="s">
         <v>308</v>
       </c>
-      <c r="D31" s="165"/>
-      <c r="E31" s="165"/>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="165" t="s">
+      <c r="D31" s="168"/>
+      <c r="E31" s="168"/>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.7">
+      <c r="A32" s="168" t="s">
         <v>309</v>
       </c>
-      <c r="B32" s="165"/>
-      <c r="C32" s="165"/>
-      <c r="D32" s="165"/>
-      <c r="E32" s="165"/>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="175" t="s">
+      <c r="B32" s="168"/>
+      <c r="C32" s="168"/>
+      <c r="D32" s="168"/>
+      <c r="E32" s="168"/>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.7">
+      <c r="A33" s="178" t="s">
         <v>310</v>
       </c>
-      <c r="B33" s="175"/>
-      <c r="C33" s="175"/>
-      <c r="D33" s="175"/>
-      <c r="E33" s="175"/>
-    </row>
-    <row r="34" spans="1:5" ht="16.5" customHeight="1">
-      <c r="A34" s="96" t="s">
+      <c r="B33" s="178"/>
+      <c r="C33" s="178"/>
+      <c r="D33" s="178"/>
+      <c r="E33" s="178"/>
+    </row>
+    <row r="34" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A34" s="94" t="s">
         <v>311</v>
       </c>
-      <c r="B34" s="97"/>
-      <c r="C34" s="96" t="s">
+      <c r="B34" s="95"/>
+      <c r="C34" s="94" t="s">
         <v>312</v>
       </c>
-      <c r="D34" s="165"/>
-      <c r="E34" s="165"/>
-    </row>
-    <row r="35" spans="1:5">
+      <c r="D34" s="168"/>
+      <c r="E34" s="168"/>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A35" s="25"/>
       <c r="B35" s="23"/>
       <c r="C35" s="25"/>
-      <c r="D35" s="165"/>
-      <c r="E35" s="165"/>
-    </row>
-    <row r="36" spans="1:5">
+      <c r="D35" s="168"/>
+      <c r="E35" s="168"/>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A36" s="25" t="s">
         <v>313</v>
       </c>
@@ -7343,40 +7242,40 @@
       <c r="C36" s="25" t="s">
         <v>314</v>
       </c>
-      <c r="D36" s="165"/>
-      <c r="E36" s="165"/>
-    </row>
-    <row r="37" spans="1:5">
+      <c r="D36" s="168"/>
+      <c r="E36" s="168"/>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A37" s="26"/>
       <c r="B37" s="26"/>
       <c r="C37" s="26"/>
       <c r="D37" s="26"/>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A38" s="21"/>
     </row>
-    <row r="39" spans="1:5">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A39" s="21"/>
     </row>
-    <row r="40" spans="1:5">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A40" s="21"/>
     </row>
-    <row r="41" spans="1:5">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.7">
       <c r="A41" s="21"/>
     </row>
-    <row r="42" spans="1:5" ht="18.600000000000001">
+    <row r="42" spans="1:5" ht="29.25" x14ac:dyDescent="0.75">
       <c r="A42" s="27"/>
     </row>
-    <row r="43" spans="1:5" ht="15.6">
+    <row r="43" spans="1:5" ht="26.25" x14ac:dyDescent="0.7">
       <c r="A43" s="28"/>
     </row>
-    <row r="44" spans="1:5" ht="15.6">
+    <row r="44" spans="1:5" ht="26.25" x14ac:dyDescent="0.7">
       <c r="A44" s="28"/>
     </row>
-    <row r="45" spans="1:5" ht="15.6">
+    <row r="45" spans="1:5" ht="26.25" x14ac:dyDescent="0.7">
       <c r="A45" s="28"/>
     </row>
-    <row r="46" spans="1:5" ht="15.6">
+    <row r="46" spans="1:5" ht="26.25" x14ac:dyDescent="0.7">
       <c r="A46" s="28"/>
     </row>
   </sheetData>
@@ -7413,25 +7312,25 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:J32"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="25.5" x14ac:dyDescent="0.7"/>
   <cols>
     <col min="1" max="1" width="23" style="20" customWidth="1"/>
-    <col min="2" max="2" width="12.140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.140625" style="20"/>
-    <col min="4" max="4" width="10.140625" style="20" customWidth="1"/>
-    <col min="5" max="7" width="9.140625" style="20"/>
-    <col min="8" max="8" width="10.28515625" style="20" customWidth="1"/>
-    <col min="9" max="16384" width="9.140625" style="20"/>
+    <col min="2" max="2" width="12.109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" style="20"/>
+    <col min="4" max="4" width="10.109375" style="20" customWidth="1"/>
+    <col min="5" max="7" width="9.109375" style="20"/>
+    <col min="8" max="8" width="10.33203125" style="20" customWidth="1"/>
+    <col min="9" max="16384" width="9.109375" style="20"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.6">
+    <row r="1" spans="1:10" ht="26.25" x14ac:dyDescent="0.7">
       <c r="A1" s="28"/>
     </row>
-    <row r="3" spans="1:10" ht="23.45">
+    <row r="3" spans="1:10" ht="37.5" x14ac:dyDescent="0.7">
       <c r="A3" s="29"/>
       <c r="B3" s="29"/>
       <c r="C3" s="29"/>
@@ -7443,32 +7342,32 @@
       <c r="I3" s="29"/>
       <c r="J3" s="29"/>
     </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="169" t="s">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.7">
+      <c r="A4" s="172" t="s">
         <v>315</v>
       </c>
-      <c r="B4" s="169"/>
-      <c r="C4" s="169"/>
-      <c r="D4" s="169"/>
-      <c r="E4" s="169"/>
-      <c r="F4" s="169"/>
-      <c r="G4" s="169"/>
-      <c r="H4" s="169"/>
+      <c r="B4" s="172"/>
+      <c r="C4" s="172"/>
+      <c r="D4" s="172"/>
+      <c r="E4" s="172"/>
+      <c r="F4" s="172"/>
+      <c r="G4" s="172"/>
+      <c r="H4" s="172"/>
       <c r="I4" s="18"/>
     </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="182" t="s">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.7">
+      <c r="A5" s="185" t="s">
         <v>316</v>
       </c>
-      <c r="B5" s="182"/>
-      <c r="C5" s="182"/>
-      <c r="D5" s="182"/>
-      <c r="E5" s="182"/>
-      <c r="F5" s="182"/>
-      <c r="G5" s="182"/>
-      <c r="H5" s="182"/>
-    </row>
-    <row r="6" spans="1:10">
+      <c r="B5" s="185"/>
+      <c r="C5" s="185"/>
+      <c r="D5" s="185"/>
+      <c r="E5" s="185"/>
+      <c r="F5" s="185"/>
+      <c r="G5" s="185"/>
+      <c r="H5" s="185"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.7">
       <c r="A6" s="18"/>
       <c r="B6" s="18"/>
       <c r="C6" s="18"/>
@@ -7479,88 +7378,88 @@
       <c r="H6" s="18"/>
       <c r="I6" s="18"/>
     </row>
-    <row r="7" spans="1:10" ht="47.25" customHeight="1">
-      <c r="A7" s="183" t="s">
+    <row r="7" spans="1:10" ht="47.25" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A7" s="186" t="s">
         <v>317</v>
       </c>
-      <c r="B7" s="183"/>
-      <c r="C7" s="183"/>
-      <c r="D7" s="183"/>
-      <c r="E7" s="183"/>
-      <c r="F7" s="183"/>
-      <c r="G7" s="183"/>
-      <c r="H7" s="183"/>
+      <c r="B7" s="186"/>
+      <c r="C7" s="186"/>
+      <c r="D7" s="186"/>
+      <c r="E7" s="186"/>
+      <c r="F7" s="186"/>
+      <c r="G7" s="186"/>
+      <c r="H7" s="186"/>
       <c r="I7" s="18"/>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.7">
       <c r="A10" s="30" t="s">
         <v>318</v>
       </c>
-      <c r="B10" s="181" t="e">
+      <c r="B10" s="184" t="e">
         <f>Data!FX5</f>
         <v>#REF!</v>
       </c>
-      <c r="C10" s="181"/>
-      <c r="D10" s="181"/>
-    </row>
-    <row r="11" spans="1:10">
+      <c r="C10" s="184"/>
+      <c r="D10" s="184"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.7">
       <c r="A11" s="31" t="s">
         <v>319</v>
       </c>
-      <c r="B11" s="180" t="str">
+      <c r="B11" s="183" t="str">
         <f>Data!B5</f>
-        <v/>
-      </c>
-      <c r="C11" s="180"/>
-      <c r="D11" s="180"/>
-    </row>
-    <row r="12" spans="1:10">
+        <v>Pushkar Singh</v>
+      </c>
+      <c r="C11" s="183"/>
+      <c r="D11" s="183"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.7">
       <c r="A12" s="32"/>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.7">
       <c r="A13" s="30" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
-      <c r="A14" s="180" t="s">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.7">
+      <c r="A14" s="183" t="s">
         <v>321</v>
       </c>
-      <c r="B14" s="180"/>
-      <c r="C14" s="180"/>
-      <c r="D14" s="180"/>
-    </row>
-    <row r="15" spans="1:10">
+      <c r="B14" s="183"/>
+      <c r="C14" s="183"/>
+      <c r="D14" s="183"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.7">
       <c r="A15" s="30" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.7">
       <c r="A16" s="30" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.7">
       <c r="A17" s="30"/>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.7">
       <c r="A18" s="30" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="30.75" customHeight="1">
-      <c r="A20" s="176" t="s">
+    <row r="20" spans="1:10" ht="30.75" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A20" s="179" t="s">
         <v>325</v>
       </c>
-      <c r="B20" s="176"/>
-      <c r="C20" s="176"/>
-      <c r="D20" s="176"/>
-      <c r="E20" s="176"/>
-      <c r="F20" s="176"/>
-      <c r="G20" s="176"/>
-      <c r="H20" s="176"/>
-    </row>
-    <row r="21" spans="1:10" ht="14.45" customHeight="1">
+      <c r="B20" s="179"/>
+      <c r="C20" s="179"/>
+      <c r="D20" s="179"/>
+      <c r="E20" s="179"/>
+      <c r="F20" s="179"/>
+      <c r="G20" s="179"/>
+      <c r="H20" s="179"/>
+    </row>
+    <row r="21" spans="1:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A21" s="18"/>
       <c r="B21" s="18"/>
       <c r="C21" s="18"/>
@@ -7572,21 +7471,21 @@
       <c r="I21" s="18"/>
       <c r="J21" s="18"/>
     </row>
-    <row r="22" spans="1:10" ht="160.5" customHeight="1">
-      <c r="A22" s="179" t="s">
+    <row r="22" spans="1:10" ht="160.5" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A22" s="182" t="s">
         <v>326</v>
       </c>
-      <c r="B22" s="179"/>
-      <c r="C22" s="179"/>
-      <c r="D22" s="179"/>
-      <c r="E22" s="179"/>
-      <c r="F22" s="179"/>
-      <c r="G22" s="179"/>
-      <c r="H22" s="179"/>
+      <c r="B22" s="182"/>
+      <c r="C22" s="182"/>
+      <c r="D22" s="182"/>
+      <c r="E22" s="182"/>
+      <c r="F22" s="182"/>
+      <c r="G22" s="182"/>
+      <c r="H22" s="182"/>
       <c r="I22" s="18"/>
       <c r="J22" s="18"/>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.7">
       <c r="A23" s="18"/>
       <c r="B23" s="18"/>
       <c r="C23" s="18"/>
@@ -7598,7 +7497,7 @@
       <c r="I23" s="18"/>
       <c r="J23" s="18"/>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.7">
       <c r="A24" s="33" t="s">
         <v>327</v>
       </c>
@@ -7612,7 +7511,7 @@
       <c r="I24" s="18"/>
       <c r="J24" s="18"/>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.7">
       <c r="A25" s="18"/>
       <c r="B25" s="18"/>
       <c r="C25" s="18"/>
@@ -7624,7 +7523,7 @@
       <c r="I25" s="18"/>
       <c r="J25" s="18"/>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.7">
       <c r="A26" s="33" t="s">
         <v>328</v>
       </c>
@@ -7638,7 +7537,7 @@
       <c r="I26" s="18"/>
       <c r="J26" s="18"/>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.7">
       <c r="A27" s="18"/>
       <c r="B27" s="18"/>
       <c r="C27" s="18"/>
@@ -7650,16 +7549,16 @@
       <c r="I27" s="18"/>
       <c r="J27" s="18"/>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.7">
       <c r="A28" s="34" t="s">
         <v>329</v>
       </c>
-      <c r="B28" s="177" t="str">
+      <c r="B28" s="180" t="str">
         <f>Data!B5</f>
-        <v/>
-      </c>
-      <c r="C28" s="177"/>
-      <c r="D28" s="177"/>
+        <v>Pushkar Singh</v>
+      </c>
+      <c r="C28" s="180"/>
+      <c r="D28" s="180"/>
       <c r="E28" s="18"/>
       <c r="F28" s="18"/>
       <c r="G28" s="18"/>
@@ -7667,16 +7566,16 @@
       <c r="I28" s="18"/>
       <c r="J28" s="18"/>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.7">
       <c r="A29" s="30" t="s">
         <v>330</v>
       </c>
-      <c r="B29" s="178" t="e">
+      <c r="B29" s="181" t="e">
         <f>Data!A5</f>
         <v>#REF!</v>
       </c>
-      <c r="C29" s="178"/>
-      <c r="D29" s="178"/>
+      <c r="C29" s="181"/>
+      <c r="D29" s="181"/>
       <c r="E29" s="18"/>
       <c r="F29" s="18"/>
       <c r="G29" s="18"/>
@@ -7684,16 +7583,16 @@
       <c r="I29" s="18"/>
       <c r="J29" s="18"/>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.7">
       <c r="A30" s="30" t="s">
         <v>250</v>
       </c>
-      <c r="B30" s="177" t="e">
+      <c r="B30" s="180" t="e">
         <f>Data!FX5</f>
         <v>#REF!</v>
       </c>
-      <c r="C30" s="177"/>
-      <c r="D30" s="177"/>
+      <c r="C30" s="180"/>
+      <c r="D30" s="180"/>
       <c r="E30" s="18"/>
       <c r="F30" s="18"/>
       <c r="G30" s="18"/>
@@ -7701,16 +7600,16 @@
       <c r="I30" s="18"/>
       <c r="J30" s="18"/>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.7">
       <c r="A31" s="30" t="s">
         <v>331</v>
       </c>
-      <c r="B31" s="177" t="e">
+      <c r="B31" s="180" t="e">
         <f>Data!FZ5</f>
         <v>#REF!</v>
       </c>
-      <c r="C31" s="177"/>
-      <c r="D31" s="177"/>
+      <c r="C31" s="180"/>
+      <c r="D31" s="180"/>
       <c r="E31" s="18"/>
       <c r="F31" s="18"/>
       <c r="G31" s="18"/>
@@ -7718,7 +7617,7 @@
       <c r="I31" s="18"/>
       <c r="J31" s="18"/>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.7">
       <c r="A32" s="18"/>
       <c r="B32" s="18"/>
       <c r="C32" s="18"/>
@@ -7751,108 +7650,108 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A4:J53"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="25.5" x14ac:dyDescent="0.7"/>
   <cols>
-    <col min="1" max="1" width="14.85546875" style="20" customWidth="1"/>
-    <col min="2" max="2" width="15.28515625" style="20" customWidth="1"/>
-    <col min="3" max="3" width="15.5703125" style="20" customWidth="1"/>
-    <col min="4" max="4" width="17.5703125" style="20" customWidth="1"/>
-    <col min="5" max="5" width="13.28515625" style="20" customWidth="1"/>
-    <col min="6" max="6" width="15.140625" style="20" customWidth="1"/>
-    <col min="7" max="9" width="9.140625" style="20"/>
-    <col min="10" max="10" width="8.28515625" style="20" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="20"/>
+    <col min="1" max="1" width="14.88671875" style="20" customWidth="1"/>
+    <col min="2" max="2" width="15.33203125" style="20" customWidth="1"/>
+    <col min="3" max="3" width="15.5546875" style="20" customWidth="1"/>
+    <col min="4" max="4" width="17.5546875" style="20" customWidth="1"/>
+    <col min="5" max="5" width="13.33203125" style="20" customWidth="1"/>
+    <col min="6" max="6" width="15.109375" style="20" customWidth="1"/>
+    <col min="7" max="9" width="9.109375" style="20"/>
+    <col min="10" max="10" width="8.33203125" style="20" customWidth="1"/>
+    <col min="11" max="16384" width="9.109375" style="20"/>
   </cols>
   <sheetData>
-    <row r="4" spans="1:10">
-      <c r="A4" s="184" t="s">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.7">
+      <c r="A4" s="187" t="s">
         <v>332</v>
       </c>
-      <c r="B4" s="184"/>
-      <c r="C4" s="184"/>
-      <c r="D4" s="184"/>
-      <c r="E4" s="184"/>
-      <c r="F4" s="184"/>
-    </row>
-    <row r="6" spans="1:10" ht="14.45" customHeight="1">
-      <c r="A6" s="183" t="s">
+      <c r="B4" s="187"/>
+      <c r="C4" s="187"/>
+      <c r="D4" s="187"/>
+      <c r="E4" s="187"/>
+      <c r="F4" s="187"/>
+    </row>
+    <row r="6" spans="1:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A6" s="186" t="s">
         <v>333</v>
       </c>
-      <c r="B6" s="183"/>
-      <c r="C6" s="183"/>
-      <c r="D6" s="183"/>
-      <c r="E6" s="183"/>
-      <c r="F6" s="183"/>
+      <c r="B6" s="186"/>
+      <c r="C6" s="186"/>
+      <c r="D6" s="186"/>
+      <c r="E6" s="186"/>
+      <c r="F6" s="186"/>
       <c r="G6" s="33"/>
       <c r="H6" s="18"/>
       <c r="I6" s="18"/>
       <c r="J6" s="18"/>
     </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="183"/>
-      <c r="B7" s="183"/>
-      <c r="C7" s="183"/>
-      <c r="D7" s="183"/>
-      <c r="E7" s="183"/>
-      <c r="F7" s="183"/>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.7">
+      <c r="A7" s="186"/>
+      <c r="B7" s="186"/>
+      <c r="C7" s="186"/>
+      <c r="D7" s="186"/>
+      <c r="E7" s="186"/>
+      <c r="F7" s="186"/>
       <c r="G7" s="33"/>
       <c r="H7" s="18"/>
       <c r="I7" s="18"/>
       <c r="J7" s="18"/>
     </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="183"/>
-      <c r="B8" s="183"/>
-      <c r="C8" s="183"/>
-      <c r="D8" s="183"/>
-      <c r="E8" s="183"/>
-      <c r="F8" s="183"/>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.7">
+      <c r="A8" s="186"/>
+      <c r="B8" s="186"/>
+      <c r="C8" s="186"/>
+      <c r="D8" s="186"/>
+      <c r="E8" s="186"/>
+      <c r="F8" s="186"/>
       <c r="G8" s="33"/>
       <c r="H8" s="18"/>
       <c r="I8" s="18"/>
       <c r="J8" s="18"/>
     </row>
-    <row r="9" spans="1:10">
-      <c r="A9" s="183"/>
-      <c r="B9" s="183"/>
-      <c r="C9" s="183"/>
-      <c r="D9" s="183"/>
-      <c r="E9" s="183"/>
-      <c r="F9" s="183"/>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.7">
+      <c r="A9" s="186"/>
+      <c r="B9" s="186"/>
+      <c r="C9" s="186"/>
+      <c r="D9" s="186"/>
+      <c r="E9" s="186"/>
+      <c r="F9" s="186"/>
       <c r="G9" s="33"/>
       <c r="H9" s="18"/>
       <c r="I9" s="18"/>
       <c r="J9" s="18"/>
     </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="183"/>
-      <c r="B10" s="183"/>
-      <c r="C10" s="183"/>
-      <c r="D10" s="183"/>
-      <c r="E10" s="183"/>
-      <c r="F10" s="183"/>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.7">
+      <c r="A10" s="186"/>
+      <c r="B10" s="186"/>
+      <c r="C10" s="186"/>
+      <c r="D10" s="186"/>
+      <c r="E10" s="186"/>
+      <c r="F10" s="186"/>
       <c r="G10" s="33"/>
       <c r="H10" s="18"/>
       <c r="I10" s="18"/>
       <c r="J10" s="18"/>
     </row>
-    <row r="11" spans="1:10" ht="37.5" customHeight="1">
-      <c r="A11" s="183"/>
-      <c r="B11" s="183"/>
-      <c r="C11" s="183"/>
-      <c r="D11" s="183"/>
-      <c r="E11" s="183"/>
-      <c r="F11" s="183"/>
+    <row r="11" spans="1:10" ht="37.5" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A11" s="186"/>
+      <c r="B11" s="186"/>
+      <c r="C11" s="186"/>
+      <c r="D11" s="186"/>
+      <c r="E11" s="186"/>
+      <c r="F11" s="186"/>
       <c r="G11" s="33"/>
       <c r="H11" s="18"/>
       <c r="I11" s="18"/>
       <c r="J11" s="18"/>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.7">
       <c r="A12" s="33"/>
       <c r="B12" s="33"/>
       <c r="C12" s="33"/>
@@ -7864,21 +7763,21 @@
       <c r="I12" s="18"/>
       <c r="J12" s="18"/>
     </row>
-    <row r="13" spans="1:10">
-      <c r="A13" s="183" t="s">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.7">
+      <c r="A13" s="186" t="s">
         <v>334</v>
       </c>
-      <c r="B13" s="183"/>
-      <c r="C13" s="183"/>
-      <c r="D13" s="183"/>
-      <c r="E13" s="183"/>
-      <c r="F13" s="183"/>
-      <c r="G13" s="183"/>
+      <c r="B13" s="186"/>
+      <c r="C13" s="186"/>
+      <c r="D13" s="186"/>
+      <c r="E13" s="186"/>
+      <c r="F13" s="186"/>
+      <c r="G13" s="186"/>
       <c r="H13" s="18"/>
       <c r="I13" s="18"/>
       <c r="J13" s="18"/>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.7">
       <c r="A14" s="18"/>
       <c r="B14" s="18"/>
       <c r="C14" s="18"/>
@@ -7890,7 +7789,7 @@
       <c r="I14" s="18"/>
       <c r="J14" s="18"/>
     </row>
-    <row r="15" spans="1:10" ht="33.75" customHeight="1">
+    <row r="15" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A15" s="35" t="s">
         <v>24</v>
       </c>
@@ -7900,222 +7799,222 @@
       <c r="C15" s="35" t="s">
         <v>335</v>
       </c>
-      <c r="D15" s="188" t="s">
+      <c r="D15" s="191" t="s">
         <v>336</v>
       </c>
-      <c r="E15" s="188"/>
+      <c r="E15" s="191"/>
       <c r="F15" s="35" t="s">
         <v>28</v>
       </c>
       <c r="H15" s="36"/>
       <c r="J15" s="36"/>
     </row>
-    <row r="16" spans="1:10">
-      <c r="A16" s="83" t="str">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.7">
+      <c r="A16" s="81" t="str">
         <f>Data!AB5</f>
         <v/>
       </c>
-      <c r="B16" s="83" t="str">
+      <c r="B16" s="81" t="str">
         <f>Data!AC5</f>
         <v/>
       </c>
-      <c r="C16" s="83" t="str">
+      <c r="C16" s="81" t="str">
         <f>Data!AD5</f>
         <v/>
       </c>
-      <c r="D16" s="189" t="str">
+      <c r="D16" s="192" t="str">
         <f>Data!AE5</f>
         <v/>
       </c>
-      <c r="E16" s="189"/>
-      <c r="F16" s="83" t="str">
+      <c r="E16" s="192"/>
+      <c r="F16" s="81" t="str">
         <f>Data!AF5</f>
         <v/>
       </c>
       <c r="H16" s="36"/>
       <c r="J16" s="36"/>
     </row>
-    <row r="17" spans="1:10">
-      <c r="A17" s="84" t="str">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.7">
+      <c r="A17" s="82" t="str">
         <f>Data!AG5</f>
         <v/>
       </c>
-      <c r="B17" s="84" t="str">
+      <c r="B17" s="82" t="str">
         <f>Data!AH5</f>
         <v/>
       </c>
-      <c r="C17" s="84" t="str">
+      <c r="C17" s="82" t="str">
         <f>Data!AI5</f>
         <v/>
       </c>
-      <c r="D17" s="189" t="str">
+      <c r="D17" s="192" t="str">
         <f>Data!AJ5</f>
         <v/>
       </c>
-      <c r="E17" s="189"/>
-      <c r="F17" s="84" t="str">
+      <c r="E17" s="192"/>
+      <c r="F17" s="82" t="str">
         <f>Data!AK5</f>
         <v/>
       </c>
       <c r="H17" s="37"/>
       <c r="J17" s="37"/>
     </row>
-    <row r="18" spans="1:10">
-      <c r="A18" s="84" t="str">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.7">
+      <c r="A18" s="82" t="str">
         <f>Data!AL5</f>
         <v/>
       </c>
-      <c r="B18" s="84" t="str">
+      <c r="B18" s="82" t="str">
         <f>Data!AM5</f>
         <v/>
       </c>
-      <c r="C18" s="84" t="str">
+      <c r="C18" s="82" t="str">
         <f>Data!AN5</f>
         <v/>
       </c>
-      <c r="D18" s="189" t="str">
+      <c r="D18" s="192" t="str">
         <f>Data!AO5</f>
         <v/>
       </c>
-      <c r="E18" s="189"/>
-      <c r="F18" s="84" t="str">
+      <c r="E18" s="192"/>
+      <c r="F18" s="82" t="str">
         <f>Data!AP5</f>
         <v/>
       </c>
       <c r="H18" s="37"/>
       <c r="J18" s="37"/>
     </row>
-    <row r="19" spans="1:10">
-      <c r="A19" s="84" t="str">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.7">
+      <c r="A19" s="82" t="str">
         <f>Data!AQ5</f>
         <v/>
       </c>
-      <c r="B19" s="84" t="str">
+      <c r="B19" s="82" t="str">
         <f>Data!AR5</f>
         <v/>
       </c>
-      <c r="C19" s="84" t="str">
+      <c r="C19" s="82" t="str">
         <f>Data!AS5</f>
         <v/>
       </c>
-      <c r="D19" s="189" t="str">
+      <c r="D19" s="192" t="str">
         <f>Data!AT5</f>
         <v/>
       </c>
-      <c r="E19" s="189"/>
-      <c r="F19" s="84" t="str">
+      <c r="E19" s="192"/>
+      <c r="F19" s="82" t="str">
         <f>Data!AU5</f>
         <v/>
       </c>
       <c r="H19" s="37"/>
       <c r="J19" s="37"/>
     </row>
-    <row r="20" spans="1:10">
-      <c r="A20" s="84" t="str">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.7">
+      <c r="A20" s="82" t="str">
         <f>Data!AV5</f>
         <v/>
       </c>
-      <c r="B20" s="84" t="str">
+      <c r="B20" s="82" t="str">
         <f>Data!AW5</f>
         <v/>
       </c>
-      <c r="C20" s="84" t="str">
+      <c r="C20" s="82" t="str">
         <f>Data!AX5</f>
         <v/>
       </c>
-      <c r="D20" s="189" t="str">
+      <c r="D20" s="192" t="str">
         <f>Data!AY5</f>
         <v/>
       </c>
-      <c r="E20" s="189"/>
-      <c r="F20" s="84" t="str">
+      <c r="E20" s="192"/>
+      <c r="F20" s="82" t="str">
         <f>Data!AZ5</f>
         <v/>
       </c>
       <c r="H20" s="37"/>
       <c r="J20" s="37"/>
     </row>
-    <row r="22" spans="1:10" ht="18.75" customHeight="1">
-      <c r="A22" s="187" t="s">
+    <row r="22" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A22" s="190" t="s">
         <v>337</v>
       </c>
-      <c r="B22" s="187"/>
-      <c r="C22" s="174" t="str">
+      <c r="B22" s="190"/>
+      <c r="C22" s="177" t="str">
         <f>UPPER( Data!B5)</f>
-        <v/>
-      </c>
-      <c r="D22" s="174"/>
-      <c r="E22" s="174"/>
-      <c r="F22" s="174"/>
-    </row>
-    <row r="23" spans="1:10" ht="19.5" customHeight="1">
+        <v>PUSHKAR SINGH</v>
+      </c>
+      <c r="D22" s="177"/>
+      <c r="E22" s="177"/>
+      <c r="F22" s="177"/>
+    </row>
+    <row r="23" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A23" s="38" t="s">
         <v>338</v>
       </c>
-      <c r="B23" s="82" t="e">
+      <c r="B23" s="80" t="e">
         <f>Data!A5</f>
         <v>#REF!</v>
       </c>
       <c r="C23" s="25" t="s">
         <v>339</v>
       </c>
-      <c r="D23" s="190"/>
-      <c r="E23" s="190"/>
-      <c r="F23" s="190"/>
-    </row>
-    <row r="24" spans="1:10" ht="19.5" customHeight="1">
+      <c r="D23" s="193"/>
+      <c r="E23" s="193"/>
+      <c r="F23" s="193"/>
+    </row>
+    <row r="24" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A24" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="B24" s="90" t="str">
+      <c r="B24" s="88" t="str">
         <f>Data!D5</f>
-        <v/>
+        <v>23/04/1994</v>
       </c>
       <c r="C24" s="38" t="s">
         <v>13</v>
       </c>
-      <c r="D24" s="154" t="str">
+      <c r="D24" s="157" t="str">
         <f>Data!E5</f>
-        <v/>
-      </c>
-      <c r="E24" s="154"/>
-      <c r="F24" s="154"/>
-    </row>
-    <row r="25" spans="1:10">
+        <v>A+</v>
+      </c>
+      <c r="E24" s="157"/>
+      <c r="F24" s="157"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.7">
       <c r="A25" s="38" t="s">
         <v>340</v>
       </c>
-      <c r="B25" s="90" t="e">
+      <c r="B25" s="88" t="e">
         <f>Data!EZ5</f>
         <v>#REF!</v>
       </c>
       <c r="C25" s="38"/>
-      <c r="D25" s="154"/>
-      <c r="E25" s="154"/>
-      <c r="F25" s="154"/>
-    </row>
-    <row r="26" spans="1:10">
-      <c r="A26" s="165" t="s">
+      <c r="D25" s="157"/>
+      <c r="E25" s="157"/>
+      <c r="F25" s="157"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.7">
+      <c r="A26" s="168" t="s">
         <v>341</v>
       </c>
-      <c r="B26" s="165"/>
-      <c r="C26" s="165"/>
-      <c r="D26" s="174" t="str">
+      <c r="B26" s="168"/>
+      <c r="C26" s="168"/>
+      <c r="D26" s="177" t="str">
         <f>Data!F5</f>
         <v/>
       </c>
-      <c r="E26" s="174"/>
-      <c r="F26" s="174"/>
-    </row>
-    <row r="28" spans="1:10" ht="33" customHeight="1">
-      <c r="C28" s="191" t="s">
+      <c r="E26" s="177"/>
+      <c r="F26" s="177"/>
+    </row>
+    <row r="28" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="C28" s="194" t="s">
         <v>342</v>
       </c>
-      <c r="D28" s="191"/>
-      <c r="E28" s="192"/>
-      <c r="F28" s="193"/>
-    </row>
-    <row r="30" spans="1:10">
+      <c r="D28" s="194"/>
+      <c r="E28" s="195"/>
+      <c r="F28" s="196"/>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.7">
       <c r="E30" s="39"/>
       <c r="F30" s="39"/>
       <c r="G30" s="39"/>
@@ -8123,223 +8022,223 @@
       <c r="I30" s="39"/>
       <c r="J30" s="39"/>
     </row>
-    <row r="31" spans="1:10" ht="15.6">
+    <row r="31" spans="1:10" ht="26.25" x14ac:dyDescent="0.7">
       <c r="A31" s="40" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.7">
       <c r="A32" s="20" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="30.75" customHeight="1">
-      <c r="C34" s="100"/>
-      <c r="D34" s="95" t="s">
+    <row r="34" spans="1:10" ht="30.75" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="C34" s="98"/>
+      <c r="D34" s="93" t="s">
         <v>345</v>
       </c>
-      <c r="E34" s="186"/>
-      <c r="F34" s="186"/>
-    </row>
-    <row r="37" spans="1:10" ht="15.6">
-      <c r="A37" s="185" t="s">
+      <c r="E34" s="189"/>
+      <c r="F34" s="189"/>
+    </row>
+    <row r="37" spans="1:10" ht="26.25" x14ac:dyDescent="0.7">
+      <c r="A37" s="188" t="s">
         <v>346</v>
       </c>
-      <c r="B37" s="185"/>
-      <c r="C37" s="185"/>
-      <c r="D37" s="185"/>
-      <c r="E37" s="185"/>
-      <c r="F37" s="185"/>
-    </row>
-    <row r="38" spans="1:10" ht="18.75" customHeight="1">
-      <c r="A38" s="183" t="s">
+      <c r="B37" s="188"/>
+      <c r="C37" s="188"/>
+      <c r="D37" s="188"/>
+      <c r="E37" s="188"/>
+      <c r="F37" s="188"/>
+    </row>
+    <row r="38" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A38" s="186" t="s">
         <v>347</v>
       </c>
-      <c r="B38" s="183"/>
-      <c r="C38" s="183"/>
-      <c r="D38" s="183"/>
-      <c r="E38" s="183"/>
-      <c r="F38" s="183"/>
+      <c r="B38" s="186"/>
+      <c r="C38" s="186"/>
+      <c r="D38" s="186"/>
+      <c r="E38" s="186"/>
+      <c r="F38" s="186"/>
       <c r="G38" s="18"/>
       <c r="H38" s="18"/>
       <c r="I38" s="18"/>
       <c r="J38" s="18"/>
     </row>
-    <row r="39" spans="1:10">
-      <c r="A39" s="183"/>
-      <c r="B39" s="183"/>
-      <c r="C39" s="183"/>
-      <c r="D39" s="183"/>
-      <c r="E39" s="183"/>
-      <c r="F39" s="183"/>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.7">
+      <c r="A39" s="186"/>
+      <c r="B39" s="186"/>
+      <c r="C39" s="186"/>
+      <c r="D39" s="186"/>
+      <c r="E39" s="186"/>
+      <c r="F39" s="186"/>
       <c r="G39" s="18"/>
       <c r="H39" s="18"/>
       <c r="I39" s="18"/>
       <c r="J39" s="18"/>
     </row>
-    <row r="40" spans="1:10">
-      <c r="A40" s="183"/>
-      <c r="B40" s="183"/>
-      <c r="C40" s="183"/>
-      <c r="D40" s="183"/>
-      <c r="E40" s="183"/>
-      <c r="F40" s="183"/>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.7">
+      <c r="A40" s="186"/>
+      <c r="B40" s="186"/>
+      <c r="C40" s="186"/>
+      <c r="D40" s="186"/>
+      <c r="E40" s="186"/>
+      <c r="F40" s="186"/>
       <c r="G40" s="18"/>
       <c r="H40" s="18"/>
       <c r="I40" s="18"/>
       <c r="J40" s="18"/>
     </row>
-    <row r="41" spans="1:10">
-      <c r="A41" s="183"/>
-      <c r="B41" s="183"/>
-      <c r="C41" s="183"/>
-      <c r="D41" s="183"/>
-      <c r="E41" s="183"/>
-      <c r="F41" s="183"/>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.7">
+      <c r="A41" s="186"/>
+      <c r="B41" s="186"/>
+      <c r="C41" s="186"/>
+      <c r="D41" s="186"/>
+      <c r="E41" s="186"/>
+      <c r="F41" s="186"/>
       <c r="G41" s="18"/>
       <c r="H41" s="18"/>
       <c r="I41" s="18"/>
       <c r="J41" s="18"/>
     </row>
-    <row r="42" spans="1:10">
-      <c r="A42" s="183"/>
-      <c r="B42" s="183"/>
-      <c r="C42" s="183"/>
-      <c r="D42" s="183"/>
-      <c r="E42" s="183"/>
-      <c r="F42" s="183"/>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.7">
+      <c r="A42" s="186"/>
+      <c r="B42" s="186"/>
+      <c r="C42" s="186"/>
+      <c r="D42" s="186"/>
+      <c r="E42" s="186"/>
+      <c r="F42" s="186"/>
       <c r="G42" s="18"/>
       <c r="H42" s="18"/>
       <c r="I42" s="18"/>
       <c r="J42" s="18"/>
     </row>
-    <row r="43" spans="1:10">
-      <c r="A43" s="183"/>
-      <c r="B43" s="183"/>
-      <c r="C43" s="183"/>
-      <c r="D43" s="183"/>
-      <c r="E43" s="183"/>
-      <c r="F43" s="183"/>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.7">
+      <c r="A43" s="186"/>
+      <c r="B43" s="186"/>
+      <c r="C43" s="186"/>
+      <c r="D43" s="186"/>
+      <c r="E43" s="186"/>
+      <c r="F43" s="186"/>
       <c r="G43" s="18"/>
       <c r="H43" s="18"/>
       <c r="I43" s="18"/>
       <c r="J43" s="18"/>
     </row>
-    <row r="44" spans="1:10">
-      <c r="A44" s="183"/>
-      <c r="B44" s="183"/>
-      <c r="C44" s="183"/>
-      <c r="D44" s="183"/>
-      <c r="E44" s="183"/>
-      <c r="F44" s="183"/>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.7">
+      <c r="A44" s="186"/>
+      <c r="B44" s="186"/>
+      <c r="C44" s="186"/>
+      <c r="D44" s="186"/>
+      <c r="E44" s="186"/>
+      <c r="F44" s="186"/>
       <c r="G44" s="18"/>
       <c r="H44" s="18"/>
       <c r="I44" s="18"/>
       <c r="J44" s="18"/>
     </row>
-    <row r="45" spans="1:10">
-      <c r="A45" s="183"/>
-      <c r="B45" s="183"/>
-      <c r="C45" s="183"/>
-      <c r="D45" s="183"/>
-      <c r="E45" s="183"/>
-      <c r="F45" s="183"/>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.7">
+      <c r="A45" s="186"/>
+      <c r="B45" s="186"/>
+      <c r="C45" s="186"/>
+      <c r="D45" s="186"/>
+      <c r="E45" s="186"/>
+      <c r="F45" s="186"/>
       <c r="G45" s="18"/>
       <c r="H45" s="18"/>
       <c r="I45" s="18"/>
       <c r="J45" s="18"/>
     </row>
-    <row r="46" spans="1:10">
-      <c r="A46" s="183"/>
-      <c r="B46" s="183"/>
-      <c r="C46" s="183"/>
-      <c r="D46" s="183"/>
-      <c r="E46" s="183"/>
-      <c r="F46" s="183"/>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.7">
+      <c r="A46" s="186"/>
+      <c r="B46" s="186"/>
+      <c r="C46" s="186"/>
+      <c r="D46" s="186"/>
+      <c r="E46" s="186"/>
+      <c r="F46" s="186"/>
       <c r="G46" s="18"/>
       <c r="H46" s="18"/>
       <c r="I46" s="18"/>
       <c r="J46" s="18"/>
     </row>
-    <row r="47" spans="1:10">
-      <c r="A47" s="183"/>
-      <c r="B47" s="183"/>
-      <c r="C47" s="183"/>
-      <c r="D47" s="183"/>
-      <c r="E47" s="183"/>
-      <c r="F47" s="183"/>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.7">
+      <c r="A47" s="186"/>
+      <c r="B47" s="186"/>
+      <c r="C47" s="186"/>
+      <c r="D47" s="186"/>
+      <c r="E47" s="186"/>
+      <c r="F47" s="186"/>
       <c r="G47" s="18"/>
       <c r="H47" s="18"/>
       <c r="I47" s="18"/>
       <c r="J47" s="18"/>
     </row>
-    <row r="48" spans="1:10">
-      <c r="A48" s="183"/>
-      <c r="B48" s="183"/>
-      <c r="C48" s="183"/>
-      <c r="D48" s="183"/>
-      <c r="E48" s="183"/>
-      <c r="F48" s="183"/>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.7">
+      <c r="A48" s="186"/>
+      <c r="B48" s="186"/>
+      <c r="C48" s="186"/>
+      <c r="D48" s="186"/>
+      <c r="E48" s="186"/>
+      <c r="F48" s="186"/>
       <c r="G48" s="18"/>
       <c r="H48" s="18"/>
       <c r="I48" s="18"/>
       <c r="J48" s="18"/>
     </row>
-    <row r="49" spans="1:10">
-      <c r="A49" s="183"/>
-      <c r="B49" s="183"/>
-      <c r="C49" s="183"/>
-      <c r="D49" s="183"/>
-      <c r="E49" s="183"/>
-      <c r="F49" s="183"/>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.7">
+      <c r="A49" s="186"/>
+      <c r="B49" s="186"/>
+      <c r="C49" s="186"/>
+      <c r="D49" s="186"/>
+      <c r="E49" s="186"/>
+      <c r="F49" s="186"/>
       <c r="G49" s="18"/>
       <c r="H49" s="18"/>
       <c r="I49" s="18"/>
       <c r="J49" s="18"/>
     </row>
-    <row r="50" spans="1:10">
-      <c r="A50" s="183"/>
-      <c r="B50" s="183"/>
-      <c r="C50" s="183"/>
-      <c r="D50" s="183"/>
-      <c r="E50" s="183"/>
-      <c r="F50" s="183"/>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.7">
+      <c r="A50" s="186"/>
+      <c r="B50" s="186"/>
+      <c r="C50" s="186"/>
+      <c r="D50" s="186"/>
+      <c r="E50" s="186"/>
+      <c r="F50" s="186"/>
       <c r="G50" s="18"/>
       <c r="H50" s="18"/>
       <c r="I50" s="18"/>
       <c r="J50" s="18"/>
     </row>
-    <row r="51" spans="1:10">
-      <c r="A51" s="183"/>
-      <c r="B51" s="183"/>
-      <c r="C51" s="183"/>
-      <c r="D51" s="183"/>
-      <c r="E51" s="183"/>
-      <c r="F51" s="183"/>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.7">
+      <c r="A51" s="186"/>
+      <c r="B51" s="186"/>
+      <c r="C51" s="186"/>
+      <c r="D51" s="186"/>
+      <c r="E51" s="186"/>
+      <c r="F51" s="186"/>
       <c r="G51" s="18"/>
       <c r="H51" s="18"/>
       <c r="I51" s="18"/>
       <c r="J51" s="18"/>
     </row>
-    <row r="52" spans="1:10">
-      <c r="A52" s="183"/>
-      <c r="B52" s="183"/>
-      <c r="C52" s="183"/>
-      <c r="D52" s="183"/>
-      <c r="E52" s="183"/>
-      <c r="F52" s="183"/>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.7">
+      <c r="A52" s="186"/>
+      <c r="B52" s="186"/>
+      <c r="C52" s="186"/>
+      <c r="D52" s="186"/>
+      <c r="E52" s="186"/>
+      <c r="F52" s="186"/>
       <c r="G52" s="18"/>
       <c r="H52" s="18"/>
       <c r="I52" s="18"/>
       <c r="J52" s="18"/>
     </row>
-    <row r="53" spans="1:10" ht="29.25" customHeight="1">
-      <c r="A53" s="183"/>
-      <c r="B53" s="183"/>
-      <c r="C53" s="183"/>
-      <c r="D53" s="183"/>
-      <c r="E53" s="183"/>
-      <c r="F53" s="183"/>
+    <row r="53" spans="1:10" ht="29.25" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A53" s="186"/>
+      <c r="B53" s="186"/>
+      <c r="C53" s="186"/>
+      <c r="D53" s="186"/>
+      <c r="E53" s="186"/>
+      <c r="F53" s="186"/>
       <c r="G53" s="18"/>
       <c r="H53" s="18"/>
       <c r="I53" s="18"/>
@@ -8375,75 +8274,75 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr codeName="Sheet7"/>
   <dimension ref="A4:J85"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="25.5" x14ac:dyDescent="0.7"/>
   <cols>
-    <col min="1" max="1" width="10.85546875" style="20" customWidth="1"/>
+    <col min="1" max="1" width="10.88671875" style="20" customWidth="1"/>
     <col min="2" max="4" width="8" style="20" customWidth="1"/>
     <col min="5" max="5" width="15" style="20" customWidth="1"/>
-    <col min="6" max="6" width="11.42578125" style="20" customWidth="1"/>
+    <col min="6" max="6" width="11.44140625" style="20" customWidth="1"/>
     <col min="7" max="7" width="9" style="20" customWidth="1"/>
-    <col min="8" max="8" width="7.42578125" style="20" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="20" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.44140625" style="20" customWidth="1"/>
+    <col min="9" max="9" width="13.5546875" style="20" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9" style="20" customWidth="1"/>
-    <col min="11" max="16384" width="8.7109375" style="20"/>
+    <col min="11" max="16384" width="8.6640625" style="20"/>
   </cols>
   <sheetData>
-    <row r="4" spans="1:10">
-      <c r="A4" s="182" t="s">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.7">
+      <c r="A4" s="185" t="s">
         <v>348</v>
       </c>
-      <c r="B4" s="182"/>
-      <c r="C4" s="182"/>
-      <c r="D4" s="182"/>
-      <c r="E4" s="182"/>
-      <c r="F4" s="182"/>
-      <c r="G4" s="182"/>
-      <c r="H4" s="182"/>
-      <c r="I4" s="182"/>
-    </row>
-    <row r="6" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A6" s="219" t="s">
+      <c r="B4" s="185"/>
+      <c r="C4" s="185"/>
+      <c r="D4" s="185"/>
+      <c r="E4" s="185"/>
+      <c r="F4" s="185"/>
+      <c r="G4" s="185"/>
+      <c r="H4" s="185"/>
+      <c r="I4" s="185"/>
+    </row>
+    <row r="6" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A6" s="222" t="s">
         <v>349</v>
       </c>
-      <c r="B6" s="219"/>
-      <c r="C6" s="219"/>
-      <c r="D6" s="219"/>
-      <c r="E6" s="219"/>
-      <c r="F6" s="219"/>
-      <c r="G6" s="219"/>
-      <c r="H6" s="219"/>
-      <c r="I6" s="219"/>
+      <c r="B6" s="222"/>
+      <c r="C6" s="222"/>
+      <c r="D6" s="222"/>
+      <c r="E6" s="222"/>
+      <c r="F6" s="222"/>
+      <c r="G6" s="222"/>
+      <c r="H6" s="222"/>
+      <c r="I6" s="222"/>
       <c r="J6" s="18"/>
     </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="219"/>
-      <c r="B7" s="219"/>
-      <c r="C7" s="219"/>
-      <c r="D7" s="219"/>
-      <c r="E7" s="219"/>
-      <c r="F7" s="219"/>
-      <c r="G7" s="219"/>
-      <c r="H7" s="219"/>
-      <c r="I7" s="219"/>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.7">
+      <c r="A7" s="222"/>
+      <c r="B7" s="222"/>
+      <c r="C7" s="222"/>
+      <c r="D7" s="222"/>
+      <c r="E7" s="222"/>
+      <c r="F7" s="222"/>
+      <c r="G7" s="222"/>
+      <c r="H7" s="222"/>
+      <c r="I7" s="222"/>
       <c r="J7" s="18"/>
     </row>
-    <row r="8" spans="1:10" ht="37.5" customHeight="1">
-      <c r="A8" s="219"/>
-      <c r="B8" s="219"/>
-      <c r="C8" s="219"/>
-      <c r="D8" s="219"/>
-      <c r="E8" s="219"/>
-      <c r="F8" s="219"/>
-      <c r="G8" s="219"/>
-      <c r="H8" s="219"/>
-      <c r="I8" s="219"/>
+    <row r="8" spans="1:10" ht="37.5" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A8" s="222"/>
+      <c r="B8" s="222"/>
+      <c r="C8" s="222"/>
+      <c r="D8" s="222"/>
+      <c r="E8" s="222"/>
+      <c r="F8" s="222"/>
+      <c r="G8" s="222"/>
+      <c r="H8" s="222"/>
+      <c r="I8" s="222"/>
       <c r="J8" s="18"/>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.7">
       <c r="A9" s="18"/>
       <c r="B9" s="18"/>
       <c r="C9" s="18"/>
@@ -8455,12 +8354,12 @@
       <c r="I9" s="18"/>
       <c r="J9" s="18"/>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.7">
       <c r="A10" s="20" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.7">
       <c r="A11" s="18" t="s">
         <v>350</v>
       </c>
@@ -8474,7 +8373,7 @@
       <c r="I11" s="18"/>
       <c r="J11" s="18"/>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.7">
       <c r="A12" s="18"/>
       <c r="B12" s="18"/>
       <c r="C12" s="18"/>
@@ -8486,7 +8385,7 @@
       <c r="I12" s="18"/>
       <c r="J12" s="18"/>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.7">
       <c r="A13" s="18" t="s">
         <v>351</v>
       </c>
@@ -8500,11 +8399,11 @@
       <c r="I13" s="18"/>
       <c r="J13" s="18"/>
     </row>
-    <row r="14" spans="1:10">
-      <c r="A14" s="177" t="s">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.7">
+      <c r="A14" s="180" t="s">
         <v>352</v>
       </c>
-      <c r="B14" s="177"/>
+      <c r="B14" s="180"/>
       <c r="C14" s="18"/>
       <c r="D14" s="18"/>
       <c r="E14" s="18"/>
@@ -8514,7 +8413,7 @@
       <c r="I14" s="18"/>
       <c r="J14" s="18"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.7">
       <c r="A15" s="18"/>
       <c r="B15" s="18"/>
       <c r="C15" s="18"/>
@@ -8526,135 +8425,135 @@
       <c r="I15" s="18"/>
       <c r="J15" s="18"/>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.7">
       <c r="A16" s="18" t="s">
         <v>353</v>
       </c>
-      <c r="B16" s="177" t="str">
+      <c r="B16" s="180" t="str">
         <f>Data!B5</f>
-        <v/>
-      </c>
-      <c r="C16" s="177"/>
-      <c r="D16" s="177"/>
-      <c r="E16" s="177"/>
-      <c r="F16" s="177"/>
-      <c r="G16" s="177"/>
-      <c r="H16" s="177"/>
+        <v>Pushkar Singh</v>
+      </c>
+      <c r="C16" s="180"/>
+      <c r="D16" s="180"/>
+      <c r="E16" s="180"/>
+      <c r="F16" s="180"/>
+      <c r="G16" s="180"/>
+      <c r="H16" s="180"/>
       <c r="I16" s="18"/>
       <c r="J16" s="18"/>
     </row>
-    <row r="17" spans="1:10" ht="83.25" customHeight="1">
-      <c r="A17" s="176" t="s">
+    <row r="17" spans="1:10" ht="83.25" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A17" s="179" t="s">
         <v>354</v>
       </c>
-      <c r="B17" s="177"/>
-      <c r="C17" s="177"/>
-      <c r="D17" s="177"/>
-      <c r="E17" s="177"/>
-      <c r="F17" s="177"/>
-      <c r="G17" s="177"/>
-      <c r="H17" s="177"/>
-      <c r="I17" s="177"/>
-    </row>
-    <row r="18" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A18" s="183" t="s">
+      <c r="B17" s="180"/>
+      <c r="C17" s="180"/>
+      <c r="D17" s="180"/>
+      <c r="E17" s="180"/>
+      <c r="F17" s="180"/>
+      <c r="G17" s="180"/>
+      <c r="H17" s="180"/>
+      <c r="I17" s="180"/>
+    </row>
+    <row r="18" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A18" s="186" t="s">
         <v>355</v>
       </c>
-      <c r="B18" s="183"/>
-      <c r="C18" s="183"/>
-      <c r="D18" s="183"/>
-      <c r="E18" s="183"/>
-      <c r="F18" s="183"/>
-      <c r="G18" s="183"/>
-      <c r="H18" s="183"/>
-      <c r="I18" s="183"/>
-    </row>
-    <row r="19" spans="1:10" ht="21" customHeight="1">
-      <c r="A19" s="183"/>
-      <c r="B19" s="183"/>
-      <c r="C19" s="183"/>
-      <c r="D19" s="183"/>
-      <c r="E19" s="183"/>
-      <c r="F19" s="183"/>
-      <c r="G19" s="183"/>
-      <c r="H19" s="183"/>
-      <c r="I19" s="183"/>
-    </row>
-    <row r="20" spans="1:10">
-      <c r="A20" s="220" t="s">
+      <c r="B18" s="186"/>
+      <c r="C18" s="186"/>
+      <c r="D18" s="186"/>
+      <c r="E18" s="186"/>
+      <c r="F18" s="186"/>
+      <c r="G18" s="186"/>
+      <c r="H18" s="186"/>
+      <c r="I18" s="186"/>
+    </row>
+    <row r="19" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A19" s="186"/>
+      <c r="B19" s="186"/>
+      <c r="C19" s="186"/>
+      <c r="D19" s="186"/>
+      <c r="E19" s="186"/>
+      <c r="F19" s="186"/>
+      <c r="G19" s="186"/>
+      <c r="H19" s="186"/>
+      <c r="I19" s="186"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.7">
+      <c r="A20" s="223" t="s">
         <v>356</v>
       </c>
-      <c r="B20" s="220"/>
-      <c r="C20" s="220"/>
-      <c r="D20" s="220"/>
-      <c r="E20" s="220"/>
-      <c r="F20" s="220"/>
-      <c r="G20" s="220"/>
-      <c r="H20" s="220"/>
-      <c r="I20" s="220"/>
+      <c r="B20" s="223"/>
+      <c r="C20" s="223"/>
+      <c r="D20" s="223"/>
+      <c r="E20" s="223"/>
+      <c r="F20" s="223"/>
+      <c r="G20" s="223"/>
+      <c r="H20" s="223"/>
+      <c r="I20" s="223"/>
       <c r="J20" s="18"/>
     </row>
-    <row r="21" spans="1:10">
-      <c r="A21" s="220" t="s">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.7">
+      <c r="A21" s="223" t="s">
         <v>357</v>
       </c>
-      <c r="B21" s="220"/>
-      <c r="C21" s="220"/>
-      <c r="D21" s="220"/>
-      <c r="E21" s="220"/>
-      <c r="F21" s="220"/>
-      <c r="G21" s="220"/>
-      <c r="H21" s="220"/>
-      <c r="I21" s="220"/>
+      <c r="B21" s="223"/>
+      <c r="C21" s="223"/>
+      <c r="D21" s="223"/>
+      <c r="E21" s="223"/>
+      <c r="F21" s="223"/>
+      <c r="G21" s="223"/>
+      <c r="H21" s="223"/>
+      <c r="I21" s="223"/>
       <c r="J21" s="18"/>
     </row>
-    <row r="22" spans="1:10">
-      <c r="A22" s="220" t="s">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.7">
+      <c r="A22" s="223" t="s">
         <v>358</v>
       </c>
-      <c r="B22" s="220"/>
-      <c r="C22" s="220"/>
-      <c r="D22" s="220"/>
-      <c r="E22" s="220"/>
-      <c r="F22" s="220"/>
-      <c r="G22" s="220"/>
-      <c r="H22" s="220"/>
-      <c r="I22" s="220"/>
+      <c r="B22" s="223"/>
+      <c r="C22" s="223"/>
+      <c r="D22" s="223"/>
+      <c r="E22" s="223"/>
+      <c r="F22" s="223"/>
+      <c r="G22" s="223"/>
+      <c r="H22" s="223"/>
+      <c r="I22" s="223"/>
       <c r="J22" s="18"/>
     </row>
-    <row r="23" spans="1:10" ht="30.75" customHeight="1">
-      <c r="A23" s="220" t="s">
+    <row r="23" spans="1:10" ht="30.75" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A23" s="223" t="s">
         <v>359</v>
       </c>
-      <c r="B23" s="220"/>
-      <c r="C23" s="220"/>
-      <c r="D23" s="220"/>
-      <c r="E23" s="220"/>
-      <c r="F23" s="220"/>
-      <c r="G23" s="220"/>
-      <c r="H23" s="220"/>
-      <c r="I23" s="220"/>
+      <c r="B23" s="223"/>
+      <c r="C23" s="223"/>
+      <c r="D23" s="223"/>
+      <c r="E23" s="223"/>
+      <c r="F23" s="223"/>
+      <c r="G23" s="223"/>
+      <c r="H23" s="223"/>
+      <c r="I23" s="223"/>
       <c r="J23" s="18"/>
     </row>
-    <row r="24" spans="1:10" ht="15" customHeight="1">
-      <c r="A24" s="220" t="s">
+    <row r="24" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A24" s="223" t="s">
         <v>360</v>
       </c>
-      <c r="B24" s="220"/>
-      <c r="C24" s="220"/>
-      <c r="D24" s="220"/>
-      <c r="E24" s="220"/>
-      <c r="F24" s="220"/>
-      <c r="G24" s="220"/>
-      <c r="H24" s="220"/>
-      <c r="I24" s="220"/>
+      <c r="B24" s="223"/>
+      <c r="C24" s="223"/>
+      <c r="D24" s="223"/>
+      <c r="E24" s="223"/>
+      <c r="F24" s="223"/>
+      <c r="G24" s="223"/>
+      <c r="H24" s="223"/>
+      <c r="I24" s="223"/>
       <c r="J24" s="18"/>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.7">
       <c r="I25" s="18"/>
       <c r="J25" s="18"/>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.7">
       <c r="A26" s="18"/>
       <c r="B26" s="18"/>
       <c r="C26" s="18"/>
@@ -8666,233 +8565,233 @@
       <c r="I26" s="18"/>
       <c r="J26" s="18"/>
     </row>
-    <row r="27" spans="1:10" ht="15">
-      <c r="A27" s="199" t="s">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.7">
+      <c r="A27" s="202" t="s">
         <v>361</v>
       </c>
-      <c r="B27" s="199"/>
-      <c r="C27" s="199"/>
-      <c r="D27" s="199"/>
-      <c r="E27" s="199"/>
-      <c r="F27" s="199"/>
-      <c r="G27" s="199"/>
-      <c r="H27" s="199"/>
-      <c r="I27" s="199"/>
+      <c r="B27" s="202"/>
+      <c r="C27" s="202"/>
+      <c r="D27" s="202"/>
+      <c r="E27" s="202"/>
+      <c r="F27" s="202"/>
+      <c r="G27" s="202"/>
+      <c r="H27" s="202"/>
+      <c r="I27" s="202"/>
       <c r="J27" s="18"/>
     </row>
-    <row r="28" spans="1:10">
-      <c r="A28" s="108"/>
-      <c r="B28" s="108"/>
-      <c r="C28" s="108"/>
-      <c r="D28" s="108"/>
-      <c r="E28" s="108"/>
-      <c r="F28" s="108"/>
-      <c r="G28" s="108"/>
-      <c r="H28" s="108"/>
-      <c r="I28" s="108"/>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.7">
+      <c r="A28" s="106"/>
+      <c r="B28" s="106"/>
+      <c r="C28" s="106"/>
+      <c r="D28" s="106"/>
+      <c r="E28" s="106"/>
+      <c r="F28" s="106"/>
+      <c r="G28" s="106"/>
+      <c r="H28" s="106"/>
+      <c r="I28" s="106"/>
       <c r="J28" s="18"/>
     </row>
-    <row r="29" spans="1:10" ht="76.5" customHeight="1">
-      <c r="A29" s="204" t="s">
+    <row r="29" spans="1:10" ht="76.5" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A29" s="207" t="s">
         <v>362</v>
       </c>
-      <c r="B29" s="204"/>
-      <c r="C29" s="204"/>
-      <c r="D29" s="204" t="s">
+      <c r="B29" s="207"/>
+      <c r="C29" s="207"/>
+      <c r="D29" s="207" t="s">
         <v>363</v>
       </c>
-      <c r="E29" s="204"/>
-      <c r="F29" s="83" t="s">
+      <c r="E29" s="207"/>
+      <c r="F29" s="81" t="s">
         <v>364</v>
       </c>
-      <c r="G29" s="204" t="s">
+      <c r="G29" s="207" t="s">
         <v>365</v>
       </c>
-      <c r="H29" s="204"/>
-      <c r="I29" s="204"/>
+      <c r="H29" s="207"/>
+      <c r="I29" s="207"/>
       <c r="J29" s="18"/>
     </row>
-    <row r="30" spans="1:10" ht="80.45" customHeight="1">
-      <c r="A30" s="201" t="e">
+    <row r="30" spans="1:10" ht="80.45" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A30" s="204" t="e">
         <f>CONCATENATE( Data!BA5, " ",Data!BB5, " ", Data!BE5)</f>
         <v>#REF!</v>
       </c>
-      <c r="B30" s="202"/>
-      <c r="C30" s="203"/>
-      <c r="D30" s="210" t="e">
+      <c r="B30" s="205"/>
+      <c r="C30" s="206"/>
+      <c r="D30" s="213" t="e">
         <f>Data!BC5</f>
         <v>#REF!</v>
       </c>
-      <c r="E30" s="211"/>
-      <c r="F30" s="84" t="e">
+      <c r="E30" s="214"/>
+      <c r="F30" s="82" t="e">
         <f>Data!BD5</f>
         <v>#REF!</v>
       </c>
-      <c r="G30" s="222" t="e">
+      <c r="G30" s="225" t="e">
         <f>Data!BF5</f>
         <v>#REF!</v>
       </c>
-      <c r="H30" s="222"/>
-      <c r="I30" s="222"/>
+      <c r="H30" s="225"/>
+      <c r="I30" s="225"/>
       <c r="J30" s="18"/>
     </row>
-    <row r="31" spans="1:10" ht="80.45" customHeight="1">
-      <c r="A31" s="201" t="e">
+    <row r="31" spans="1:10" ht="80.45" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A31" s="204" t="e">
         <f>CONCATENATE( Data!BG5, " ",Data!BH5, " ", Data!BK5)</f>
         <v>#REF!</v>
       </c>
-      <c r="B31" s="202"/>
-      <c r="C31" s="203"/>
-      <c r="D31" s="210" t="e">
+      <c r="B31" s="205"/>
+      <c r="C31" s="206"/>
+      <c r="D31" s="213" t="e">
         <f>Data!BI5</f>
         <v>#REF!</v>
       </c>
-      <c r="E31" s="211"/>
-      <c r="F31" s="84" t="e">
+      <c r="E31" s="214"/>
+      <c r="F31" s="82" t="e">
         <f>Data!BJ5</f>
         <v>#REF!</v>
       </c>
-      <c r="G31" s="222" t="e">
+      <c r="G31" s="225" t="e">
         <f>Data!BL5</f>
         <v>#REF!</v>
       </c>
-      <c r="H31" s="222"/>
-      <c r="I31" s="222"/>
+      <c r="H31" s="225"/>
+      <c r="I31" s="225"/>
       <c r="J31" s="18"/>
     </row>
-    <row r="32" spans="1:10" ht="80.45" customHeight="1">
-      <c r="A32" s="201" t="e">
+    <row r="32" spans="1:10" ht="80.45" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A32" s="204" t="e">
         <f>CONCATENATE( Data!BM5, " ",Data!BN5, " ", Data!BQ5)</f>
         <v>#REF!</v>
       </c>
-      <c r="B32" s="202"/>
-      <c r="C32" s="203"/>
-      <c r="D32" s="210" t="e">
+      <c r="B32" s="205"/>
+      <c r="C32" s="206"/>
+      <c r="D32" s="213" t="e">
         <f>Data!BO5</f>
         <v>#REF!</v>
       </c>
-      <c r="E32" s="211"/>
-      <c r="F32" s="84" t="e">
+      <c r="E32" s="214"/>
+      <c r="F32" s="82" t="e">
         <f>Data!BP5</f>
         <v>#REF!</v>
       </c>
-      <c r="G32" s="222" t="e">
+      <c r="G32" s="225" t="e">
         <f>Data!BR5</f>
         <v>#REF!</v>
       </c>
-      <c r="H32" s="222"/>
-      <c r="I32" s="222"/>
+      <c r="H32" s="225"/>
+      <c r="I32" s="225"/>
       <c r="J32" s="18"/>
     </row>
-    <row r="33" spans="1:10" ht="80.45" customHeight="1">
-      <c r="A33" s="201" t="e">
+    <row r="33" spans="1:10" ht="80.45" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A33" s="204" t="e">
         <f>CONCATENATE( Data!BS5, " ",Data!BT5, " ", Data!BW5)</f>
         <v>#REF!</v>
       </c>
-      <c r="B33" s="202"/>
-      <c r="C33" s="203"/>
-      <c r="D33" s="210" t="e">
+      <c r="B33" s="205"/>
+      <c r="C33" s="206"/>
+      <c r="D33" s="213" t="e">
         <f>Data!BU5</f>
         <v>#REF!</v>
       </c>
-      <c r="E33" s="211"/>
-      <c r="F33" s="84" t="e">
+      <c r="E33" s="214"/>
+      <c r="F33" s="82" t="e">
         <f>Data!BV5</f>
         <v>#REF!</v>
       </c>
-      <c r="G33" s="222" t="e">
+      <c r="G33" s="225" t="e">
         <f>Data!BX5</f>
         <v>#REF!</v>
       </c>
-      <c r="H33" s="222"/>
-      <c r="I33" s="222"/>
+      <c r="H33" s="225"/>
+      <c r="I33" s="225"/>
       <c r="J33" s="18"/>
     </row>
-    <row r="34" spans="1:10" ht="80.45" customHeight="1">
-      <c r="A34" s="205" t="e">
+    <row r="34" spans="1:10" ht="80.45" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A34" s="208" t="e">
         <f>CONCATENATE( Data!BY5, " ",Data!BZ5, " ", Data!CC5)</f>
         <v>#REF!</v>
       </c>
-      <c r="B34" s="206"/>
-      <c r="C34" s="207"/>
-      <c r="D34" s="208" t="e">
+      <c r="B34" s="209"/>
+      <c r="C34" s="210"/>
+      <c r="D34" s="211" t="e">
         <f>Data!CA5</f>
         <v>#REF!</v>
       </c>
-      <c r="E34" s="209"/>
-      <c r="F34" s="82" t="e">
+      <c r="E34" s="212"/>
+      <c r="F34" s="80" t="e">
         <f>Data!CB5</f>
         <v>#REF!</v>
       </c>
-      <c r="G34" s="222" t="e">
+      <c r="G34" s="225" t="e">
         <f>Data!CD5</f>
         <v>#REF!</v>
       </c>
-      <c r="H34" s="222"/>
-      <c r="I34" s="222"/>
-      <c r="J34" s="74"/>
-    </row>
-    <row r="35" spans="1:10">
-      <c r="A35" s="102"/>
-      <c r="B35" s="102"/>
-      <c r="C35" s="102"/>
-      <c r="D35" s="103"/>
-      <c r="E35" s="103"/>
-      <c r="F35" s="104"/>
-      <c r="G35" s="101"/>
-      <c r="H35" s="101"/>
-      <c r="I35" s="101"/>
-      <c r="J35" s="74"/>
-    </row>
-    <row r="36" spans="1:10">
-      <c r="A36" s="102"/>
-      <c r="B36" s="102"/>
-      <c r="C36" s="102"/>
-      <c r="D36" s="103"/>
-      <c r="E36" s="103"/>
-      <c r="F36" s="104"/>
-      <c r="G36" s="101"/>
-      <c r="H36" s="101"/>
-      <c r="I36" s="101"/>
-      <c r="J36" s="74"/>
-    </row>
-    <row r="37" spans="1:10">
-      <c r="A37" s="102"/>
-      <c r="B37" s="102"/>
-      <c r="C37" s="102"/>
-      <c r="D37" s="103"/>
-      <c r="E37" s="103"/>
-      <c r="F37" s="104"/>
-      <c r="G37" s="101"/>
-      <c r="H37" s="101"/>
-      <c r="I37" s="101"/>
-      <c r="J37" s="74"/>
-    </row>
-    <row r="38" spans="1:10">
-      <c r="A38" s="102"/>
-      <c r="B38" s="102"/>
-      <c r="C38" s="102"/>
-      <c r="D38" s="103"/>
-      <c r="E38" s="103"/>
-      <c r="F38" s="104"/>
-      <c r="G38" s="101"/>
-      <c r="H38" s="101"/>
-      <c r="I38" s="101"/>
-      <c r="J38" s="74"/>
-    </row>
-    <row r="39" spans="1:10">
-      <c r="A39" s="102"/>
-      <c r="B39" s="102"/>
-      <c r="C39" s="102"/>
-      <c r="D39" s="103"/>
-      <c r="E39" s="103"/>
-      <c r="F39" s="104"/>
-      <c r="G39" s="101"/>
-      <c r="H39" s="101"/>
-      <c r="I39" s="101"/>
-      <c r="J39" s="74"/>
-    </row>
-    <row r="40" spans="1:10">
+      <c r="H34" s="225"/>
+      <c r="I34" s="225"/>
+      <c r="J34" s="72"/>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.7">
+      <c r="A35" s="100"/>
+      <c r="B35" s="100"/>
+      <c r="C35" s="100"/>
+      <c r="D35" s="101"/>
+      <c r="E35" s="101"/>
+      <c r="F35" s="102"/>
+      <c r="G35" s="99"/>
+      <c r="H35" s="99"/>
+      <c r="I35" s="99"/>
+      <c r="J35" s="72"/>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.7">
+      <c r="A36" s="100"/>
+      <c r="B36" s="100"/>
+      <c r="C36" s="100"/>
+      <c r="D36" s="101"/>
+      <c r="E36" s="101"/>
+      <c r="F36" s="102"/>
+      <c r="G36" s="99"/>
+      <c r="H36" s="99"/>
+      <c r="I36" s="99"/>
+      <c r="J36" s="72"/>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.7">
+      <c r="A37" s="100"/>
+      <c r="B37" s="100"/>
+      <c r="C37" s="100"/>
+      <c r="D37" s="101"/>
+      <c r="E37" s="101"/>
+      <c r="F37" s="102"/>
+      <c r="G37" s="99"/>
+      <c r="H37" s="99"/>
+      <c r="I37" s="99"/>
+      <c r="J37" s="72"/>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.7">
+      <c r="A38" s="100"/>
+      <c r="B38" s="100"/>
+      <c r="C38" s="100"/>
+      <c r="D38" s="101"/>
+      <c r="E38" s="101"/>
+      <c r="F38" s="102"/>
+      <c r="G38" s="99"/>
+      <c r="H38" s="99"/>
+      <c r="I38" s="99"/>
+      <c r="J38" s="72"/>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.7">
+      <c r="A39" s="100"/>
+      <c r="B39" s="100"/>
+      <c r="C39" s="100"/>
+      <c r="D39" s="101"/>
+      <c r="E39" s="101"/>
+      <c r="F39" s="102"/>
+      <c r="G39" s="99"/>
+      <c r="H39" s="99"/>
+      <c r="I39" s="99"/>
+      <c r="J39" s="72"/>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.7">
       <c r="A40" s="18"/>
       <c r="B40" s="18"/>
       <c r="C40" s="18"/>
@@ -8901,416 +8800,416 @@
       <c r="F40" s="18"/>
       <c r="G40" s="18"/>
       <c r="H40" s="18"/>
-      <c r="I40" s="87"/>
-      <c r="J40" s="87"/>
-    </row>
-    <row r="41" spans="1:10" ht="15">
-      <c r="A41" s="199" t="s">
+      <c r="I40" s="85"/>
+      <c r="J40" s="85"/>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.7">
+      <c r="A41" s="202" t="s">
         <v>366</v>
       </c>
-      <c r="B41" s="199"/>
-      <c r="C41" s="199"/>
-      <c r="D41" s="199"/>
-      <c r="E41" s="199"/>
-      <c r="F41" s="199"/>
-      <c r="G41" s="199"/>
-      <c r="H41" s="199"/>
-      <c r="I41" s="199"/>
-      <c r="J41" s="88"/>
-    </row>
-    <row r="42" spans="1:10">
-      <c r="A42" s="107"/>
-      <c r="B42" s="107"/>
-      <c r="C42" s="107"/>
-      <c r="D42" s="107"/>
-      <c r="E42" s="107"/>
-      <c r="F42" s="107"/>
-      <c r="G42" s="107"/>
-      <c r="H42" s="107"/>
-      <c r="I42" s="107"/>
-      <c r="J42" s="88"/>
-    </row>
-    <row r="43" spans="1:10" ht="15" customHeight="1">
-      <c r="A43" s="178" t="s">
+      <c r="B41" s="202"/>
+      <c r="C41" s="202"/>
+      <c r="D41" s="202"/>
+      <c r="E41" s="202"/>
+      <c r="F41" s="202"/>
+      <c r="G41" s="202"/>
+      <c r="H41" s="202"/>
+      <c r="I41" s="202"/>
+      <c r="J41" s="86"/>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.7">
+      <c r="A42" s="105"/>
+      <c r="B42" s="105"/>
+      <c r="C42" s="105"/>
+      <c r="D42" s="105"/>
+      <c r="E42" s="105"/>
+      <c r="F42" s="105"/>
+      <c r="G42" s="105"/>
+      <c r="H42" s="105"/>
+      <c r="I42" s="105"/>
+      <c r="J42" s="86"/>
+    </row>
+    <row r="43" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A43" s="181" t="s">
         <v>367</v>
       </c>
-      <c r="B43" s="178"/>
-      <c r="C43" s="178"/>
-      <c r="D43" s="178"/>
-      <c r="E43" s="178"/>
-      <c r="F43" s="178" t="str">
+      <c r="B43" s="181"/>
+      <c r="C43" s="181"/>
+      <c r="D43" s="181"/>
+      <c r="E43" s="181"/>
+      <c r="F43" s="181" t="str">
         <f>Data!B5</f>
-        <v/>
-      </c>
-      <c r="G43" s="178"/>
-      <c r="H43" s="178"/>
-      <c r="I43" s="88"/>
-      <c r="J43" s="88"/>
-    </row>
-    <row r="44" spans="1:10">
-      <c r="A44" s="178" t="s">
+        <v>Pushkar Singh</v>
+      </c>
+      <c r="G43" s="181"/>
+      <c r="H43" s="181"/>
+      <c r="I43" s="86"/>
+      <c r="J43" s="86"/>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.7">
+      <c r="A44" s="181" t="s">
         <v>368</v>
       </c>
-      <c r="B44" s="178"/>
-      <c r="C44" s="178"/>
-      <c r="D44" s="178"/>
-      <c r="E44" s="178"/>
-      <c r="F44" s="178" t="str">
+      <c r="B44" s="181"/>
+      <c r="C44" s="181"/>
+      <c r="D44" s="181"/>
+      <c r="E44" s="181"/>
+      <c r="F44" s="181" t="str">
         <f>Data!C5</f>
-        <v/>
-      </c>
-      <c r="G44" s="178"/>
-      <c r="H44" s="178"/>
-      <c r="I44" s="88"/>
-      <c r="J44" s="88"/>
-    </row>
-    <row r="45" spans="1:10">
-      <c r="A45" s="178" t="s">
+        <v>Male</v>
+      </c>
+      <c r="G44" s="181"/>
+      <c r="H44" s="181"/>
+      <c r="I44" s="86"/>
+      <c r="J44" s="86"/>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.7">
+      <c r="A45" s="181" t="s">
         <v>369</v>
       </c>
-      <c r="B45" s="178"/>
-      <c r="C45" s="178"/>
-      <c r="D45" s="178"/>
-      <c r="E45" s="178"/>
-      <c r="F45" s="178" t="str">
+      <c r="B45" s="181"/>
+      <c r="C45" s="181"/>
+      <c r="D45" s="181"/>
+      <c r="E45" s="181"/>
+      <c r="F45" s="181" t="str">
         <f>Data!I5</f>
-        <v/>
-      </c>
-      <c r="G45" s="178"/>
-      <c r="H45" s="178"/>
-      <c r="I45" s="88"/>
-      <c r="J45" s="88"/>
-    </row>
-    <row r="46" spans="1:10">
-      <c r="A46" s="178" t="s">
+        <v>Hindu</v>
+      </c>
+      <c r="G45" s="181"/>
+      <c r="H45" s="181"/>
+      <c r="I45" s="86"/>
+      <c r="J45" s="86"/>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.7">
+      <c r="A46" s="181" t="s">
         <v>370</v>
       </c>
-      <c r="B46" s="178"/>
-      <c r="C46" s="178"/>
-      <c r="D46" s="178"/>
-      <c r="E46" s="178"/>
-      <c r="F46" s="178" t="e">
+      <c r="B46" s="181"/>
+      <c r="C46" s="181"/>
+      <c r="D46" s="181"/>
+      <c r="E46" s="181"/>
+      <c r="F46" s="181" t="e">
         <f>Data!EW5</f>
         <v>#REF!</v>
       </c>
-      <c r="G46" s="178"/>
-      <c r="H46" s="178"/>
-      <c r="I46" s="88"/>
-      <c r="J46" s="88"/>
-    </row>
-    <row r="47" spans="1:10">
-      <c r="A47" s="178" t="s">
+      <c r="G46" s="181"/>
+      <c r="H46" s="181"/>
+      <c r="I46" s="86"/>
+      <c r="J46" s="86"/>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.7">
+      <c r="A47" s="181" t="s">
         <v>371</v>
       </c>
-      <c r="B47" s="178"/>
-      <c r="C47" s="178"/>
-      <c r="D47" s="178"/>
-      <c r="E47" s="178"/>
-      <c r="F47" s="221"/>
-      <c r="G47" s="221"/>
-      <c r="H47" s="221"/>
-      <c r="I47" s="88"/>
-      <c r="J47" s="88"/>
-    </row>
-    <row r="48" spans="1:10" ht="15" customHeight="1">
-      <c r="A48" s="178" t="s">
+      <c r="B47" s="181"/>
+      <c r="C47" s="181"/>
+      <c r="D47" s="181"/>
+      <c r="E47" s="181"/>
+      <c r="F47" s="224"/>
+      <c r="G47" s="224"/>
+      <c r="H47" s="224"/>
+      <c r="I47" s="86"/>
+      <c r="J47" s="86"/>
+    </row>
+    <row r="48" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A48" s="181" t="s">
         <v>372</v>
       </c>
-      <c r="B48" s="178"/>
-      <c r="C48" s="178"/>
-      <c r="D48" s="178"/>
-      <c r="E48" s="178"/>
-      <c r="F48" s="221"/>
-      <c r="G48" s="221"/>
-      <c r="H48" s="221"/>
-      <c r="I48" s="88"/>
-      <c r="J48" s="88"/>
-    </row>
-    <row r="49" spans="1:10" ht="15" customHeight="1">
-      <c r="A49" s="178" t="s">
+      <c r="B48" s="181"/>
+      <c r="C48" s="181"/>
+      <c r="D48" s="181"/>
+      <c r="E48" s="181"/>
+      <c r="F48" s="224"/>
+      <c r="G48" s="224"/>
+      <c r="H48" s="224"/>
+      <c r="I48" s="86"/>
+      <c r="J48" s="86"/>
+    </row>
+    <row r="49" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A49" s="181" t="s">
         <v>373</v>
       </c>
-      <c r="B49" s="178"/>
-      <c r="C49" s="178"/>
-      <c r="D49" s="178"/>
-      <c r="E49" s="178"/>
-      <c r="F49" s="200" t="e">
+      <c r="B49" s="181"/>
+      <c r="C49" s="181"/>
+      <c r="D49" s="181"/>
+      <c r="E49" s="181"/>
+      <c r="F49" s="203" t="e">
         <f>Data!FX5</f>
         <v>#REF!</v>
       </c>
-      <c r="G49" s="178"/>
-      <c r="H49" s="178"/>
-      <c r="I49" s="88"/>
-      <c r="J49" s="88"/>
-    </row>
-    <row r="50" spans="1:10" ht="15" customHeight="1">
-      <c r="A50" s="178" t="s">
+      <c r="G49" s="181"/>
+      <c r="H49" s="181"/>
+      <c r="I49" s="86"/>
+      <c r="J49" s="86"/>
+    </row>
+    <row r="50" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A50" s="181" t="s">
         <v>374</v>
       </c>
-      <c r="B50" s="178"/>
-      <c r="C50" s="178"/>
-      <c r="D50" s="178"/>
-      <c r="E50" s="178"/>
-      <c r="F50" s="178" t="str">
+      <c r="B50" s="181"/>
+      <c r="C50" s="181"/>
+      <c r="D50" s="181"/>
+      <c r="E50" s="181"/>
+      <c r="F50" s="181" t="str">
         <f>Data!O5</f>
-        <v/>
-      </c>
-      <c r="G50" s="178"/>
-      <c r="H50" s="178"/>
-      <c r="I50" s="88"/>
-      <c r="J50" s="88"/>
-    </row>
-    <row r="51" spans="1:10">
-      <c r="A51" s="88" t="s">
+        <v>159-160,1st floor, Pocket-7, Sector-24 Rohini</v>
+      </c>
+      <c r="G50" s="181"/>
+      <c r="H50" s="181"/>
+      <c r="I50" s="86"/>
+      <c r="J50" s="86"/>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.7">
+      <c r="A51" s="86" t="s">
         <v>375</v>
       </c>
-      <c r="B51" s="178"/>
-      <c r="C51" s="178"/>
-      <c r="D51" s="88" t="s">
+      <c r="B51" s="181"/>
+      <c r="C51" s="181"/>
+      <c r="D51" s="86" t="s">
         <v>376</v>
       </c>
-      <c r="E51" s="88"/>
-      <c r="F51" s="88" t="s">
+      <c r="E51" s="86"/>
+      <c r="F51" s="86" t="s">
         <v>377</v>
       </c>
-      <c r="G51" s="178"/>
-      <c r="H51" s="178"/>
-      <c r="I51" s="88"/>
-      <c r="J51" s="88"/>
-    </row>
-    <row r="52" spans="1:10">
+      <c r="G51" s="181"/>
+      <c r="H51" s="181"/>
+      <c r="I51" s="86"/>
+      <c r="J51" s="86"/>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.7">
       <c r="A52" s="22" t="s">
         <v>378</v>
       </c>
-      <c r="B52" s="178"/>
-      <c r="C52" s="178"/>
+      <c r="B52" s="181"/>
+      <c r="C52" s="181"/>
       <c r="D52" s="20" t="s">
         <v>379</v>
       </c>
       <c r="F52" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="G52" s="178"/>
-      <c r="H52" s="178"/>
-    </row>
-    <row r="53" spans="1:10">
-      <c r="B53" s="98"/>
-      <c r="C53" s="98"/>
-      <c r="G53" s="98"/>
-      <c r="H53" s="98"/>
-    </row>
-    <row r="54" spans="1:10">
+      <c r="G52" s="181"/>
+      <c r="H52" s="181"/>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.7">
+      <c r="B53" s="96"/>
+      <c r="C53" s="96"/>
+      <c r="G53" s="96"/>
+      <c r="H53" s="96"/>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.7">
       <c r="A54" s="21"/>
     </row>
-    <row r="55" spans="1:10">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.7">
       <c r="A55" s="20" t="s">
         <v>380</v>
       </c>
-      <c r="B55" s="178" t="e">
+      <c r="B55" s="181" t="e">
         <f>Data!FZ5</f>
         <v>#REF!</v>
       </c>
-      <c r="C55" s="178"/>
-    </row>
-    <row r="56" spans="1:10">
+      <c r="C55" s="181"/>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.7">
       <c r="A56" s="24" t="s">
         <v>250</v>
       </c>
-      <c r="B56" s="200" t="e">
+      <c r="B56" s="203" t="e">
         <f>Data!FX5</f>
         <v>#REF!</v>
       </c>
-      <c r="C56" s="178"/>
-    </row>
-    <row r="58" spans="1:10">
+      <c r="C56" s="181"/>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.7">
       <c r="A58" s="24"/>
-      <c r="F58" s="196" t="s">
+      <c r="F58" s="199" t="s">
         <v>342</v>
       </c>
-      <c r="G58" s="197"/>
-      <c r="H58" s="198"/>
-      <c r="I58" s="198"/>
-    </row>
-    <row r="59" spans="1:10">
-      <c r="F59" s="196"/>
-      <c r="G59" s="197"/>
-      <c r="H59" s="198"/>
-      <c r="I59" s="198"/>
-    </row>
-    <row r="60" spans="1:10">
+      <c r="G58" s="200"/>
+      <c r="H58" s="201"/>
+      <c r="I58" s="201"/>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.7">
+      <c r="F59" s="199"/>
+      <c r="G59" s="200"/>
+      <c r="H59" s="201"/>
+      <c r="I59" s="201"/>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.7">
       <c r="A60" s="24"/>
-      <c r="F60" s="100"/>
-      <c r="G60" s="100"/>
-      <c r="H60" s="100"/>
-    </row>
-    <row r="61" spans="1:10">
-      <c r="A61" s="194" t="s">
+      <c r="F60" s="98"/>
+      <c r="G60" s="98"/>
+      <c r="H60" s="98"/>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.7">
+      <c r="A61" s="197" t="s">
         <v>381</v>
       </c>
-      <c r="B61" s="195"/>
-      <c r="C61" s="195"/>
-      <c r="D61" s="195"/>
-      <c r="E61" s="195"/>
-      <c r="F61" s="195"/>
-      <c r="G61" s="195"/>
-      <c r="H61" s="195"/>
-      <c r="I61" s="195"/>
-    </row>
-    <row r="63" spans="1:10" ht="15">
-      <c r="A63" s="199" t="s">
+      <c r="B61" s="198"/>
+      <c r="C61" s="198"/>
+      <c r="D61" s="198"/>
+      <c r="E61" s="198"/>
+      <c r="F61" s="198"/>
+      <c r="G61" s="198"/>
+      <c r="H61" s="198"/>
+      <c r="I61" s="198"/>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.7">
+      <c r="A63" s="202" t="s">
         <v>382</v>
       </c>
-      <c r="B63" s="199"/>
-      <c r="C63" s="199"/>
-      <c r="D63" s="199"/>
-      <c r="E63" s="199"/>
-      <c r="F63" s="199"/>
-      <c r="G63" s="199"/>
-      <c r="H63" s="199"/>
-      <c r="I63" s="199"/>
-    </row>
-    <row r="65" spans="1:9">
-      <c r="A65" s="177" t="s">
+      <c r="B63" s="202"/>
+      <c r="C63" s="202"/>
+      <c r="D63" s="202"/>
+      <c r="E63" s="202"/>
+      <c r="F63" s="202"/>
+      <c r="G63" s="202"/>
+      <c r="H63" s="202"/>
+      <c r="I63" s="202"/>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.7">
+      <c r="A65" s="180" t="s">
         <v>383</v>
       </c>
-      <c r="B65" s="177"/>
-      <c r="C65" s="177"/>
-      <c r="D65" s="177"/>
-      <c r="E65" s="177"/>
-      <c r="F65" s="177"/>
-      <c r="G65" s="177"/>
-      <c r="H65" s="177"/>
-    </row>
-    <row r="66" spans="1:9">
-      <c r="A66" s="177"/>
-      <c r="B66" s="177"/>
-      <c r="C66" s="177"/>
-      <c r="D66" s="177"/>
-      <c r="E66" s="177"/>
-      <c r="F66" s="177"/>
-      <c r="G66" s="177"/>
-      <c r="H66" s="177"/>
-    </row>
-    <row r="68" spans="1:9">
-      <c r="A68" s="151" t="s">
+      <c r="B65" s="180"/>
+      <c r="C65" s="180"/>
+      <c r="D65" s="180"/>
+      <c r="E65" s="180"/>
+      <c r="F65" s="180"/>
+      <c r="G65" s="180"/>
+      <c r="H65" s="180"/>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.7">
+      <c r="A66" s="180"/>
+      <c r="B66" s="180"/>
+      <c r="C66" s="180"/>
+      <c r="D66" s="180"/>
+      <c r="E66" s="180"/>
+      <c r="F66" s="180"/>
+      <c r="G66" s="180"/>
+      <c r="H66" s="180"/>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.7">
+      <c r="A68" s="154" t="s">
         <v>384</v>
       </c>
-      <c r="B68" s="151"/>
-      <c r="C68" s="151"/>
-      <c r="D68" s="151"/>
+      <c r="B68" s="154"/>
+      <c r="C68" s="154"/>
+      <c r="D68" s="154"/>
       <c r="F68" s="24"/>
     </row>
-    <row r="69" spans="1:9">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.7">
       <c r="A69" s="24" t="s">
         <v>250</v>
       </c>
-      <c r="B69" s="178"/>
-      <c r="C69" s="178"/>
-    </row>
-    <row r="70" spans="1:9">
+      <c r="B69" s="181"/>
+      <c r="C69" s="181"/>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.7">
       <c r="F70" s="24"/>
     </row>
-    <row r="71" spans="1:9">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.7">
       <c r="F71" s="24"/>
-      <c r="G71" s="213"/>
-      <c r="H71" s="214"/>
-      <c r="I71" s="215"/>
-    </row>
-    <row r="72" spans="1:9">
+      <c r="G71" s="216"/>
+      <c r="H71" s="217"/>
+      <c r="I71" s="218"/>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.7">
       <c r="F72" s="24"/>
-      <c r="G72" s="216"/>
-      <c r="H72" s="217"/>
-      <c r="I72" s="218"/>
-    </row>
-    <row r="73" spans="1:9" ht="32.25" customHeight="1">
-      <c r="F73" s="212" t="s">
+      <c r="G72" s="219"/>
+      <c r="H72" s="220"/>
+      <c r="I72" s="221"/>
+    </row>
+    <row r="73" spans="1:9" ht="32.25" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="F73" s="215" t="s">
         <v>385</v>
       </c>
-      <c r="G73" s="212"/>
-      <c r="H73" s="212"/>
-      <c r="I73" s="212"/>
-    </row>
-    <row r="74" spans="1:9">
+      <c r="G73" s="215"/>
+      <c r="H73" s="215"/>
+      <c r="I73" s="215"/>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.7">
       <c r="A74" s="24"/>
       <c r="F74" s="24"/>
     </row>
-    <row r="75" spans="1:9" ht="33" customHeight="1">
-      <c r="A75" s="183" t="s">
+    <row r="75" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A75" s="186" t="s">
         <v>386</v>
       </c>
-      <c r="B75" s="183"/>
-      <c r="C75" s="183"/>
-      <c r="D75" s="183"/>
-      <c r="E75" s="183"/>
-      <c r="F75" s="183"/>
-      <c r="G75" s="183"/>
-      <c r="H75" s="183"/>
-    </row>
-    <row r="76" spans="1:9">
-      <c r="A76" s="194" t="s">
+      <c r="B75" s="186"/>
+      <c r="C75" s="186"/>
+      <c r="D75" s="186"/>
+      <c r="E75" s="186"/>
+      <c r="F75" s="186"/>
+      <c r="G75" s="186"/>
+      <c r="H75" s="186"/>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.7">
+      <c r="A76" s="197" t="s">
         <v>381</v>
       </c>
-      <c r="B76" s="195"/>
-      <c r="C76" s="195"/>
-      <c r="D76" s="195"/>
-      <c r="E76" s="195"/>
-      <c r="F76" s="195"/>
-      <c r="G76" s="195"/>
-      <c r="H76" s="195"/>
-      <c r="I76" s="195"/>
-    </row>
-    <row r="78" spans="1:9" ht="15">
-      <c r="A78" s="199" t="s">
+      <c r="B76" s="198"/>
+      <c r="C76" s="198"/>
+      <c r="D76" s="198"/>
+      <c r="E76" s="198"/>
+      <c r="F76" s="198"/>
+      <c r="G76" s="198"/>
+      <c r="H76" s="198"/>
+      <c r="I76" s="198"/>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.7">
+      <c r="A78" s="202" t="s">
         <v>387</v>
       </c>
-      <c r="B78" s="199"/>
-      <c r="C78" s="199"/>
-      <c r="D78" s="199"/>
-      <c r="E78" s="199"/>
-      <c r="F78" s="199"/>
-      <c r="G78" s="199"/>
-      <c r="H78" s="199"/>
-      <c r="I78" s="199"/>
-    </row>
-    <row r="80" spans="1:9" ht="15" customHeight="1">
-      <c r="A80" s="177" t="s">
+      <c r="B78" s="202"/>
+      <c r="C78" s="202"/>
+      <c r="D78" s="202"/>
+      <c r="E78" s="202"/>
+      <c r="F78" s="202"/>
+      <c r="G78" s="202"/>
+      <c r="H78" s="202"/>
+      <c r="I78" s="202"/>
+    </row>
+    <row r="80" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A80" s="180" t="s">
         <v>388</v>
       </c>
-      <c r="B80" s="177"/>
-      <c r="C80" s="177"/>
-      <c r="D80" s="177"/>
-      <c r="E80" s="177"/>
-      <c r="F80" s="177"/>
-      <c r="G80" s="177"/>
-      <c r="H80" s="177"/>
-      <c r="I80" s="177"/>
-    </row>
-    <row r="81" spans="1:9">
-      <c r="A81" s="177"/>
-      <c r="B81" s="177"/>
-      <c r="C81" s="177"/>
-      <c r="D81" s="177"/>
-      <c r="E81" s="177"/>
-      <c r="F81" s="177"/>
-      <c r="G81" s="177"/>
-      <c r="H81" s="177"/>
-      <c r="I81" s="177"/>
-    </row>
-    <row r="83" spans="1:9">
-      <c r="F83" s="196" t="s">
+      <c r="B80" s="180"/>
+      <c r="C80" s="180"/>
+      <c r="D80" s="180"/>
+      <c r="E80" s="180"/>
+      <c r="F80" s="180"/>
+      <c r="G80" s="180"/>
+      <c r="H80" s="180"/>
+      <c r="I80" s="180"/>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.7">
+      <c r="A81" s="180"/>
+      <c r="B81" s="180"/>
+      <c r="C81" s="180"/>
+      <c r="D81" s="180"/>
+      <c r="E81" s="180"/>
+      <c r="F81" s="180"/>
+      <c r="G81" s="180"/>
+      <c r="H81" s="180"/>
+      <c r="I81" s="180"/>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.7">
+      <c r="F83" s="199" t="s">
         <v>342</v>
       </c>
-      <c r="G83" s="197"/>
-      <c r="H83" s="198"/>
-      <c r="I83" s="198"/>
-    </row>
-    <row r="84" spans="1:9">
-      <c r="F84" s="196"/>
-      <c r="G84" s="197"/>
-      <c r="H84" s="198"/>
-      <c r="I84" s="198"/>
-    </row>
-    <row r="85" spans="1:9">
+      <c r="G83" s="200"/>
+      <c r="H83" s="201"/>
+      <c r="I83" s="201"/>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.7">
+      <c r="F84" s="199"/>
+      <c r="G84" s="200"/>
+      <c r="H84" s="201"/>
+      <c r="I84" s="201"/>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.7">
       <c r="A85" s="21"/>
     </row>
   </sheetData>
@@ -9391,23 +9290,23 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr codeName="Sheet8"/>
   <dimension ref="A1:I32"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="25.5" x14ac:dyDescent="0.7"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" style="20" customWidth="1"/>
-    <col min="2" max="2" width="9.42578125" style="42" customWidth="1"/>
+    <col min="1" max="1" width="13.5546875" style="20" customWidth="1"/>
+    <col min="2" max="2" width="9.44140625" style="42" customWidth="1"/>
     <col min="3" max="3" width="13" style="42" customWidth="1"/>
     <col min="4" max="4" width="12" style="42" customWidth="1"/>
-    <col min="5" max="5" width="12.42578125" style="20" customWidth="1"/>
-    <col min="6" max="6" width="16.28515625" style="20" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="20" customWidth="1"/>
-    <col min="8" max="16384" width="8.7109375" style="20"/>
+    <col min="5" max="5" width="12.44140625" style="20" customWidth="1"/>
+    <col min="6" max="6" width="16.33203125" style="20" customWidth="1"/>
+    <col min="7" max="7" width="15.6640625" style="20" customWidth="1"/>
+    <col min="8" max="16384" width="8.6640625" style="20"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.7">
       <c r="A1" s="9"/>
       <c r="B1" s="41"/>
       <c r="C1" s="41"/>
@@ -9418,7 +9317,7 @@
       <c r="H1" s="9"/>
       <c r="I1" s="9"/>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.7">
       <c r="A2" s="9"/>
       <c r="B2" s="41"/>
       <c r="C2" s="41"/>
@@ -9429,7 +9328,7 @@
       <c r="H2" s="9"/>
       <c r="I2" s="9"/>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.7">
       <c r="B3" s="41"/>
       <c r="C3" s="41"/>
       <c r="D3" s="41"/>
@@ -9439,20 +9338,20 @@
       <c r="H3" s="9"/>
       <c r="I3" s="9"/>
     </row>
-    <row r="4" spans="1:9">
-      <c r="A4" s="225" t="s">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.7">
+      <c r="A4" s="228" t="s">
         <v>389</v>
       </c>
-      <c r="B4" s="169"/>
-      <c r="C4" s="169"/>
-      <c r="D4" s="169"/>
-      <c r="E4" s="169"/>
-      <c r="F4" s="169"/>
-      <c r="G4" s="169"/>
-      <c r="H4" s="99"/>
-      <c r="I4" s="99"/>
-    </row>
-    <row r="5" spans="1:9">
+      <c r="B4" s="172"/>
+      <c r="C4" s="172"/>
+      <c r="D4" s="172"/>
+      <c r="E4" s="172"/>
+      <c r="F4" s="172"/>
+      <c r="G4" s="172"/>
+      <c r="H4" s="97"/>
+      <c r="I4" s="97"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.7">
       <c r="A5" s="9"/>
       <c r="B5" s="41"/>
       <c r="C5" s="41"/>
@@ -9463,23 +9362,23 @@
       <c r="H5" s="9"/>
       <c r="I5" s="9"/>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.7">
       <c r="A6" s="12" t="s">
         <v>390</v>
       </c>
-      <c r="B6" s="151" t="str">
+      <c r="B6" s="154" t="str">
         <f>Data!B5</f>
-        <v/>
-      </c>
-      <c r="C6" s="151"/>
-      <c r="D6" s="151"/>
+        <v>Pushkar Singh</v>
+      </c>
+      <c r="C6" s="154"/>
+      <c r="D6" s="154"/>
       <c r="E6" s="9"/>
       <c r="F6" s="9"/>
       <c r="G6" s="9"/>
       <c r="H6" s="9"/>
       <c r="I6" s="9"/>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.7">
       <c r="A7" s="9"/>
       <c r="B7" s="41"/>
       <c r="C7" s="41"/>
@@ -9490,7 +9389,7 @@
       <c r="H7" s="9"/>
       <c r="I7" s="9"/>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.7">
       <c r="A8" s="12" t="s">
         <v>338</v>
       </c>
@@ -9507,7 +9406,7 @@
       <c r="H8" s="9"/>
       <c r="I8" s="9"/>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.7">
       <c r="A9" s="9" t="s">
         <v>392</v>
       </c>
@@ -9520,42 +9419,42 @@
       <c r="H9" s="9"/>
       <c r="I9" s="9"/>
     </row>
-    <row r="10" spans="1:9" ht="15" customHeight="1">
-      <c r="A10" s="176" t="s">
+    <row r="10" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A10" s="179" t="s">
         <v>393</v>
       </c>
-      <c r="B10" s="176"/>
-      <c r="C10" s="176"/>
-      <c r="D10" s="176"/>
-      <c r="E10" s="176"/>
-      <c r="F10" s="176"/>
-      <c r="G10" s="176"/>
+      <c r="B10" s="179"/>
+      <c r="C10" s="179"/>
+      <c r="D10" s="179"/>
+      <c r="E10" s="179"/>
+      <c r="F10" s="179"/>
+      <c r="G10" s="179"/>
       <c r="H10" s="9"/>
       <c r="I10" s="9"/>
     </row>
-    <row r="11" spans="1:9">
-      <c r="A11" s="176"/>
-      <c r="B11" s="176"/>
-      <c r="C11" s="176"/>
-      <c r="D11" s="176"/>
-      <c r="E11" s="176"/>
-      <c r="F11" s="176"/>
-      <c r="G11" s="176"/>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.7">
+      <c r="A11" s="179"/>
+      <c r="B11" s="179"/>
+      <c r="C11" s="179"/>
+      <c r="D11" s="179"/>
+      <c r="E11" s="179"/>
+      <c r="F11" s="179"/>
+      <c r="G11" s="179"/>
       <c r="H11" s="9"/>
       <c r="I11" s="9"/>
     </row>
-    <row r="12" spans="1:9">
-      <c r="A12" s="176"/>
-      <c r="B12" s="176"/>
-      <c r="C12" s="176"/>
-      <c r="D12" s="176"/>
-      <c r="E12" s="176"/>
-      <c r="F12" s="176"/>
-      <c r="G12" s="176"/>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.7">
+      <c r="A12" s="179"/>
+      <c r="B12" s="179"/>
+      <c r="C12" s="179"/>
+      <c r="D12" s="179"/>
+      <c r="E12" s="179"/>
+      <c r="F12" s="179"/>
+      <c r="G12" s="179"/>
       <c r="H12" s="9"/>
       <c r="I12" s="9"/>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.7">
       <c r="A13" s="9"/>
       <c r="B13" s="41"/>
       <c r="C13" s="41"/>
@@ -9566,175 +9465,181 @@
       <c r="H13" s="9"/>
       <c r="I13" s="9"/>
     </row>
-    <row r="14" spans="1:9" ht="92.25" customHeight="1">
-      <c r="A14" s="204" t="s">
+    <row r="14" spans="1:9" ht="92.25" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A14" s="207" t="s">
         <v>394</v>
       </c>
-      <c r="B14" s="204"/>
-      <c r="C14" s="83" t="s">
+      <c r="B14" s="207"/>
+      <c r="C14" s="81" t="s">
         <v>395</v>
       </c>
-      <c r="D14" s="83" t="s">
+      <c r="D14" s="81" t="s">
         <v>396</v>
       </c>
-      <c r="E14" s="83" t="s">
+      <c r="E14" s="81" t="s">
         <v>397</v>
       </c>
-      <c r="F14" s="85" t="s">
+      <c r="F14" s="83" t="s">
         <v>398</v>
       </c>
-      <c r="G14" s="85" t="s">
+      <c r="G14" s="83" t="s">
         <v>399</v>
       </c>
-      <c r="H14" s="74"/>
-      <c r="I14" s="86"/>
-    </row>
-    <row r="15" spans="1:9" ht="80.099999999999994" customHeight="1">
-      <c r="A15" s="154" t="str">
+      <c r="H14" s="72"/>
+      <c r="I14" s="84"/>
+    </row>
+    <row r="15" spans="1:9" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A15" s="157" t="str">
         <f>Data!CE5</f>
-        <v/>
-      </c>
-      <c r="B15" s="154"/>
-      <c r="C15" s="84" t="str">
+        <v>Satender Kumar
+159-160,1st floor, Pocket-7, Sector-24 Rohini Delhi-85</v>
+      </c>
+      <c r="B15" s="157"/>
+      <c r="C15" s="82" t="str">
         <f>Data!CF5</f>
-        <v/>
-      </c>
-      <c r="D15" s="82" t="str">
+        <v>Father</v>
+      </c>
+      <c r="D15" s="80">
         <f>Data!CG5</f>
-        <v/>
-      </c>
-      <c r="E15" s="84" t="str">
+        <v>67</v>
+      </c>
+      <c r="E15" s="82">
         <f>Data!CH5</f>
-        <v/>
-      </c>
-      <c r="F15" s="84" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="F15" s="82" t="str">
         <f>Data!CI5</f>
-        <v/>
-      </c>
-      <c r="G15" s="82" t="str">
+        <v>NA</v>
+      </c>
+      <c r="G15" s="80" t="str">
         <f>Data!CJ5</f>
-        <v/>
-      </c>
-      <c r="H15" s="74"/>
-      <c r="I15" s="74"/>
-    </row>
-    <row r="16" spans="1:9" ht="80.099999999999994" customHeight="1">
-      <c r="A16" s="154" t="str">
+        <v>Suman
+159-160,1st floor, Pocket-7, Sector-24 Rohini Delhi-85 
+Mother</v>
+      </c>
+      <c r="H15" s="72"/>
+      <c r="I15" s="72"/>
+    </row>
+    <row r="16" spans="1:9" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A16" s="157" t="str">
         <f>Data!CK5</f>
-        <v/>
-      </c>
-      <c r="B16" s="154"/>
-      <c r="C16" s="84" t="str">
+        <v>Suman
+159-160,1st floor, Pocket-7, Sector-24 Rohini Delhi-85</v>
+      </c>
+      <c r="B16" s="157"/>
+      <c r="C16" s="82" t="str">
         <f>Data!CL5</f>
-        <v/>
-      </c>
-      <c r="D16" s="82" t="str">
+        <v>Mother</v>
+      </c>
+      <c r="D16" s="80">
         <f>Data!CM5</f>
-        <v/>
-      </c>
-      <c r="E16" s="84" t="str">
+        <v>58</v>
+      </c>
+      <c r="E16" s="82">
         <f>Data!CN5</f>
-        <v/>
-      </c>
-      <c r="F16" s="84" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="F16" s="82" t="str">
         <f>Data!CO5</f>
-        <v/>
-      </c>
-      <c r="G16" s="82" t="str">
+        <v>NA</v>
+      </c>
+      <c r="G16" s="80" t="str">
         <f>Data!CP5</f>
-        <v/>
-      </c>
-      <c r="H16" s="74"/>
-      <c r="I16" s="74"/>
-    </row>
-    <row r="17" spans="1:9" ht="80.099999999999994" customHeight="1">
-      <c r="A17" s="154" t="str">
+        <v>Satender Kumar
+159-160,1st floor, Pocket-7, Sector-24 Rohini Delhi-85
+Father</v>
+      </c>
+      <c r="H16" s="72"/>
+      <c r="I16" s="72"/>
+    </row>
+    <row r="17" spans="1:9" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A17" s="157" t="str">
         <f>Data!CQ5</f>
         <v/>
       </c>
-      <c r="B17" s="154"/>
-      <c r="C17" s="84" t="str">
+      <c r="B17" s="157"/>
+      <c r="C17" s="82" t="str">
         <f>Data!CR5</f>
         <v/>
       </c>
-      <c r="D17" s="82" t="str">
+      <c r="D17" s="80" t="str">
         <f>Data!CS5</f>
         <v/>
       </c>
-      <c r="E17" s="84" t="str">
+      <c r="E17" s="82" t="str">
         <f>Data!CT5</f>
         <v/>
       </c>
-      <c r="F17" s="84" t="str">
+      <c r="F17" s="82" t="str">
         <f>Data!CU5</f>
         <v/>
       </c>
-      <c r="G17" s="82" t="str">
+      <c r="G17" s="80" t="str">
         <f>Data!CV5</f>
         <v/>
       </c>
-      <c r="H17" s="74"/>
-      <c r="I17" s="74"/>
-    </row>
-    <row r="18" spans="1:9" ht="80.099999999999994" customHeight="1">
-      <c r="A18" s="154" t="str">
+      <c r="H17" s="72"/>
+      <c r="I17" s="72"/>
+    </row>
+    <row r="18" spans="1:9" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A18" s="157" t="str">
         <f>Data!CW5</f>
         <v/>
       </c>
-      <c r="B18" s="154"/>
-      <c r="C18" s="84" t="str">
+      <c r="B18" s="157"/>
+      <c r="C18" s="82" t="str">
         <f>Data!CX5</f>
         <v/>
       </c>
-      <c r="D18" s="84" t="str">
+      <c r="D18" s="82" t="str">
         <f>Data!CY5</f>
         <v/>
       </c>
-      <c r="E18" s="84" t="str">
+      <c r="E18" s="82" t="str">
         <f>Data!CZ5</f>
         <v/>
       </c>
-      <c r="F18" s="84" t="str">
+      <c r="F18" s="82" t="str">
         <f>Data!DA5</f>
         <v/>
       </c>
-      <c r="G18" s="84" t="str">
+      <c r="G18" s="82" t="str">
         <f>Data!DB5</f>
         <v/>
       </c>
       <c r="H18" s="19"/>
       <c r="I18" s="19"/>
     </row>
-    <row r="19" spans="1:9" ht="80.099999999999994" customHeight="1">
-      <c r="A19" s="154" t="str">
+    <row r="19" spans="1:9" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A19" s="157" t="str">
         <f>Data!DC5</f>
         <v/>
       </c>
-      <c r="B19" s="154"/>
-      <c r="C19" s="84" t="str">
+      <c r="B19" s="157"/>
+      <c r="C19" s="82" t="str">
         <f>Data!DD5</f>
         <v/>
       </c>
-      <c r="D19" s="84" t="str">
+      <c r="D19" s="82" t="str">
         <f>Data!DE5</f>
         <v/>
       </c>
-      <c r="E19" s="84" t="str">
+      <c r="E19" s="82" t="str">
         <f>Data!DF5</f>
         <v/>
       </c>
-      <c r="F19" s="84" t="str">
+      <c r="F19" s="82" t="str">
         <f>Data!DG5</f>
         <v/>
       </c>
-      <c r="G19" s="84" t="str">
+      <c r="G19" s="82" t="str">
         <f>Data!DH5</f>
         <v/>
       </c>
       <c r="H19" s="19"/>
       <c r="I19" s="19"/>
     </row>
-    <row r="20" spans="1:9">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.7">
       <c r="A20" s="19"/>
       <c r="B20" s="19"/>
       <c r="C20" s="19"/>
@@ -9745,7 +9650,7 @@
       <c r="H20" s="19"/>
       <c r="I20" s="19"/>
     </row>
-    <row r="21" spans="1:9">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.7">
       <c r="A21" s="19"/>
       <c r="B21" s="19"/>
       <c r="C21" s="19"/>
@@ -9756,42 +9661,42 @@
       <c r="H21" s="19"/>
       <c r="I21" s="19"/>
     </row>
-    <row r="22" spans="1:9" ht="15" customHeight="1">
-      <c r="A22" s="226"/>
-      <c r="B22" s="226"/>
-      <c r="C22" s="106"/>
-      <c r="D22" s="191" t="s">
+    <row r="22" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A22" s="229"/>
+      <c r="B22" s="229"/>
+      <c r="C22" s="104"/>
+      <c r="D22" s="194" t="s">
         <v>342</v>
       </c>
-      <c r="E22" s="223"/>
-      <c r="F22" s="224"/>
-      <c r="G22" s="224"/>
+      <c r="E22" s="226"/>
+      <c r="F22" s="227"/>
+      <c r="G22" s="227"/>
       <c r="H22" s="19"/>
       <c r="I22" s="19"/>
     </row>
-    <row r="23" spans="1:9">
-      <c r="A23" s="226"/>
-      <c r="B23" s="226"/>
-      <c r="C23" s="106"/>
-      <c r="D23" s="191"/>
-      <c r="E23" s="223"/>
-      <c r="F23" s="224"/>
-      <c r="G23" s="224"/>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.7">
+      <c r="A23" s="229"/>
+      <c r="B23" s="229"/>
+      <c r="C23" s="104"/>
+      <c r="D23" s="194"/>
+      <c r="E23" s="226"/>
+      <c r="F23" s="227"/>
+      <c r="G23" s="227"/>
       <c r="H23" s="19"/>
       <c r="I23" s="19"/>
     </row>
-    <row r="24" spans="1:9">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.7">
       <c r="A24" s="19"/>
       <c r="B24" s="19"/>
-      <c r="C24" s="106"/>
-      <c r="D24" s="106"/>
-      <c r="E24" s="106"/>
+      <c r="C24" s="104"/>
+      <c r="D24" s="104"/>
+      <c r="E24" s="104"/>
       <c r="F24" s="19"/>
       <c r="G24" s="19"/>
       <c r="H24" s="19"/>
       <c r="I24" s="19"/>
     </row>
-    <row r="25" spans="1:9">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.7">
       <c r="A25" s="19"/>
       <c r="B25" s="19"/>
       <c r="C25" s="19"/>
@@ -9802,7 +9707,7 @@
       <c r="H25" s="19"/>
       <c r="I25" s="19"/>
     </row>
-    <row r="26" spans="1:9">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.7">
       <c r="A26" s="19"/>
       <c r="B26" s="19"/>
       <c r="C26" s="19"/>
@@ -9813,20 +9718,20 @@
       <c r="H26" s="19"/>
       <c r="I26" s="19"/>
     </row>
-    <row r="27" spans="1:9">
-      <c r="A27" s="226" t="s">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.7">
+      <c r="A27" s="229" t="s">
         <v>400</v>
       </c>
-      <c r="B27" s="226"/>
-      <c r="C27" s="226"/>
-      <c r="D27" s="227"/>
-      <c r="E27" s="227"/>
+      <c r="B27" s="229"/>
+      <c r="C27" s="229"/>
+      <c r="D27" s="230"/>
+      <c r="E27" s="230"/>
       <c r="F27" s="19"/>
       <c r="G27" s="19"/>
       <c r="H27" s="19"/>
       <c r="I27" s="19"/>
     </row>
-    <row r="28" spans="1:9">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.7">
       <c r="A28" s="19"/>
       <c r="B28" s="19"/>
       <c r="C28" s="19"/>
@@ -9837,7 +9742,7 @@
       <c r="H28" s="19"/>
       <c r="I28" s="19"/>
     </row>
-    <row r="29" spans="1:9">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.7">
       <c r="A29" s="19"/>
       <c r="B29" s="19"/>
       <c r="C29" s="19"/>
@@ -9848,31 +9753,31 @@
       <c r="H29" s="19"/>
       <c r="I29" s="19"/>
     </row>
-    <row r="30" spans="1:9">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.7">
       <c r="A30" s="9"/>
       <c r="B30" s="19"/>
       <c r="C30" s="19"/>
-      <c r="D30" s="191" t="s">
+      <c r="D30" s="194" t="s">
         <v>345</v>
       </c>
-      <c r="E30" s="223"/>
-      <c r="F30" s="224"/>
-      <c r="G30" s="224"/>
+      <c r="E30" s="226"/>
+      <c r="F30" s="227"/>
+      <c r="G30" s="227"/>
       <c r="H30" s="19"/>
       <c r="I30" s="19"/>
     </row>
-    <row r="31" spans="1:9">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.7">
       <c r="A31" s="19"/>
       <c r="B31" s="19"/>
       <c r="C31" s="19"/>
-      <c r="D31" s="191"/>
-      <c r="E31" s="223"/>
-      <c r="F31" s="224"/>
-      <c r="G31" s="224"/>
+      <c r="D31" s="194"/>
+      <c r="E31" s="226"/>
+      <c r="F31" s="227"/>
+      <c r="G31" s="227"/>
       <c r="H31" s="19"/>
       <c r="I31" s="19"/>
     </row>
-    <row r="32" spans="1:9">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.7">
       <c r="A32" s="19"/>
       <c r="B32" s="19"/>
       <c r="C32" s="19"/>
@@ -9908,7 +9813,378 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <sheetPr codeName="Sheet9"/>
+  <dimension ref="A6:H36"/>
+  <sheetFormatPr defaultRowHeight="25.5" x14ac:dyDescent="0.7"/>
+  <cols>
+    <col min="3" max="3" width="10.6640625" customWidth="1"/>
+    <col min="4" max="4" width="12.109375" customWidth="1"/>
+    <col min="5" max="5" width="11.5546875" customWidth="1"/>
+    <col min="6" max="6" width="12.44140625" customWidth="1"/>
+    <col min="7" max="7" width="14.6640625" customWidth="1"/>
+    <col min="8" max="8" width="12.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.7">
+      <c r="A6" s="233" t="s">
+        <v>401</v>
+      </c>
+      <c r="B6" s="233"/>
+      <c r="C6" s="233"/>
+      <c r="D6" s="233"/>
+      <c r="E6" s="233"/>
+      <c r="F6" s="233"/>
+      <c r="G6" s="233"/>
+      <c r="H6" s="233"/>
+    </row>
+    <row r="8" spans="1:8" ht="199.5" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A8" s="232" t="s">
+        <v>402</v>
+      </c>
+      <c r="B8" s="232"/>
+      <c r="C8" s="232"/>
+      <c r="D8" s="232"/>
+      <c r="E8" s="232"/>
+      <c r="F8" s="232"/>
+      <c r="G8" s="232"/>
+      <c r="H8" s="232"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.7">
+      <c r="A9" s="49"/>
+      <c r="B9" s="49"/>
+      <c r="C9" s="49"/>
+      <c r="D9" s="49"/>
+      <c r="E9" s="49"/>
+      <c r="F9" s="49"/>
+      <c r="G9" s="49"/>
+      <c r="H9" s="49"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.7">
+      <c r="A10" s="232" t="s">
+        <v>403</v>
+      </c>
+      <c r="B10" s="232"/>
+      <c r="C10" s="232" t="str">
+        <f>Data!B5</f>
+        <v>Pushkar Singh</v>
+      </c>
+      <c r="D10" s="232"/>
+      <c r="E10" s="232"/>
+      <c r="F10" s="232"/>
+      <c r="G10" s="232"/>
+      <c r="H10" s="232"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.7">
+      <c r="A11" s="232" t="s">
+        <v>404</v>
+      </c>
+      <c r="B11" s="232"/>
+      <c r="C11" s="234"/>
+      <c r="D11" s="234"/>
+      <c r="E11" s="234"/>
+      <c r="F11" s="234"/>
+      <c r="G11" s="234"/>
+      <c r="H11" s="234"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.7">
+      <c r="A12" s="232" t="s">
+        <v>405</v>
+      </c>
+      <c r="B12" s="232"/>
+      <c r="C12" s="234"/>
+      <c r="D12" s="234"/>
+      <c r="E12" s="234"/>
+      <c r="F12" s="234"/>
+      <c r="G12" s="234"/>
+      <c r="H12" s="234"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.7">
+      <c r="A13" s="232" t="s">
+        <v>250</v>
+      </c>
+      <c r="B13" s="232"/>
+      <c r="C13" s="231" t="e">
+        <f>Data!FX5</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D13" s="232"/>
+      <c r="E13" s="232"/>
+      <c r="F13" s="232"/>
+      <c r="G13" s="232"/>
+      <c r="H13" s="232"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.7">
+      <c r="A14" s="49"/>
+      <c r="B14" s="49"/>
+      <c r="C14" s="49"/>
+      <c r="D14" s="49"/>
+      <c r="E14" s="49"/>
+      <c r="F14" s="49"/>
+      <c r="G14" s="49"/>
+      <c r="H14" s="49"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.7">
+      <c r="A15" s="49"/>
+      <c r="B15" s="49"/>
+      <c r="C15" s="49"/>
+      <c r="D15" s="49"/>
+      <c r="E15" s="49"/>
+      <c r="F15" s="49"/>
+      <c r="G15" s="49"/>
+      <c r="H15" s="49"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.7">
+      <c r="A16" s="49"/>
+      <c r="B16" s="49"/>
+      <c r="C16" s="49"/>
+      <c r="D16" s="49"/>
+      <c r="E16" s="49"/>
+      <c r="F16" s="49"/>
+      <c r="G16" s="49"/>
+      <c r="H16" s="49"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.7">
+      <c r="A17" s="49"/>
+      <c r="B17" s="49"/>
+      <c r="C17" s="49"/>
+      <c r="D17" s="49"/>
+      <c r="E17" s="49"/>
+      <c r="F17" s="49"/>
+      <c r="G17" s="49"/>
+      <c r="H17" s="49"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.7">
+      <c r="A18" s="49"/>
+      <c r="B18" s="49"/>
+      <c r="C18" s="49"/>
+      <c r="D18" s="49"/>
+      <c r="E18" s="49"/>
+      <c r="F18" s="49"/>
+      <c r="G18" s="49"/>
+      <c r="H18" s="49"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.7">
+      <c r="A19" s="49"/>
+      <c r="B19" s="49"/>
+      <c r="C19" s="49"/>
+      <c r="D19" s="49"/>
+      <c r="E19" s="49"/>
+      <c r="F19" s="49"/>
+      <c r="G19" s="49"/>
+      <c r="H19" s="49"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.7">
+      <c r="A20" s="49"/>
+      <c r="B20" s="49"/>
+      <c r="C20" s="49"/>
+      <c r="D20" s="49"/>
+      <c r="E20" s="49"/>
+      <c r="F20" s="49"/>
+      <c r="G20" s="49"/>
+      <c r="H20" s="49"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.7">
+      <c r="A21" s="49"/>
+      <c r="B21" s="49"/>
+      <c r="C21" s="49"/>
+      <c r="D21" s="49"/>
+      <c r="E21" s="49"/>
+      <c r="F21" s="49"/>
+      <c r="G21" s="49"/>
+      <c r="H21" s="49"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.7">
+      <c r="A22" s="49"/>
+      <c r="B22" s="49"/>
+      <c r="C22" s="49"/>
+      <c r="D22" s="49"/>
+      <c r="E22" s="49"/>
+      <c r="F22" s="49"/>
+      <c r="G22" s="49"/>
+      <c r="H22" s="49"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.7">
+      <c r="A23" s="49"/>
+      <c r="B23" s="49"/>
+      <c r="C23" s="49"/>
+      <c r="D23" s="49"/>
+      <c r="E23" s="49"/>
+      <c r="F23" s="49"/>
+      <c r="G23" s="49"/>
+      <c r="H23" s="49"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.7">
+      <c r="A24" s="49"/>
+      <c r="B24" s="49"/>
+      <c r="C24" s="49"/>
+      <c r="D24" s="49"/>
+      <c r="E24" s="49"/>
+      <c r="F24" s="49"/>
+      <c r="G24" s="49"/>
+      <c r="H24" s="49"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.7">
+      <c r="A25" s="49"/>
+      <c r="B25" s="49"/>
+      <c r="C25" s="49"/>
+      <c r="D25" s="49"/>
+      <c r="E25" s="49"/>
+      <c r="F25" s="49"/>
+      <c r="G25" s="49"/>
+      <c r="H25" s="49"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.7">
+      <c r="A26" s="49"/>
+      <c r="B26" s="49"/>
+      <c r="C26" s="49"/>
+      <c r="D26" s="49"/>
+      <c r="E26" s="49"/>
+      <c r="F26" s="49"/>
+      <c r="G26" s="49"/>
+      <c r="H26" s="49"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.7">
+      <c r="A27" s="49"/>
+      <c r="B27" s="49"/>
+      <c r="C27" s="49"/>
+      <c r="D27" s="49"/>
+      <c r="E27" s="49"/>
+      <c r="F27" s="49"/>
+      <c r="G27" s="49"/>
+      <c r="H27" s="49"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.7">
+      <c r="A28" s="49"/>
+      <c r="B28" s="49"/>
+      <c r="C28" s="49"/>
+      <c r="D28" s="49"/>
+      <c r="E28" s="49"/>
+      <c r="F28" s="49"/>
+      <c r="G28" s="49"/>
+      <c r="H28" s="49"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.7">
+      <c r="A29" s="49"/>
+      <c r="B29" s="49"/>
+      <c r="C29" s="49"/>
+      <c r="D29" s="49"/>
+      <c r="E29" s="49"/>
+      <c r="F29" s="49"/>
+      <c r="G29" s="49"/>
+      <c r="H29" s="49"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.7">
+      <c r="A30" s="49"/>
+      <c r="B30" s="49"/>
+      <c r="C30" s="49"/>
+      <c r="D30" s="49"/>
+      <c r="E30" s="49"/>
+      <c r="F30" s="49"/>
+      <c r="G30" s="49"/>
+      <c r="H30" s="49"/>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.7">
+      <c r="A31" s="49"/>
+      <c r="B31" s="49"/>
+      <c r="C31" s="49"/>
+      <c r="D31" s="49"/>
+      <c r="E31" s="49"/>
+      <c r="F31" s="49"/>
+      <c r="G31" s="49"/>
+      <c r="H31" s="49"/>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.7">
+      <c r="A32" s="49"/>
+      <c r="B32" s="49"/>
+      <c r="C32" s="49"/>
+      <c r="D32" s="49"/>
+      <c r="E32" s="49"/>
+      <c r="F32" s="49"/>
+      <c r="G32" s="49"/>
+      <c r="H32" s="49"/>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.7">
+      <c r="A33" s="49"/>
+      <c r="B33" s="49"/>
+      <c r="C33" s="49"/>
+      <c r="D33" s="49"/>
+      <c r="E33" s="49"/>
+      <c r="F33" s="49"/>
+      <c r="G33" s="49"/>
+      <c r="H33" s="49"/>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.7">
+      <c r="A34" s="49"/>
+      <c r="B34" s="49"/>
+      <c r="C34" s="49"/>
+      <c r="D34" s="49"/>
+      <c r="E34" s="49"/>
+      <c r="F34" s="49"/>
+      <c r="G34" s="49"/>
+      <c r="H34" s="49"/>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.7">
+      <c r="A35" s="49"/>
+      <c r="B35" s="49"/>
+      <c r="C35" s="49"/>
+      <c r="D35" s="49"/>
+      <c r="E35" s="49"/>
+      <c r="F35" s="49"/>
+      <c r="G35" s="49"/>
+      <c r="H35" s="49"/>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.7">
+      <c r="A36" s="49"/>
+      <c r="B36" s="49"/>
+      <c r="C36" s="49"/>
+      <c r="D36" s="49"/>
+      <c r="E36" s="49"/>
+      <c r="F36" s="49"/>
+      <c r="G36" s="49"/>
+      <c r="H36" s="49"/>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="C13:H13"/>
+    <mergeCell ref="A6:H6"/>
+    <mergeCell ref="A8:H8"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="C10:H10"/>
+    <mergeCell ref="C11:H11"/>
+    <mergeCell ref="C12:H12"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" copies="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="dac5fce4-5bf5-4d72-ad05-8affa4a364ec">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="f5b4b972-ef2d-40c8-a840-80157aad3d6b" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101006797DF32A80EF04EBAF1E4E9FD8B028A" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="4f8a80b84dca43fafda364f6a2bd00dd">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="dac5fce4-5bf5-4d72-ad05-8affa4a364ec" xmlns:ns3="f5b4b972-ef2d-40c8-a840-80157aad3d6b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="188fe6a3fb9f0fbde03645453fa1572a" ns2:_="" ns3:_="">
     <xsd:import namespace="dac5fce4-5bf5-4d72-ad05-8affa4a364ec"/>
@@ -10145,34 +10421,40 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="dac5fce4-5bf5-4d72-ad05-8affa4a364ec">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="f5b4b972-ef2d-40c8-a840-80157aad3d6b" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EAE8D5FF-634E-4903-8332-D58F7F46E181}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{272DCA59-27F6-4926-B3A0-175D56F1725A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="dac5fce4-5bf5-4d72-ad05-8affa4a364ec"/>
+    <ds:schemaRef ds:uri="f5b4b972-ef2d-40c8-a840-80157aad3d6b"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{272DCA59-27F6-4926-B3A0-175D56F1725A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{888A73F9-A9BF-42CB-9C17-A88C1A935026}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{888A73F9-A9BF-42CB-9C17-A88C1A935026}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EAE8D5FF-634E-4903-8332-D58F7F46E181}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="dac5fce4-5bf5-4d72-ad05-8affa4a364ec"/>
+    <ds:schemaRef ds:uri="f5b4b972-ef2d-40c8-a840-80157aad3d6b"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>